--- a/produkte+.xlsx
+++ b/produkte+.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\statistika shitje BI\FAJLET PER UPDATE TE STATISTIKA SHITJESH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92639820-FB4F-4BE5-8157-E661E4161CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB43F28-0752-4DF3-943F-04C70A184525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F852DC8A-6273-46A5-80EE-4F7A2FD95859}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8122" uniqueCount="1750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8138" uniqueCount="1758">
   <si>
     <t>TOTAL</t>
   </si>
@@ -5288,6 +5288,30 @@
   </si>
   <si>
     <t>Deka Gel Power 400ml Jeshil</t>
+  </si>
+  <si>
+    <t>B0001289</t>
+  </si>
+  <si>
+    <t>Set 2 Deka Gel Power 400ml+ Sfungjer Enesh Macromax</t>
+  </si>
+  <si>
+    <t>B6007039</t>
+  </si>
+  <si>
+    <t>Deka Gel Power Jeshil 4.5 Lit</t>
+  </si>
+  <si>
+    <t>B7005097</t>
+  </si>
+  <si>
+    <t>Deka Pllakash Blu 4.5 kg</t>
+  </si>
+  <si>
+    <t>B0001291</t>
+  </si>
+  <si>
+    <t>Set Deka Liquid 22mz  x 3 cope</t>
   </si>
 </sst>
 </file>
@@ -32966,10 +32990,10 @@
         <v>0</v>
       </c>
       <c r="G2" s="2">
-        <v>69.543928911036403</v>
+        <v>68.698954388059803</v>
       </c>
       <c r="H2" s="2">
-        <v>311.90452116599823</v>
+        <v>308.11481043044819</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -32989,13 +33013,13 @@
         <v>30</v>
       </c>
       <c r="F3" s="2">
-        <v>91.779841408224428</v>
+        <v>89.842854985552009</v>
       </c>
       <c r="G3" s="2">
-        <v>113.27984140822443</v>
+        <v>111.34285498555201</v>
       </c>
       <c r="H3" s="2">
-        <v>566.39920704112217</v>
+        <v>556.71427492776002</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -33015,13 +33039,13 @@
         <v>30</v>
       </c>
       <c r="F4" s="2">
-        <v>64.457434250968262</v>
+        <v>63.07011857820418</v>
       </c>
       <c r="G4" s="2">
-        <v>85.957434250968262</v>
+        <v>84.570118578204188</v>
       </c>
       <c r="H4" s="2">
-        <v>200.28082180475604</v>
+        <v>197.04837628721577</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -33093,13 +33117,13 @@
         <v>30</v>
       </c>
       <c r="F7" s="2">
-        <v>31.235231594578597</v>
+        <v>30.905302471447129</v>
       </c>
       <c r="G7" s="2">
-        <v>52.735231594578593</v>
+        <v>52.405302471447129</v>
       </c>
       <c r="H7" s="2">
-        <v>168.7527411026515</v>
+        <v>167.69696790863082</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -33119,13 +33143,13 @@
         <v>63</v>
       </c>
       <c r="F8" s="2">
-        <v>34.755867517142853</v>
+        <v>34.319262775238101</v>
       </c>
       <c r="G8" s="2">
-        <v>56.255867517142853</v>
+        <v>55.819262775238101</v>
       </c>
       <c r="H8" s="2">
-        <v>196.89553630999998</v>
+        <v>195.36741971333336</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -33197,13 +33221,13 @@
         <v>30</v>
       </c>
       <c r="F11" s="2">
-        <v>90.019731262563766</v>
+        <v>88.714878008326835</v>
       </c>
       <c r="G11" s="2">
-        <v>111.51973126256377</v>
+        <v>110.21487800832683</v>
       </c>
       <c r="H11" s="2">
-        <v>312.25524753517851</v>
+        <v>308.60165842331514</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -33301,13 +33325,13 @@
         <v>30</v>
       </c>
       <c r="F15" s="2">
-        <v>72.424281633074557</v>
+        <v>71.271401788168646</v>
       </c>
       <c r="G15" s="2">
-        <v>93.924281633074557</v>
+        <v>92.771401788168646</v>
       </c>
       <c r="H15" s="2">
-        <v>152.15733624558078</v>
+        <v>150.28967089683323</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -33327,13 +33351,13 @@
         <v>30</v>
       </c>
       <c r="F16" s="2">
-        <v>122.42543172222223</v>
+        <v>120.16833172222222</v>
       </c>
       <c r="G16" s="2">
-        <v>143.92543172222224</v>
+        <v>141.66833172222221</v>
       </c>
       <c r="H16" s="2">
-        <v>25.906577710000004</v>
+        <v>25.500299709999997</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -33353,13 +33377,13 @@
         <v>63</v>
       </c>
       <c r="F17" s="2">
-        <v>142.40540110000001</v>
+        <v>140.14918110000002</v>
       </c>
       <c r="G17" s="2">
-        <v>163.90540110000001</v>
+        <v>161.64918110000002</v>
       </c>
       <c r="H17" s="2">
-        <v>163.90540110000001</v>
+        <v>161.64918110000002</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -33379,13 +33403,13 @@
         <v>30</v>
       </c>
       <c r="F18" s="2">
-        <v>52.125754066666673</v>
+        <v>51.17019406666666</v>
       </c>
       <c r="G18" s="2">
-        <v>73.625754066666673</v>
+        <v>72.670194066666653</v>
       </c>
       <c r="H18" s="2">
-        <v>110.43863110000001</v>
+        <v>109.00529109999998</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -33405,13 +33429,13 @@
         <v>30</v>
       </c>
       <c r="F19" s="2">
-        <v>52.019154066666673</v>
+        <v>51.066194066666661</v>
       </c>
       <c r="G19" s="2">
-        <v>73.519154066666673</v>
+        <v>72.566194066666668</v>
       </c>
       <c r="H19" s="2">
-        <v>110.27873110000002</v>
+        <v>108.8492911</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -33431,13 +33455,13 @@
         <v>30</v>
       </c>
       <c r="F20" s="2">
-        <v>51.53535406666667</v>
+        <v>50.594194066666667</v>
       </c>
       <c r="G20" s="2">
-        <v>73.03535406666667</v>
+        <v>72.09419406666666</v>
       </c>
       <c r="H20" s="2">
-        <v>109.5530311</v>
+        <v>108.14129109999999</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -33457,13 +33481,13 @@
         <v>30</v>
       </c>
       <c r="F21" s="2">
-        <v>48.21171838888889</v>
+        <v>47.256158388888878</v>
       </c>
       <c r="G21" s="2">
-        <v>69.711718388888897</v>
+        <v>68.756158388888878</v>
       </c>
       <c r="H21" s="2">
-        <v>209.13515516666669</v>
+        <v>206.26847516666663</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -33483,13 +33507,13 @@
         <v>30</v>
       </c>
       <c r="F22" s="2">
-        <v>48.105118388888883</v>
+        <v>47.152158388888878</v>
       </c>
       <c r="G22" s="2">
-        <v>69.605118388888883</v>
+        <v>68.652158388888878</v>
       </c>
       <c r="H22" s="2">
-        <v>208.81535516666665</v>
+        <v>205.95647516666662</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -33509,13 +33533,13 @@
         <v>63</v>
       </c>
       <c r="F23" s="2">
-        <v>47.621318388888881</v>
+        <v>46.680158388888877</v>
       </c>
       <c r="G23" s="2">
-        <v>69.121318388888881</v>
+        <v>68.180158388888884</v>
       </c>
       <c r="H23" s="2">
-        <v>207.36395516666664</v>
+        <v>204.54047516666665</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -33535,13 +33559,13 @@
         <v>30</v>
       </c>
       <c r="F24" s="2">
-        <v>47.953383388888888</v>
+        <v>46.997823388888882</v>
       </c>
       <c r="G24" s="2">
-        <v>69.453383388888881</v>
+        <v>68.497823388888889</v>
       </c>
       <c r="H24" s="2">
-        <v>416.72030033333328</v>
+        <v>410.98694033333334</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -33561,13 +33585,13 @@
         <v>30</v>
       </c>
       <c r="F25" s="2">
-        <v>47.43671338888889</v>
+        <v>46.481153388888877</v>
       </c>
       <c r="G25" s="2">
-        <v>68.93671338888889</v>
+        <v>67.981153388888885</v>
       </c>
       <c r="H25" s="2">
-        <v>620.43042049999997</v>
+        <v>611.83038049999993</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -33587,13 +33611,13 @@
         <v>30</v>
       </c>
       <c r="F26" s="2">
-        <v>61.413015550000004</v>
+        <v>60.457455549999992</v>
       </c>
       <c r="G26" s="2">
-        <v>82.913015550000011</v>
+        <v>81.957455549999992</v>
       </c>
       <c r="H26" s="2">
-        <v>82.913015550000011</v>
+        <v>81.957455549999992</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -33613,13 +33637,13 @@
         <v>63</v>
       </c>
       <c r="F27" s="2">
-        <v>57.528442922222226</v>
+        <v>56.226779722222219</v>
       </c>
       <c r="G27" s="2">
-        <v>79.028442922222226</v>
+        <v>77.726779722222219</v>
       </c>
       <c r="H27" s="2">
-        <v>237.08532876666669</v>
+        <v>233.18033916666667</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -33639,13 +33663,13 @@
         <v>63</v>
       </c>
       <c r="F28" s="2">
-        <v>55.732269827070922</v>
+        <v>54.455105970855101</v>
       </c>
       <c r="G28" s="2">
-        <v>77.232269827070922</v>
+        <v>75.955105970855101</v>
       </c>
       <c r="H28" s="2">
-        <v>231.69680948121277</v>
+        <v>227.8653179125653</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -33665,13 +33689,13 @@
         <v>63</v>
       </c>
       <c r="F29" s="2">
-        <v>51.744069827070923</v>
+        <v>50.564305970855109</v>
       </c>
       <c r="G29" s="2">
-        <v>73.244069827070916</v>
+        <v>72.064305970855116</v>
       </c>
       <c r="H29" s="2">
-        <v>219.73220948121275</v>
+        <v>216.19291791256535</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -33691,13 +33715,13 @@
         <v>63</v>
       </c>
       <c r="F30" s="2">
-        <v>57.300284588888893</v>
+        <v>56.003424722222221</v>
       </c>
       <c r="G30" s="2">
-        <v>78.8002845888889</v>
+        <v>77.503424722222221</v>
       </c>
       <c r="H30" s="2">
-        <v>472.8017075333334</v>
+        <v>465.02054833333329</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -33743,13 +33767,13 @@
         <v>30</v>
       </c>
       <c r="F32" s="2">
-        <v>138.29563739999998</v>
+        <v>135.33807955999998</v>
       </c>
       <c r="G32" s="2">
-        <v>159.79563739999998</v>
+        <v>156.83807955999998</v>
       </c>
       <c r="H32" s="2">
-        <v>1142.5388074099999</v>
+        <v>1121.3922688539999</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -33769,13 +33793,13 @@
         <v>63</v>
       </c>
       <c r="F33" s="2">
-        <v>111.36662818750001</v>
+        <v>108.9214656875</v>
       </c>
       <c r="G33" s="2">
-        <v>132.8666281875</v>
+        <v>130.42146568750002</v>
       </c>
       <c r="H33" s="2">
-        <v>265.733256375</v>
+        <v>260.84293137500003</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -33795,13 +33819,13 @@
         <v>63</v>
       </c>
       <c r="F34" s="2">
-        <v>102.26562818750001</v>
+        <v>100.0120656875</v>
       </c>
       <c r="G34" s="2">
-        <v>123.76562818750001</v>
+        <v>121.5120656875</v>
       </c>
       <c r="H34" s="2">
-        <v>247.53125637500003</v>
+        <v>243.024131375</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -33821,13 +33845,13 @@
         <v>63</v>
       </c>
       <c r="F35" s="2">
-        <v>106.18594818750002</v>
+        <v>103.99658568749999</v>
       </c>
       <c r="G35" s="2">
-        <v>127.68594818750002</v>
+        <v>125.49658568749999</v>
       </c>
       <c r="H35" s="2">
-        <v>255.37189637500003</v>
+        <v>250.99317137499997</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -33847,13 +33871,13 @@
         <v>63</v>
       </c>
       <c r="F36" s="2">
-        <v>109.91620172222224</v>
+        <v>107.50152172222222</v>
       </c>
       <c r="G36" s="2">
-        <v>131.41620172222224</v>
+        <v>129.00152172222221</v>
       </c>
       <c r="H36" s="2">
-        <v>394.24860516666672</v>
+        <v>387.00456516666662</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -33873,13 +33897,13 @@
         <v>63</v>
       </c>
       <c r="F37" s="2">
-        <v>101.08120172222223</v>
+        <v>98.852521722222207</v>
       </c>
       <c r="G37" s="2">
-        <v>122.58120172222223</v>
+        <v>120.35252172222221</v>
       </c>
       <c r="H37" s="2">
-        <v>367.74360516666673</v>
+        <v>361.05756516666662</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -33899,13 +33923,13 @@
         <v>63</v>
       </c>
       <c r="F38" s="2">
-        <v>103.94463172222223</v>
+        <v>101.76135172222223</v>
       </c>
       <c r="G38" s="2">
-        <v>125.44463172222223</v>
+        <v>123.26135172222223</v>
       </c>
       <c r="H38" s="2">
-        <v>376.33389516666671</v>
+        <v>369.78405516666669</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -33925,13 +33949,13 @@
         <v>63</v>
       </c>
       <c r="F39" s="2">
-        <v>109.01062818750002</v>
+        <v>106.61506568749999</v>
       </c>
       <c r="G39" s="2">
-        <v>130.5106281875</v>
+        <v>128.11506568749999</v>
       </c>
       <c r="H39" s="2">
-        <v>522.04251275000001</v>
+        <v>512.46026274999997</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -33951,13 +33975,13 @@
         <v>63</v>
       </c>
       <c r="F40" s="2">
-        <v>101.37262818750001</v>
+        <v>99.137865687499982</v>
       </c>
       <c r="G40" s="2">
-        <v>122.87262818750001</v>
+        <v>120.63786568749998</v>
       </c>
       <c r="H40" s="2">
-        <v>491.49051275000005</v>
+        <v>482.55146274999993</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -33977,13 +34001,13 @@
         <v>63</v>
       </c>
       <c r="F41" s="2">
-        <v>111.32728828361743</v>
+        <v>108.88292879498107</v>
       </c>
       <c r="G41" s="2">
-        <v>132.82728828361743</v>
+        <v>130.38292879498107</v>
       </c>
       <c r="H41" s="2">
-        <v>93.510410951666671</v>
+        <v>91.78958187166667</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -34003,13 +34027,13 @@
         <v>30</v>
       </c>
       <c r="F42" s="2">
-        <v>34.938101130952383</v>
+        <v>34.104685416666662</v>
       </c>
       <c r="G42" s="2">
-        <v>56.438101130952383</v>
+        <v>55.604685416666662</v>
       </c>
       <c r="H42" s="2">
-        <v>39.506670791666664</v>
+        <v>38.923279791666658</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -34029,13 +34053,13 @@
         <v>63</v>
       </c>
       <c r="F43" s="2">
-        <v>44.115544652777778</v>
+        <v>43.273439652777782</v>
       </c>
       <c r="G43" s="2">
-        <v>65.615544652777771</v>
+        <v>64.773439652777782</v>
       </c>
       <c r="H43" s="2">
-        <v>39.369326791666658</v>
+        <v>38.864063791666666</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -34055,13 +34079,13 @@
         <v>63</v>
       </c>
       <c r="F44" s="2">
-        <v>53.856773452777773</v>
+        <v>52.563391652777781</v>
       </c>
       <c r="G44" s="2">
-        <v>75.356773452777773</v>
+        <v>74.063391652777781</v>
       </c>
       <c r="H44" s="2">
-        <v>45.214064071666662</v>
+        <v>44.438034991666669</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -34081,13 +34105,13 @@
         <v>63</v>
       </c>
       <c r="F45" s="2">
-        <v>61.980724349999996</v>
+        <v>60.918407550000005</v>
       </c>
       <c r="G45" s="2">
-        <v>83.480724350000003</v>
+        <v>82.418407550000012</v>
       </c>
       <c r="H45" s="2">
-        <v>83.480724350000003</v>
+        <v>82.418407550000012</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -34107,13 +34131,13 @@
         <v>63</v>
       </c>
       <c r="F46" s="2">
-        <v>108.41245118991399</v>
+        <v>106.85680538702691</v>
       </c>
       <c r="G46" s="2">
-        <v>129.91245118991401</v>
+        <v>128.3568053870269</v>
       </c>
       <c r="H46" s="2">
-        <v>233.84241214184522</v>
+        <v>231.04224969664841</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -34133,13 +34157,13 @@
         <v>63</v>
       </c>
       <c r="F47" s="2">
-        <v>114.06239115663206</v>
+        <v>112.51300135444566</v>
       </c>
       <c r="G47" s="2">
-        <v>135.56239115663206</v>
+        <v>134.01300135444566</v>
       </c>
       <c r="H47" s="2">
-        <v>244.01230408193771</v>
+        <v>241.22340243800221</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -34159,13 +34183,13 @@
         <v>63</v>
       </c>
       <c r="F48" s="2">
-        <v>102.4515348357737</v>
+        <v>100.89311417250595</v>
       </c>
       <c r="G48" s="2">
-        <v>123.9515348357737</v>
+        <v>122.39311417250595</v>
       </c>
       <c r="H48" s="2">
-        <v>223.11276270439265</v>
+        <v>220.30760551051071</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -34185,13 +34209,13 @@
         <v>63</v>
       </c>
       <c r="F49" s="2">
-        <v>113.3386573540554</v>
+        <v>111.62041513803702</v>
       </c>
       <c r="G49" s="2">
-        <v>134.83865735405539</v>
+        <v>133.120415138037</v>
       </c>
       <c r="H49" s="2">
-        <v>177.98702770735312</v>
+        <v>175.71894798220885</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -34211,13 +34235,13 @@
         <v>63</v>
       </c>
       <c r="F50" s="2">
-        <v>119.75308216925831</v>
+        <v>118.04109595394061</v>
       </c>
       <c r="G50" s="2">
-        <v>141.25308216925831</v>
+        <v>139.54109595394061</v>
       </c>
       <c r="H50" s="2">
-        <v>186.45406846342098</v>
+        <v>184.19424665920161</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -34237,13 +34261,13 @@
         <v>63</v>
       </c>
       <c r="F51" s="2">
-        <v>109.48093238733732</v>
+        <v>107.76081229183039</v>
       </c>
       <c r="G51" s="2">
-        <v>130.9809323873373</v>
+        <v>129.2608122918304</v>
       </c>
       <c r="H51" s="2">
-        <v>172.89483075128524</v>
+        <v>170.62427222521615</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -34263,13 +34287,13 @@
         <v>63</v>
       </c>
       <c r="F52" s="2">
-        <v>111.26412242602511</v>
+        <v>109.25033446758246</v>
       </c>
       <c r="G52" s="2">
-        <v>132.7641224260251</v>
+        <v>130.75033446758246</v>
       </c>
       <c r="H52" s="2">
-        <v>663.82061213012548</v>
+        <v>653.75167233791228</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -34289,13 +34313,13 @@
         <v>63</v>
       </c>
       <c r="F53" s="2">
-        <v>106.26678245930702</v>
+        <v>104.24673850016372</v>
       </c>
       <c r="G53" s="2">
-        <v>127.76678245930702</v>
+        <v>125.74673850016372</v>
       </c>
       <c r="H53" s="2">
-        <v>638.83391229653512</v>
+        <v>628.73369250081862</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -34315,13 +34339,13 @@
         <v>30</v>
       </c>
       <c r="F54" s="2">
-        <v>88.344105544258312</v>
+        <v>87.029591404698195</v>
       </c>
       <c r="G54" s="2">
-        <v>109.84410554425831</v>
+        <v>108.52959140469819</v>
       </c>
       <c r="H54" s="2">
-        <v>36.248554829605247</v>
+        <v>35.814765163550405</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -34341,13 +34365,13 @@
         <v>30</v>
       </c>
       <c r="F55" s="2">
-        <v>1565.3851577309349</v>
+        <v>1532.7696144092311</v>
       </c>
       <c r="G55" s="2">
-        <v>1586.8851577309349</v>
+        <v>1554.2696144092311</v>
       </c>
       <c r="H55" s="2">
-        <v>7934.4257886546748</v>
+        <v>7771.3480720461557</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -34367,13 +34391,13 @@
         <v>63</v>
       </c>
       <c r="F56" s="2">
-        <v>86.569322408333335</v>
+        <v>85.50383274166667</v>
       </c>
       <c r="G56" s="2">
-        <v>108.06932240833333</v>
+        <v>107.00383274166667</v>
       </c>
       <c r="H56" s="2">
-        <v>194.524780335</v>
+        <v>192.606898935</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -34393,13 +34417,13 @@
         <v>63</v>
       </c>
       <c r="F57" s="2">
-        <v>77.432311232611099</v>
+        <v>76.329939929877781</v>
       </c>
       <c r="G57" s="2">
-        <v>98.932311232611099</v>
+        <v>97.829939929877781</v>
       </c>
       <c r="H57" s="2">
-        <v>178.07816021869999</v>
+        <v>176.09389187378002</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -34419,13 +34443,13 @@
         <v>63</v>
       </c>
       <c r="F58" s="2">
-        <v>98.269351429323294</v>
+        <v>96.962812857894733</v>
       </c>
       <c r="G58" s="2">
-        <v>119.76935142932329</v>
+        <v>118.46281285789473</v>
       </c>
       <c r="H58" s="2">
-        <v>158.09554388670676</v>
+        <v>156.37091297242105</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -34445,13 +34469,13 @@
         <v>30</v>
       </c>
       <c r="F59" s="2">
-        <v>80.60017849699247</v>
+        <v>79.293639925563895</v>
       </c>
       <c r="G59" s="2">
-        <v>102.10017849699247</v>
+        <v>100.79363992556389</v>
       </c>
       <c r="H59" s="2">
-        <v>183.78032129458646</v>
+        <v>181.42855186601503</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -34471,13 +34495,13 @@
         <v>30</v>
       </c>
       <c r="F60" s="2">
-        <v>72.23776648112208</v>
+        <v>70.650301034426718</v>
       </c>
       <c r="G60" s="2">
-        <v>93.73776648112208</v>
+        <v>92.150301034426718</v>
       </c>
       <c r="H60" s="2">
-        <v>93.73776648112208</v>
+        <v>92.150301034426718</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -34497,13 +34521,13 @@
         <v>30</v>
       </c>
       <c r="F61" s="2">
-        <v>75.644039503327647</v>
+        <v>74.013005679055397</v>
       </c>
       <c r="G61" s="2">
-        <v>97.144039503327647</v>
+        <v>95.513005679055397</v>
       </c>
       <c r="H61" s="2">
-        <v>145.71605925499148</v>
+        <v>143.26950851858311</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -34523,13 +34547,13 @@
         <v>63</v>
       </c>
       <c r="F62" s="2">
-        <v>64.086803934279274</v>
+        <v>62.684289397774364</v>
       </c>
       <c r="G62" s="2">
-        <v>85.586803934279274</v>
+        <v>84.184289397774364</v>
       </c>
       <c r="H62" s="2">
-        <v>157.47971923907386</v>
+        <v>154.89909249190484</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -34549,13 +34573,13 @@
         <v>30</v>
       </c>
       <c r="F63" s="2">
-        <v>62.4320771188832</v>
+        <v>61.218051437975298</v>
       </c>
       <c r="G63" s="2">
-        <v>83.9320771188832</v>
+        <v>82.718051437975305</v>
       </c>
       <c r="H63" s="2">
-        <v>27.697585449231457</v>
+        <v>27.296956974531852</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -34575,13 +34599,13 @@
         <v>30</v>
       </c>
       <c r="F64" s="2">
-        <v>39.525018881004414</v>
+        <v>38.659078594035911</v>
       </c>
       <c r="G64" s="2">
-        <v>61.025018881004414</v>
+        <v>60.159078594035911</v>
       </c>
       <c r="H64" s="2">
-        <v>305.12509440502208</v>
+        <v>300.79539297017953</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -34601,13 +34625,13 @@
         <v>30</v>
       </c>
       <c r="F65" s="2">
-        <v>49.769368881004418</v>
+        <v>48.68772859403591</v>
       </c>
       <c r="G65" s="2">
-        <v>71.269368881004425</v>
+        <v>70.187728594035917</v>
       </c>
       <c r="H65" s="2">
-        <v>356.34684440502213</v>
+        <v>350.93864297017956</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -34627,13 +34651,13 @@
         <v>30</v>
       </c>
       <c r="F66" s="2">
-        <v>72.487558290117647</v>
+        <v>70.896391962390808</v>
       </c>
       <c r="G66" s="2">
-        <v>93.987558290117647</v>
+        <v>92.396391962390808</v>
       </c>
       <c r="H66" s="2">
-        <v>93.987558290117647</v>
+        <v>92.396391962390808</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -34653,13 +34677,13 @@
         <v>30</v>
       </c>
       <c r="F67" s="2">
-        <v>83.62257011135496</v>
+        <v>81.943943361159313</v>
       </c>
       <c r="G67" s="2">
-        <v>105.12257011135496</v>
+        <v>103.44394336115931</v>
       </c>
       <c r="H67" s="2">
-        <v>157.68385516703245</v>
+        <v>155.16591504173897</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -34679,13 +34703,13 @@
         <v>63</v>
       </c>
       <c r="F68" s="2">
-        <v>64.791618177762288</v>
+        <v>63.375709656341947</v>
       </c>
       <c r="G68" s="2">
-        <v>86.291618177762288</v>
+        <v>84.87570965634194</v>
       </c>
       <c r="H68" s="2">
-        <v>172.58323635552458</v>
+        <v>169.75141931268388</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -34705,13 +34729,13 @@
         <v>30</v>
       </c>
       <c r="F69" s="2">
-        <v>56.791914811515156</v>
+        <v>55.574284508484851</v>
       </c>
       <c r="G69" s="2">
-        <v>78.291914811515156</v>
+        <v>77.074284508484851</v>
       </c>
       <c r="H69" s="2">
-        <v>25.836331887800004</v>
+        <v>25.434513887800001</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -34731,13 +34755,13 @@
         <v>30</v>
       </c>
       <c r="F70" s="2">
-        <v>76.548746850810574</v>
+        <v>75.08254919212176</v>
       </c>
       <c r="G70" s="2">
-        <v>98.048746850810574</v>
+        <v>96.58254919212176</v>
       </c>
       <c r="H70" s="2">
-        <v>98.048746850810574</v>
+        <v>96.58254919212176</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -34757,13 +34781,13 @@
         <v>30</v>
       </c>
       <c r="F71" s="2">
-        <v>78.017338718021634</v>
+        <v>76.456621407825992</v>
       </c>
       <c r="G71" s="2">
-        <v>99.517338718021634</v>
+        <v>97.956621407825992</v>
       </c>
       <c r="H71" s="2">
-        <v>149.27600807703246</v>
+        <v>146.93493211173899</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -34783,13 +34807,13 @@
         <v>30</v>
       </c>
       <c r="F72" s="2">
-        <v>69.281649096578988</v>
+        <v>67.913617826130917</v>
       </c>
       <c r="G72" s="2">
-        <v>90.781649096578988</v>
+        <v>89.413617826130917</v>
       </c>
       <c r="H72" s="2">
-        <v>181.56329819315798</v>
+        <v>178.82723565226183</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -34809,13 +34833,13 @@
         <v>30</v>
       </c>
       <c r="F73" s="2">
-        <v>68.693512792396803</v>
+        <v>67.392566355990382</v>
       </c>
       <c r="G73" s="2">
-        <v>90.193512792396803</v>
+        <v>88.892566355990382</v>
       </c>
       <c r="H73" s="2">
-        <v>90.193512792396803</v>
+        <v>88.892566355990382</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -34835,13 +34859,13 @@
         <v>30</v>
       </c>
       <c r="F74" s="2">
-        <v>60.896690088165201</v>
+        <v>59.556148459999548</v>
       </c>
       <c r="G74" s="2">
-        <v>82.396690088165201</v>
+        <v>81.056148459999548</v>
       </c>
       <c r="H74" s="2">
-        <v>164.7933801763304</v>
+        <v>162.1122969199991</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -34861,13 +34885,13 @@
         <v>30</v>
       </c>
       <c r="F75" s="2">
-        <v>66.746051253715336</v>
+        <v>65.268887169702211</v>
       </c>
       <c r="G75" s="2">
-        <v>88.246051253715336</v>
+        <v>86.768887169702211</v>
       </c>
       <c r="H75" s="2">
-        <v>88.246051253715336</v>
+        <v>86.768887169702211</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -34887,13 +34911,13 @@
         <v>30</v>
       </c>
       <c r="F76" s="2">
-        <v>60.195878549483744</v>
+        <v>58.870419273711377</v>
       </c>
       <c r="G76" s="2">
-        <v>81.695878549483751</v>
+        <v>80.370419273711377</v>
       </c>
       <c r="H76" s="2">
-        <v>163.3917570989675</v>
+        <v>160.74083854742275</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -34913,13 +34937,13 @@
         <v>30</v>
       </c>
       <c r="F77" s="2">
-        <v>66.296501053715332</v>
+        <v>65.04615696970221</v>
       </c>
       <c r="G77" s="2">
-        <v>87.796501053715332</v>
+        <v>86.54615696970221</v>
       </c>
       <c r="H77" s="2">
-        <v>87.796501053715332</v>
+        <v>86.54615696970221</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -34939,13 +34963,13 @@
         <v>30</v>
       </c>
       <c r="F78" s="2">
-        <v>58.513078349483742</v>
+        <v>57.22313907371138</v>
       </c>
       <c r="G78" s="2">
-        <v>80.013078349483749</v>
+        <v>78.72313907371138</v>
       </c>
       <c r="H78" s="2">
-        <v>160.0261566989675</v>
+        <v>157.44627814742276</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -34965,13 +34989,13 @@
         <v>63</v>
       </c>
       <c r="F79" s="2">
-        <v>28.059661166666665</v>
+        <v>27.737625388888883</v>
       </c>
       <c r="G79" s="2">
-        <v>49.559661166666665</v>
+        <v>49.237625388888887</v>
       </c>
       <c r="H79" s="2">
-        <v>49.559661166666665</v>
+        <v>49.237625388888887</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -34991,13 +35015,13 @@
         <v>63</v>
       </c>
       <c r="F80" s="2">
-        <v>30.145146426666663</v>
+        <v>29.791363540888881</v>
       </c>
       <c r="G80" s="2">
-        <v>51.645146426666663</v>
+        <v>51.291363540888881</v>
       </c>
       <c r="H80" s="2">
-        <v>51.645146426666663</v>
+        <v>51.291363540888881</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -35017,13 +35041,13 @@
         <v>63</v>
       </c>
       <c r="F81" s="2">
-        <v>12.514899999999999</v>
+        <v>12.500500000000001</v>
       </c>
       <c r="G81" s="2">
-        <v>34.014899999999997</v>
+        <v>34.000500000000002</v>
       </c>
       <c r="H81" s="2">
-        <v>34.014899999999997</v>
+        <v>34.000500000000002</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -35043,13 +35067,13 @@
         <v>63</v>
       </c>
       <c r="F82" s="2">
-        <v>23.890895106666665</v>
+        <v>23.652766242666669</v>
       </c>
       <c r="G82" s="2">
-        <v>45.390895106666662</v>
+        <v>45.152766242666672</v>
       </c>
       <c r="H82" s="2">
-        <v>113.47723776666666</v>
+        <v>112.88191560666668</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -35069,13 +35093,13 @@
         <v>63</v>
       </c>
       <c r="F83" s="2">
-        <v>25.893080366666666</v>
+        <v>25.623204394666672</v>
       </c>
       <c r="G83" s="2">
-        <v>47.393080366666666</v>
+        <v>47.123204394666672</v>
       </c>
       <c r="H83" s="2">
-        <v>118.48270091666666</v>
+        <v>117.80801098666669</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -35095,13 +35119,13 @@
         <v>63</v>
       </c>
       <c r="F84" s="2">
-        <v>21.904370549999999</v>
+        <v>21.716256549999997</v>
       </c>
       <c r="G84" s="2">
-        <v>43.404370549999996</v>
+        <v>43.216256549999997</v>
       </c>
       <c r="H84" s="2">
-        <v>217.02185274999999</v>
+        <v>216.08128274999999</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -35121,13 +35145,13 @@
         <v>63</v>
       </c>
       <c r="F85" s="2">
-        <v>23.90655581</v>
+        <v>23.686694702</v>
       </c>
       <c r="G85" s="2">
-        <v>45.40655581</v>
+        <v>45.186694701999997</v>
       </c>
       <c r="H85" s="2">
-        <v>227.03277904999999</v>
+        <v>225.93347351</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -35147,13 +35171,13 @@
         <v>30</v>
       </c>
       <c r="F86" s="2">
-        <v>24.036066219751085</v>
+        <v>23.973103396879136</v>
       </c>
       <c r="G86" s="2">
-        <v>45.536066219751085</v>
+        <v>45.473103396879139</v>
       </c>
       <c r="H86" s="2">
-        <v>45.536066219751085</v>
+        <v>45.473103396879139</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -35173,13 +35197,13 @@
         <v>30</v>
       </c>
       <c r="F87" s="2">
-        <v>102.54990687147394</v>
+        <v>101.29589664926336</v>
       </c>
       <c r="G87" s="2">
-        <v>124.04990687147394</v>
+        <v>122.79589664926336</v>
       </c>
       <c r="H87" s="2">
-        <v>60.164204832664858</v>
+        <v>59.556009874892723</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -35199,13 +35223,13 @@
         <v>30</v>
       </c>
       <c r="F88" s="2">
-        <v>97.110235863547771</v>
+        <v>96.283278942235469</v>
       </c>
       <c r="G88" s="2">
-        <v>118.61023586354777</v>
+        <v>117.78327894223547</v>
       </c>
       <c r="H88" s="2">
-        <v>57.525964393820665</v>
+        <v>57.124890286984204</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -35225,13 +35249,13 @@
         <v>30</v>
       </c>
       <c r="F89" s="2">
-        <v>99.673118965954842</v>
+        <v>98.941719790697121</v>
       </c>
       <c r="G89" s="2">
-        <v>121.17311896595484</v>
+        <v>120.44171979069712</v>
       </c>
       <c r="H89" s="2">
-        <v>58.768962698488096</v>
+        <v>58.414234098488102</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -35251,13 +35275,13 @@
         <v>30</v>
       </c>
       <c r="F90" s="2">
-        <v>101.6686461296555</v>
+        <v>100.93721742114093</v>
       </c>
       <c r="G90" s="2">
-        <v>123.1686461296555</v>
+        <v>122.43721742114093</v>
       </c>
       <c r="H90" s="2">
-        <v>59.736793372882914</v>
+        <v>59.382050449253349</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -35277,13 +35301,13 @@
         <v>30</v>
       </c>
       <c r="F91" s="2">
-        <v>101.88524396595484</v>
+        <v>100.95784479069712</v>
       </c>
       <c r="G91" s="2">
-        <v>123.38524396595484</v>
+        <v>122.45784479069712</v>
       </c>
       <c r="H91" s="2">
-        <v>59.841843323488099</v>
+        <v>59.392054723488101</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -35303,13 +35327,13 @@
         <v>30</v>
       </c>
       <c r="F92" s="2">
-        <v>101.88508846142743</v>
+        <v>100.95760834521241</v>
       </c>
       <c r="G92" s="2">
-        <v>123.38508846142743</v>
+        <v>122.45760834521241</v>
       </c>
       <c r="H92" s="2">
-        <v>59.841767903792302</v>
+        <v>59.391940047428015</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -35329,13 +35353,13 @@
         <v>30</v>
       </c>
       <c r="F93" s="2">
-        <v>79.302729830027445</v>
+        <v>78.647906765359267</v>
       </c>
       <c r="G93" s="2">
-        <v>100.80272983002745</v>
+        <v>100.14790676535927</v>
       </c>
       <c r="H93" s="2">
-        <v>97.274634285976475</v>
+        <v>96.642730028571691</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -35355,13 +35379,13 @@
         <v>30</v>
       </c>
       <c r="F94" s="2">
-        <v>77.867643563482403</v>
+        <v>77.242945575631609</v>
       </c>
       <c r="G94" s="2">
-        <v>99.367643563482403</v>
+        <v>98.742945575631609</v>
       </c>
       <c r="H94" s="2">
-        <v>95.889776038760516</v>
+        <v>95.286942480484498</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -35381,13 +35405,13 @@
         <v>30</v>
       </c>
       <c r="F95" s="2">
-        <v>80.430526665889474</v>
+        <v>79.901386424093261</v>
       </c>
       <c r="G95" s="2">
-        <v>101.93052666588947</v>
+        <v>101.40138642409326</v>
       </c>
       <c r="H95" s="2">
-        <v>98.362958232583338</v>
+        <v>97.852337899249989</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -35407,13 +35431,13 @@
         <v>30</v>
       </c>
       <c r="F96" s="2">
-        <v>82.426053829590131</v>
+        <v>81.896884054537068</v>
       </c>
       <c r="G96" s="2">
-        <v>103.92605382959013</v>
+        <v>103.39688405453707</v>
       </c>
       <c r="H96" s="2">
-        <v>100.28864194555447</v>
+        <v>99.777993112628266</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -35433,13 +35457,13 @@
         <v>30</v>
       </c>
       <c r="F97" s="2">
-        <v>82.642651665889474</v>
+        <v>81.917511424093263</v>
       </c>
       <c r="G97" s="2">
-        <v>104.14265166588947</v>
+        <v>103.41751142409326</v>
       </c>
       <c r="H97" s="2">
-        <v>100.49765885758335</v>
+        <v>99.797898524250002</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -35459,13 +35483,13 @@
         <v>30</v>
       </c>
       <c r="F98" s="2">
-        <v>82.646641239082271</v>
+        <v>81.921420056328728</v>
       </c>
       <c r="G98" s="2">
-        <v>104.14664123908227</v>
+        <v>103.42142005632873</v>
       </c>
       <c r="H98" s="2">
-        <v>100.50150879571439</v>
+        <v>99.801670354357213</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -35485,13 +35509,13 @@
         <v>63</v>
       </c>
       <c r="F99" s="2">
-        <v>141.83407442657776</v>
+        <v>141.03158819810886</v>
       </c>
       <c r="G99" s="2">
-        <v>163.33407442657776</v>
+        <v>162.53158819810886</v>
       </c>
       <c r="H99" s="2">
-        <v>78.400355724757318</v>
+        <v>78.015162335092256</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -35511,13 +35535,13 @@
         <v>63</v>
       </c>
       <c r="F100" s="2">
-        <v>131.9972972734781</v>
+        <v>131.34951543576983</v>
       </c>
       <c r="G100" s="2">
-        <v>153.4972972734781</v>
+        <v>152.84951543576983</v>
       </c>
       <c r="H100" s="2">
-        <v>119.72789187331291</v>
+        <v>119.22262203990047</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -35537,13 +35561,13 @@
         <v>30</v>
       </c>
       <c r="F101" s="2">
-        <v>67.726202420776261</v>
+        <v>67.33920242077626</v>
       </c>
       <c r="G101" s="2">
-        <v>89.226202420776261</v>
+        <v>88.83920242077626</v>
       </c>
       <c r="H101" s="2">
-        <v>130.27025553433333</v>
+        <v>129.70523553433333</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -35563,13 +35587,13 @@
         <v>30</v>
       </c>
       <c r="F102" s="2">
-        <v>69.729729184476923</v>
+        <v>69.342699651220059</v>
       </c>
       <c r="G102" s="2">
-        <v>91.229729184476923</v>
+        <v>90.842699651220059</v>
       </c>
       <c r="H102" s="2">
-        <v>133.19540460933629</v>
+        <v>132.63034149078129</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -35589,13 +35613,13 @@
         <v>63</v>
       </c>
       <c r="F103" s="2">
-        <v>45.805675083822244</v>
+        <v>45.240127957765552</v>
       </c>
       <c r="G103" s="2">
-        <v>67.305675083822251</v>
+        <v>66.740127957765552</v>
       </c>
       <c r="H103" s="2">
-        <v>134.6113501676445</v>
+        <v>133.4802559155311</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -35615,13 +35639,13 @@
         <v>63</v>
       </c>
       <c r="F104" s="2">
-        <v>44.492379955182891</v>
+        <v>43.954817979202815</v>
       </c>
       <c r="G104" s="2">
-        <v>65.992379955182884</v>
+        <v>65.454817979202815</v>
       </c>
       <c r="H104" s="2">
-        <v>131.98475991036577</v>
+        <v>130.90963595840563</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -35641,13 +35665,13 @@
         <v>63</v>
       </c>
       <c r="F105" s="2">
-        <v>38.088336769751074</v>
+        <v>37.98157994687913</v>
       </c>
       <c r="G105" s="2">
-        <v>59.588336769751074</v>
+        <v>59.48157994687913</v>
       </c>
       <c r="H105" s="2">
-        <v>297.94168384875536</v>
+        <v>297.40789973439564</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -35667,13 +35691,13 @@
         <v>63</v>
       </c>
       <c r="F106" s="2">
-        <v>40.845277753227855</v>
+        <v>40.776268066213348</v>
       </c>
       <c r="G106" s="2">
-        <v>62.345277753227855</v>
+        <v>62.276268066213348</v>
       </c>
       <c r="H106" s="2">
-        <v>165.21498604605381</v>
+        <v>165.03211037546538</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -35693,13 +35717,13 @@
         <v>63</v>
       </c>
       <c r="F107" s="2">
-        <v>43.557449038834221</v>
+        <v>43.552019505577363</v>
       </c>
       <c r="G107" s="2">
-        <v>65.057449038834221</v>
+        <v>65.052019505577363</v>
       </c>
       <c r="H107" s="2">
-        <v>172.40223995291069</v>
+        <v>172.38785168978001</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -35719,13 +35743,13 @@
         <v>63</v>
       </c>
       <c r="F108" s="2">
-        <v>42.648944539284507</v>
+        <v>42.643544539284505</v>
       </c>
       <c r="G108" s="2">
-        <v>64.148944539284514</v>
+        <v>64.143544539284505</v>
       </c>
       <c r="H108" s="2">
-        <v>169.99470302910396</v>
+        <v>169.98039302910394</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -35745,13 +35769,13 @@
         <v>30</v>
       </c>
       <c r="F109" s="2">
-        <v>50.597764540893131</v>
+        <v>50.597675046175382</v>
       </c>
       <c r="G109" s="2">
-        <v>72.097764540893138</v>
+        <v>72.097675046175382</v>
       </c>
       <c r="H109" s="2">
-        <v>191.05907603336681</v>
+        <v>191.05883887236476</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -35771,13 +35795,13 @@
         <v>30</v>
       </c>
       <c r="F110" s="2">
-        <v>48.586513241800233</v>
+        <v>48.453313241800231</v>
       </c>
       <c r="G110" s="2">
-        <v>70.086513241800233</v>
+        <v>69.953313241800231</v>
       </c>
       <c r="H110" s="2">
-        <v>185.72926009077062</v>
+        <v>185.37628009077059</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -35797,13 +35821,13 @@
         <v>63</v>
       </c>
       <c r="F111" s="2">
-        <v>50.31434312283551</v>
+        <v>49.769938459948747</v>
       </c>
       <c r="G111" s="2">
-        <v>71.81434312283551</v>
+        <v>71.269938459948747</v>
       </c>
       <c r="H111" s="2">
-        <v>50.270040185984854</v>
+        <v>49.888956921964123</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -35823,13 +35847,13 @@
         <v>30</v>
       </c>
       <c r="F112" s="2">
-        <v>22.167489022835504</v>
+        <v>21.914983377091602</v>
       </c>
       <c r="G112" s="2">
-        <v>43.667489022835504</v>
+        <v>43.414983377091602</v>
       </c>
       <c r="H112" s="2">
-        <v>43.667489022835504</v>
+        <v>43.414983377091602</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -35849,13 +35873,13 @@
         <v>30</v>
       </c>
       <c r="F113" s="2">
-        <v>33.377714481168837</v>
+        <v>33.088713835424933</v>
       </c>
       <c r="G113" s="2">
-        <v>54.877714481168837</v>
+        <v>54.588713835424933</v>
       </c>
       <c r="H113" s="2">
-        <v>329.26628688701305</v>
+        <v>327.53228301254961</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -35875,13 +35899,13 @@
         <v>30</v>
       </c>
       <c r="F114" s="2">
-        <v>106.06031123986014</v>
+        <v>104.76014830961965</v>
       </c>
       <c r="G114" s="2">
-        <v>127.56031123986014</v>
+        <v>126.26014830961965</v>
       </c>
       <c r="H114" s="2">
-        <v>63.780155619930071</v>
+        <v>63.130074154809826</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -35901,13 +35925,13 @@
         <v>30</v>
       </c>
       <c r="F115" s="2">
-        <v>44.771110550000003</v>
+        <v>44.707696550000001</v>
       </c>
       <c r="G115" s="2">
-        <v>66.271110550000003</v>
+        <v>66.207696550000009</v>
       </c>
       <c r="H115" s="2">
-        <v>331.35555275000002</v>
+        <v>331.03848275000007</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -35927,13 +35951,13 @@
         <v>30</v>
       </c>
       <c r="F116" s="2">
-        <v>70.994972676573425</v>
+        <v>70.192590723079775</v>
       </c>
       <c r="G116" s="2">
-        <v>92.494972676573425</v>
+        <v>91.692590723079775</v>
       </c>
       <c r="H116" s="2">
-        <v>69.371229507430073</v>
+        <v>68.769443042309831</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -35953,13 +35977,13 @@
         <v>63</v>
       </c>
       <c r="F117" s="2">
-        <v>56.912835393333324</v>
+        <v>56.059408726666675</v>
       </c>
       <c r="G117" s="2">
-        <v>78.412835393333324</v>
+        <v>77.559408726666675</v>
       </c>
       <c r="H117" s="2">
-        <v>78.412835393333324</v>
+        <v>77.559408726666675</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -35979,13 +36003,13 @@
         <v>63</v>
       </c>
       <c r="F118" s="2">
-        <v>54.487540283333331</v>
+        <v>53.683113616666667</v>
       </c>
       <c r="G118" s="2">
-        <v>75.987540283333331</v>
+        <v>75.183113616666674</v>
       </c>
       <c r="H118" s="2">
-        <v>75.987540283333331</v>
+        <v>75.183113616666674</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -36005,13 +36029,13 @@
         <v>63</v>
       </c>
       <c r="F119" s="2">
-        <v>57.76790088015553</v>
+        <v>56.872119260410706</v>
       </c>
       <c r="G119" s="2">
-        <v>79.267900880155537</v>
+        <v>78.372119260410699</v>
       </c>
       <c r="H119" s="2">
-        <v>79.267900880155537</v>
+        <v>78.372119260410699</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -36031,13 +36055,13 @@
         <v>30</v>
       </c>
       <c r="F120" s="2">
-        <v>22.769640733333336</v>
+        <v>22.334214066666664</v>
       </c>
       <c r="G120" s="2">
-        <v>44.269640733333333</v>
+        <v>43.834214066666661</v>
       </c>
       <c r="H120" s="2">
-        <v>44.269640733333333</v>
+        <v>43.834214066666661</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -36057,13 +36081,13 @@
         <v>63</v>
       </c>
       <c r="F121" s="2">
-        <v>55.597151920633884</v>
+        <v>54.728472327918801</v>
       </c>
       <c r="G121" s="2">
-        <v>77.097151920633877</v>
+        <v>76.228472327918809</v>
       </c>
       <c r="H121" s="2">
-        <v>77.097151920633877</v>
+        <v>76.228472327918809</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -36083,13 +36107,13 @@
         <v>63</v>
       </c>
       <c r="F122" s="2">
-        <v>52.705787933333333</v>
+        <v>51.939861266666675</v>
       </c>
       <c r="G122" s="2">
-        <v>74.20578793333334</v>
+        <v>73.439861266666668</v>
       </c>
       <c r="H122" s="2">
-        <v>74.20578793333334</v>
+        <v>73.439861266666668</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -36109,13 +36133,13 @@
         <v>30</v>
       </c>
       <c r="F123" s="2">
-        <v>22.792706506168845</v>
+        <v>22.356794193758269</v>
       </c>
       <c r="G123" s="2">
-        <v>44.292706506168841</v>
+        <v>43.856794193758269</v>
       </c>
       <c r="H123" s="2">
-        <v>44.292706506168841</v>
+        <v>43.856794193758269</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -36135,13 +36159,13 @@
         <v>30</v>
       </c>
       <c r="F124" s="2">
-        <v>22.865635933333333</v>
+        <v>22.430209266666665</v>
       </c>
       <c r="G124" s="2">
-        <v>44.365635933333337</v>
+        <v>43.930209266666665</v>
       </c>
       <c r="H124" s="2">
-        <v>44.365635933333337</v>
+        <v>43.930209266666665</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -36161,13 +36185,13 @@
         <v>63</v>
       </c>
       <c r="F125" s="2">
-        <v>22.830906295007779</v>
+        <v>22.65830629500778</v>
       </c>
       <c r="G125" s="2">
-        <v>44.330906295007779</v>
+        <v>44.158306295007776</v>
       </c>
       <c r="H125" s="2">
-        <v>117.47690168177061</v>
+        <v>117.01951168177061</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -36187,13 +36211,13 @@
         <v>63</v>
       </c>
       <c r="F126" s="2">
-        <v>22.76029684284768</v>
+        <v>22.599156217427414</v>
       </c>
       <c r="G126" s="2">
-        <v>44.26029684284768</v>
+        <v>44.099156217427414</v>
       </c>
       <c r="H126" s="2">
-        <v>117.28978663354634</v>
+        <v>116.86276397618265</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -36213,13 +36237,13 @@
         <v>63</v>
       </c>
       <c r="F127" s="2">
-        <v>24.237143017271926</v>
+        <v>24.06134301727193</v>
       </c>
       <c r="G127" s="2">
-        <v>45.737143017271926</v>
+        <v>45.56134301727193</v>
       </c>
       <c r="H127" s="2">
-        <v>121.20342899577059</v>
+        <v>120.73755899577061</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -36265,13 +36289,13 @@
         <v>30</v>
       </c>
       <c r="F129" s="2">
-        <v>28.948767749999998</v>
+        <v>28.768573749999998</v>
       </c>
       <c r="G129" s="2">
-        <v>50.448767750000002</v>
+        <v>50.268573750000002</v>
       </c>
       <c r="H129" s="2">
-        <v>252.24383875000001</v>
+        <v>251.34286875000001</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -36291,13 +36315,13 @@
         <v>30</v>
       </c>
       <c r="F130" s="2">
-        <v>28.20662972121244</v>
+        <v>28.040880768134279</v>
       </c>
       <c r="G130" s="2">
-        <v>49.706629721212437</v>
+        <v>49.540880768134279</v>
       </c>
       <c r="H130" s="2">
-        <v>248.53314860606218</v>
+        <v>247.7044038406714</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -36317,13 +36341,13 @@
         <v>63</v>
       </c>
       <c r="F131" s="2">
-        <v>34.976173370246215</v>
+        <v>34.913494382241026</v>
       </c>
       <c r="G131" s="2">
-        <v>56.476173370246215</v>
+        <v>56.413494382241026</v>
       </c>
       <c r="H131" s="2">
-        <v>282.38086685123108</v>
+        <v>282.06747191120513</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -36343,13 +36367,13 @@
         <v>30</v>
       </c>
       <c r="F132" s="2">
-        <v>17.086802820246213</v>
+        <v>17.086717832241028</v>
       </c>
       <c r="G132" s="2">
-        <v>38.586802820246213</v>
+        <v>38.586717832241028</v>
       </c>
       <c r="H132" s="2">
-        <v>38.586802820246213</v>
+        <v>38.586717832241028</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -36421,13 +36445,13 @@
         <v>30</v>
       </c>
       <c r="F135" s="2">
-        <v>33.901868949999994</v>
+        <v>33.739874950000001</v>
       </c>
       <c r="G135" s="2">
-        <v>55.401868949999994</v>
+        <v>55.239874950000001</v>
       </c>
       <c r="H135" s="2">
-        <v>277.00934474999997</v>
+        <v>276.19937475</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -36447,13 +36471,13 @@
         <v>30</v>
       </c>
       <c r="F136" s="2">
-        <v>1513.5284689500002</v>
+        <v>1482.6797149499996</v>
       </c>
       <c r="G136" s="2">
-        <v>1535.0284689500002</v>
+        <v>1504.1797149499996</v>
       </c>
       <c r="H136" s="2">
-        <v>7675.142344750001</v>
+        <v>7520.8985747499983</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -36473,13 +36497,13 @@
         <v>30</v>
       </c>
       <c r="F137" s="2">
-        <v>114.04184104128458</v>
+        <v>113.76785394306457</v>
       </c>
       <c r="G137" s="2">
-        <v>135.54184104128458</v>
+        <v>135.26785394306455</v>
       </c>
       <c r="H137" s="2">
-        <v>54.216736416513839</v>
+        <v>54.107141577225825</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -36499,13 +36523,13 @@
         <v>30</v>
       </c>
       <c r="F138" s="2">
-        <v>127.77612267322904</v>
+        <v>127.17995501945346</v>
       </c>
       <c r="G138" s="2">
-        <v>149.27612267322905</v>
+        <v>148.67995501945347</v>
       </c>
       <c r="H138" s="2">
-        <v>44.782836801968713</v>
+        <v>44.603986505836041</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -36525,13 +36549,13 @@
         <v>63</v>
       </c>
       <c r="F139" s="2">
-        <v>125.0221542702497</v>
+        <v>124.51262388402222</v>
       </c>
       <c r="G139" s="2">
-        <v>146.5221542702497</v>
+        <v>146.01262388402222</v>
       </c>
       <c r="H139" s="2">
-        <v>36.630538567562425</v>
+        <v>36.503155971005555</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -36551,13 +36575,13 @@
         <v>30</v>
       </c>
       <c r="F140" s="2">
-        <v>107.83606281211793</v>
+        <v>107.69932404723123</v>
       </c>
       <c r="G140" s="2">
-        <v>129.33606281211792</v>
+        <v>129.19932404723124</v>
       </c>
       <c r="H140" s="2">
-        <v>129.33606281211792</v>
+        <v>129.19932404723124</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -36577,13 +36601,13 @@
         <v>30</v>
       </c>
       <c r="F141" s="2">
-        <v>7.7140000000000004</v>
+        <v>7.5515999999999996</v>
       </c>
       <c r="G141" s="2">
-        <v>29.213999999999999</v>
+        <v>29.051600000000001</v>
       </c>
       <c r="H141" s="2">
-        <v>116.85599999999999</v>
+        <v>116.2064</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -36603,13 +36627,13 @@
         <v>30</v>
       </c>
       <c r="F142" s="2">
-        <v>7.7140000000000004</v>
+        <v>7.5515999999999996</v>
       </c>
       <c r="G142" s="2">
-        <v>29.213999999999999</v>
+        <v>29.051600000000001</v>
       </c>
       <c r="H142" s="2">
-        <v>116.85599999999999</v>
+        <v>116.2064</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -36629,13 +36653,13 @@
         <v>30</v>
       </c>
       <c r="F143" s="2">
-        <v>7.7140000000000004</v>
+        <v>7.5515999999999996</v>
       </c>
       <c r="G143" s="2">
-        <v>29.213999999999999</v>
+        <v>29.051600000000001</v>
       </c>
       <c r="H143" s="2">
-        <v>116.85599999999999</v>
+        <v>116.2064</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -36655,13 +36679,13 @@
         <v>30</v>
       </c>
       <c r="F144" s="2">
-        <v>7.7140000000000004</v>
+        <v>7.5515999999999996</v>
       </c>
       <c r="G144" s="2">
-        <v>29.213999999999999</v>
+        <v>29.051600000000001</v>
       </c>
       <c r="H144" s="2">
-        <v>116.85599999999999</v>
+        <v>116.2064</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -36681,13 +36705,13 @@
         <v>30</v>
       </c>
       <c r="F145" s="2">
-        <v>11.571</v>
+        <v>11.327399999999999</v>
       </c>
       <c r="G145" s="2">
-        <v>33.070999999999998</v>
+        <v>32.827399999999997</v>
       </c>
       <c r="H145" s="2">
-        <v>24.803249999999998</v>
+        <v>24.620549999999998</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -36707,13 +36731,13 @@
         <v>30</v>
       </c>
       <c r="F146" s="2">
-        <v>36.883192865306007</v>
+        <v>36.06055862322939</v>
       </c>
       <c r="G146" s="2">
-        <v>58.383192865306007</v>
+        <v>57.56055862322939</v>
       </c>
       <c r="H146" s="2">
-        <v>58.383192865306007</v>
+        <v>57.56055862322939</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -36733,13 +36757,13 @@
         <v>30</v>
       </c>
       <c r="F147" s="2">
-        <v>28.903990426521968</v>
+        <v>28.834980739507465</v>
       </c>
       <c r="G147" s="2">
-        <v>50.403990426521972</v>
+        <v>50.334980739507465</v>
       </c>
       <c r="H147" s="2">
-        <v>50.403990426521972</v>
+        <v>50.334980739507465</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -36759,13 +36783,13 @@
         <v>30</v>
       </c>
       <c r="F148" s="2">
-        <v>57.358001100000003</v>
+        <v>56.950431100000003</v>
       </c>
       <c r="G148" s="2">
-        <v>78.858001099999996</v>
+        <v>78.450431100000003</v>
       </c>
       <c r="H148" s="2">
-        <v>78.858001099999996</v>
+        <v>78.450431100000003</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -36785,13 +36809,13 @@
         <v>30</v>
       </c>
       <c r="F149" s="2">
-        <v>42.061055916666668</v>
+        <v>41.55610191666667</v>
       </c>
       <c r="G149" s="2">
-        <v>63.561055916666668</v>
+        <v>63.05610191666667</v>
       </c>
       <c r="H149" s="2">
-        <v>31.780527958333334</v>
+        <v>31.528050958333335</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -36863,13 +36887,13 @@
         <v>30</v>
       </c>
       <c r="F152" s="2">
-        <v>110.96195205417126</v>
+        <v>108.76007248816563</v>
       </c>
       <c r="G152" s="2">
-        <v>132.46195205417126</v>
+        <v>130.26007248816563</v>
       </c>
       <c r="H152" s="2">
-        <v>572.23563287401987</v>
+        <v>562.72351314887555</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -36889,13 +36913,13 @@
         <v>30</v>
       </c>
       <c r="F153" s="2">
-        <v>112.15068797661239</v>
+        <v>109.99454197506292</v>
       </c>
       <c r="G153" s="2">
-        <v>133.6506879766124</v>
+        <v>131.49454197506293</v>
       </c>
       <c r="H153" s="2">
-        <v>443.72028408235315</v>
+        <v>436.56187935720891</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -36915,13 +36939,13 @@
         <v>30</v>
       </c>
       <c r="F154" s="2">
-        <v>109.96728118864348</v>
+        <v>107.94346870306539</v>
       </c>
       <c r="G154" s="2">
-        <v>131.46728118864348</v>
+        <v>129.44346870306538</v>
       </c>
       <c r="H154" s="2">
-        <v>499.57566851684521</v>
+        <v>491.88518107164839</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -36941,13 +36965,13 @@
         <v>30</v>
       </c>
       <c r="F155" s="2">
-        <v>27.107956383809519</v>
+        <v>26.814107007873019</v>
       </c>
       <c r="G155" s="2">
-        <v>48.607956383809523</v>
+        <v>48.314107007873019</v>
       </c>
       <c r="H155" s="2">
-        <v>170.12784734333331</v>
+        <v>169.09937452755557</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -36967,13 +36991,13 @@
         <v>30</v>
       </c>
       <c r="F156" s="2">
-        <v>37.420899096678625</v>
+        <v>37.295962534340454</v>
       </c>
       <c r="G156" s="2">
-        <v>58.920899096678625</v>
+        <v>58.795962534340454</v>
       </c>
       <c r="H156" s="2">
-        <v>468.42114781859505</v>
+        <v>467.42790214800658</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -36993,13 +37017,13 @@
         <v>30</v>
       </c>
       <c r="F157" s="2">
-        <v>93.108533845513421</v>
+        <v>91.143906247865274</v>
       </c>
       <c r="G157" s="2">
-        <v>114.60853384551342</v>
+        <v>112.64390624786527</v>
       </c>
       <c r="H157" s="2">
-        <v>458.43413538205368</v>
+        <v>450.5756249914611</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -37019,13 +37043,13 @@
         <v>30</v>
       </c>
       <c r="F158" s="2">
-        <v>113.3386573540554</v>
+        <v>111.62041513803702</v>
       </c>
       <c r="G158" s="2">
-        <v>134.83865735405539</v>
+        <v>133.120415138037</v>
       </c>
       <c r="H158" s="2">
-        <v>355.97405541470624</v>
+        <v>351.43789596441769</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -37045,13 +37069,13 @@
         <v>30</v>
       </c>
       <c r="F159" s="2">
-        <v>86.569322408333335</v>
+        <v>85.50383274166667</v>
       </c>
       <c r="G159" s="2">
-        <v>108.06932240833333</v>
+        <v>107.00383274166667</v>
       </c>
       <c r="H159" s="2">
-        <v>389.04956067000001</v>
+        <v>385.21379787000001</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -37071,13 +37095,13 @@
         <v>30</v>
       </c>
       <c r="F160" s="2">
-        <v>61.097489844967527</v>
+        <v>59.882945359092837</v>
       </c>
       <c r="G160" s="2">
-        <v>82.597489844967527</v>
+        <v>81.382945359092844</v>
       </c>
       <c r="H160" s="2">
-        <v>234.57687115970776</v>
+        <v>231.12756481982368</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -37175,13 +37199,13 @@
         <v>30</v>
       </c>
       <c r="F164" s="2">
-        <v>91.519334686444481</v>
+        <v>90.351862790840087</v>
       </c>
       <c r="G164" s="2">
-        <v>113.01933468644448</v>
+        <v>111.85186279084009</v>
       </c>
       <c r="H164" s="2">
-        <v>352.62032422170677</v>
+        <v>348.97781190742108</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -37201,13 +37225,13 @@
         <v>30</v>
       </c>
       <c r="F165" s="2">
-        <v>94.104998333333327</v>
+        <v>92.044381333333334</v>
       </c>
       <c r="G165" s="2">
-        <v>115.60499833333333</v>
+        <v>113.54438133333333</v>
       </c>
       <c r="H165" s="2">
-        <v>346.81499499999995</v>
+        <v>340.63314400000002</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -37227,13 +37251,13 @@
         <v>63</v>
       </c>
       <c r="F166" s="2">
-        <v>60.51524666666667</v>
+        <v>59.501294666666659</v>
       </c>
       <c r="G166" s="2">
-        <v>82.01524666666667</v>
+        <v>81.001294666666666</v>
       </c>
       <c r="H166" s="2">
-        <v>246.04574000000002</v>
+        <v>243.003884</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -37253,13 +37277,13 @@
         <v>63</v>
       </c>
       <c r="F167" s="2">
-        <v>21.105161166666665</v>
+        <v>20.790325388888888</v>
       </c>
       <c r="G167" s="2">
-        <v>42.605161166666662</v>
+        <v>42.290325388888888</v>
       </c>
       <c r="H167" s="2">
-        <v>42.605161166666662</v>
+        <v>42.290325388888888</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -37279,13 +37303,13 @@
         <v>63</v>
       </c>
       <c r="F168" s="2">
-        <v>22.990646426666661</v>
+        <v>22.636863540888886</v>
       </c>
       <c r="G168" s="2">
-        <v>44.490646426666657</v>
+        <v>44.136863540888882</v>
       </c>
       <c r="H168" s="2">
-        <v>44.490646426666657</v>
+        <v>44.136863540888882</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -37305,13 +37329,13 @@
         <v>63</v>
       </c>
       <c r="F169" s="2">
-        <v>17.230795106666665</v>
+        <v>16.992666242666665</v>
       </c>
       <c r="G169" s="2">
-        <v>38.730795106666662</v>
+        <v>38.492666242666665</v>
       </c>
       <c r="H169" s="2">
-        <v>96.826987766666662</v>
+        <v>96.231665606666667</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -37331,13 +37355,13 @@
         <v>63</v>
       </c>
       <c r="F170" s="2">
-        <v>18.738580366666664</v>
+        <v>18.468704394666666</v>
       </c>
       <c r="G170" s="2">
-        <v>40.238580366666667</v>
+        <v>39.968704394666666</v>
       </c>
       <c r="H170" s="2">
-        <v>100.59645091666667</v>
+        <v>99.921760986666669</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -37357,13 +37381,13 @@
         <v>30</v>
       </c>
       <c r="F171" s="2">
-        <v>77.038348571084001</v>
+        <v>76.326600394249141</v>
       </c>
       <c r="G171" s="2">
-        <v>98.538348571084001</v>
+        <v>97.826600394249141</v>
       </c>
       <c r="H171" s="2">
-        <v>73.903761428313004</v>
+        <v>73.369950295686863</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -37383,13 +37407,13 @@
         <v>30</v>
       </c>
       <c r="F172" s="2">
-        <v>48.949801722222219</v>
+        <v>47.948181722222216</v>
       </c>
       <c r="G172" s="2">
-        <v>70.449801722222219</v>
+        <v>69.448181722222216</v>
       </c>
       <c r="H172" s="2">
-        <v>211.34940516666666</v>
+        <v>208.34454516666665</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -37409,13 +37433,13 @@
         <v>30</v>
       </c>
       <c r="F173" s="2">
-        <v>53.139374066666676</v>
+        <v>52.125422066666665</v>
       </c>
       <c r="G173" s="2">
-        <v>74.639374066666676</v>
+        <v>73.625422066666658</v>
       </c>
       <c r="H173" s="2">
-        <v>223.91812220000003</v>
+        <v>220.87626619999998</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -37435,13 +37459,13 @@
         <v>30</v>
       </c>
       <c r="F174" s="2">
-        <v>48.466001722222217</v>
+        <v>47.476181722222215</v>
       </c>
       <c r="G174" s="2">
-        <v>69.966001722222217</v>
+        <v>68.976181722222208</v>
       </c>
       <c r="H174" s="2">
-        <v>209.89800516666665</v>
+        <v>206.92854516666662</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -37461,13 +37485,13 @@
         <v>30</v>
       </c>
       <c r="F175" s="2">
-        <v>98.544956722222224</v>
+        <v>96.384271722222223</v>
       </c>
       <c r="G175" s="2">
-        <v>120.04495672222222</v>
+        <v>117.88427172222222</v>
       </c>
       <c r="H175" s="2">
-        <v>360.1348701666667</v>
+        <v>353.65281516666664</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -37487,13 +37511,13 @@
         <v>30</v>
       </c>
       <c r="F176" s="2">
-        <v>98.30087147713229</v>
+        <v>96.14532511387101</v>
       </c>
       <c r="G176" s="2">
-        <v>119.80087147713229</v>
+        <v>117.64532511387101</v>
       </c>
       <c r="H176" s="2">
-        <v>359.40261443139684</v>
+        <v>352.93597534161302</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -37513,13 +37537,13 @@
         <v>30</v>
       </c>
       <c r="F177" s="2">
-        <v>98.957386722222239</v>
+        <v>96.893701722222232</v>
       </c>
       <c r="G177" s="2">
-        <v>120.45738672222224</v>
+        <v>118.39370172222223</v>
       </c>
       <c r="H177" s="2">
-        <v>361.37216016666673</v>
+        <v>355.18110516666673</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -37539,13 +37563,13 @@
         <v>30</v>
       </c>
       <c r="F178" s="2">
-        <v>106.93218837339016</v>
+        <v>104.59458409339015</v>
       </c>
       <c r="G178" s="2">
-        <v>128.43218837339015</v>
+        <v>126.09458409339015</v>
       </c>
       <c r="H178" s="2">
-        <v>96.32414128004261</v>
+        <v>94.570938070042615</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -37565,13 +37589,13 @@
         <v>30</v>
       </c>
       <c r="F179" s="2">
-        <v>107.08148243991398</v>
+        <v>105.55720358147134</v>
       </c>
       <c r="G179" s="2">
-        <v>128.581482439914</v>
+        <v>127.05720358147134</v>
       </c>
       <c r="H179" s="2">
-        <v>257.162964879828</v>
+        <v>254.11440716294268</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -37591,13 +37615,13 @@
         <v>30</v>
       </c>
       <c r="F180" s="2">
-        <v>112.73142240663205</v>
+        <v>111.2133995488901</v>
       </c>
       <c r="G180" s="2">
-        <v>134.23142240663205</v>
+        <v>132.7133995488901</v>
       </c>
       <c r="H180" s="2">
-        <v>268.4628448132641</v>
+        <v>265.42679909778019</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -37617,13 +37641,13 @@
         <v>63</v>
       </c>
       <c r="F181" s="2">
-        <v>111.28919957880289</v>
+        <v>109.27541162036025</v>
       </c>
       <c r="G181" s="2">
-        <v>132.78919957880288</v>
+        <v>130.77541162036025</v>
       </c>
       <c r="H181" s="2">
-        <v>663.94599789401445</v>
+        <v>653.87705810180125</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -37643,13 +37667,13 @@
         <v>30</v>
       </c>
       <c r="F182" s="2">
-        <v>52.789680305977782</v>
+        <v>51.520947624857783</v>
       </c>
       <c r="G182" s="2">
-        <v>74.289680305977782</v>
+        <v>73.020947624857783</v>
       </c>
       <c r="H182" s="2">
-        <v>52.002776214184443</v>
+        <v>51.114663337400444</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -37669,13 +37693,13 @@
         <v>30</v>
       </c>
       <c r="F183" s="2">
-        <v>69.281649096578988</v>
+        <v>67.913617826130917</v>
       </c>
       <c r="G183" s="2">
-        <v>90.781649096578988</v>
+        <v>89.413617826130917</v>
       </c>
       <c r="H183" s="2">
-        <v>181.56329819315798</v>
+        <v>178.82723565226183</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -37695,13 +37719,13 @@
         <v>30</v>
       </c>
       <c r="F184" s="2">
-        <v>96.397324523341595</v>
+        <v>95.576592756668461</v>
       </c>
       <c r="G184" s="2">
-        <v>117.8973245233416</v>
+        <v>117.07659275666846</v>
       </c>
       <c r="H184" s="2">
-        <v>58.948662261670798</v>
+        <v>58.53829637833423</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -37721,13 +37745,13 @@
         <v>30</v>
       </c>
       <c r="F185" s="2">
-        <v>98.960207625748666</v>
+        <v>98.235033605130099</v>
       </c>
       <c r="G185" s="2">
-        <v>120.46020762574867</v>
+        <v>119.7350336051301</v>
       </c>
       <c r="H185" s="2">
-        <v>60.230103812874333</v>
+        <v>59.867516802565049</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -37747,13 +37771,13 @@
         <v>30</v>
       </c>
       <c r="F186" s="2">
-        <v>97.095065712166416</v>
+        <v>96.244208868675912</v>
       </c>
       <c r="G186" s="2">
-        <v>118.59506571216642</v>
+        <v>117.74420886867591</v>
       </c>
       <c r="H186" s="2">
-        <v>59.297532856083208</v>
+        <v>58.872104434337956</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -37773,13 +37797,13 @@
         <v>30</v>
       </c>
       <c r="F187" s="2">
-        <v>100.95573478944932</v>
+        <v>100.23053123557392</v>
       </c>
       <c r="G187" s="2">
-        <v>122.45573478944932</v>
+        <v>121.73053123557392</v>
       </c>
       <c r="H187" s="2">
-        <v>61.227867394724662</v>
+        <v>60.86526561778696</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -37799,13 +37823,13 @@
         <v>30</v>
       </c>
       <c r="F188" s="2">
-        <v>89.683987833341604</v>
+        <v>88.90992275666845</v>
       </c>
       <c r="G188" s="2">
-        <v>111.1839878333416</v>
+        <v>110.40992275666845</v>
       </c>
       <c r="H188" s="2">
-        <v>83.38799087500621</v>
+        <v>82.807442067501341</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -37825,13 +37849,13 @@
         <v>30</v>
       </c>
       <c r="F189" s="2">
-        <v>92.246870935748646</v>
+        <v>91.568363605130102</v>
       </c>
       <c r="G189" s="2">
-        <v>113.74687093574865</v>
+        <v>113.0683636051301</v>
       </c>
       <c r="H189" s="2">
-        <v>85.310153201811488</v>
+        <v>84.801272703847573</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -37851,13 +37875,13 @@
         <v>30</v>
       </c>
       <c r="F190" s="2">
-        <v>94.242398099449318</v>
+        <v>93.56386123557391</v>
       </c>
       <c r="G190" s="2">
-        <v>115.74239809944932</v>
+        <v>115.06386123557391</v>
       </c>
       <c r="H190" s="2">
-        <v>86.806798574586992</v>
+        <v>86.29789592668044</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -37877,13 +37901,13 @@
         <v>30</v>
       </c>
       <c r="F191" s="2">
-        <v>21.269238939394846</v>
+        <v>21.108098313974583</v>
       </c>
       <c r="G191" s="2">
-        <v>42.769238939394846</v>
+        <v>42.60809831397458</v>
       </c>
       <c r="H191" s="2">
-        <v>128.30771681818453</v>
+        <v>127.82429494192374</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -37903,13 +37927,13 @@
         <v>30</v>
       </c>
       <c r="F192" s="2">
-        <v>55.597151920633884</v>
+        <v>54.728472327918801</v>
       </c>
       <c r="G192" s="2">
-        <v>77.097151920633877</v>
+        <v>76.228472327918809</v>
       </c>
       <c r="H192" s="2">
-        <v>77.097151920633877</v>
+        <v>76.228472327918809</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -37929,13 +37953,13 @@
         <v>30</v>
       </c>
       <c r="F193" s="2">
-        <v>52.705787933333333</v>
+        <v>51.939861266666675</v>
       </c>
       <c r="G193" s="2">
-        <v>74.20578793333334</v>
+        <v>73.439861266666668</v>
       </c>
       <c r="H193" s="2">
-        <v>74.20578793333334</v>
+        <v>73.439861266666668</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -37955,13 +37979,13 @@
         <v>30</v>
       </c>
       <c r="F194" s="2">
-        <v>22.792706506168845</v>
+        <v>22.356794193758269</v>
       </c>
       <c r="G194" s="2">
-        <v>44.292706506168841</v>
+        <v>43.856794193758269</v>
       </c>
       <c r="H194" s="2">
-        <v>44.292706506168841</v>
+        <v>43.856794193758269</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -37981,13 +38005,13 @@
         <v>30</v>
       </c>
       <c r="F195" s="2">
-        <v>57.76790088015553</v>
+        <v>56.872119260410706</v>
       </c>
       <c r="G195" s="2">
-        <v>79.267900880155537</v>
+        <v>78.372119260410699</v>
       </c>
       <c r="H195" s="2">
-        <v>79.267900880155537</v>
+        <v>78.372119260410699</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -38007,13 +38031,13 @@
         <v>30</v>
       </c>
       <c r="F196" s="2">
-        <v>28.20662972121244</v>
+        <v>28.040880768134279</v>
       </c>
       <c r="G196" s="2">
-        <v>49.706629721212437</v>
+        <v>49.540880768134279</v>
       </c>
       <c r="H196" s="2">
-        <v>248.53314860606218</v>
+        <v>247.7044038406714</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -38033,13 +38057,13 @@
         <v>30</v>
       </c>
       <c r="F197" s="2">
-        <v>22.661550411932303</v>
+        <v>22.485750411932305</v>
       </c>
       <c r="G197" s="2">
-        <v>44.161550411932303</v>
+        <v>43.985750411932301</v>
       </c>
       <c r="H197" s="2">
-        <v>132.48465123579692</v>
+        <v>131.95725123579689</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -38059,13 +38083,13 @@
         <v>30</v>
       </c>
       <c r="F198" s="2">
-        <v>101.34350837339015</v>
+        <v>99.123934093390162</v>
       </c>
       <c r="G198" s="2">
-        <v>122.84350837339015</v>
+        <v>120.62393409339016</v>
       </c>
       <c r="H198" s="2">
-        <v>92.132631280042617</v>
+        <v>90.467950570042618</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -38085,13 +38109,13 @@
         <v>30</v>
       </c>
       <c r="F199" s="2">
-        <v>102.2057952606653</v>
+        <v>99.968067572512126</v>
       </c>
       <c r="G199" s="2">
-        <v>123.7057952606653</v>
+        <v>121.46806757251213</v>
       </c>
       <c r="H199" s="2">
-        <v>92.779346445498973</v>
+        <v>91.101050679384088</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -38111,13 +38135,13 @@
         <v>30</v>
       </c>
       <c r="F200" s="2">
-        <v>98.960207625748666</v>
+        <v>98.235033605130099</v>
       </c>
       <c r="G200" s="2">
-        <v>120.46020762574867</v>
+        <v>119.7350336051301</v>
       </c>
       <c r="H200" s="2">
-        <v>60.230103812874333</v>
+        <v>59.867516802565049</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -38137,13 +38161,13 @@
         <v>30</v>
       </c>
       <c r="F201" s="2">
-        <v>96.397324523341595</v>
+        <v>95.576592756668461</v>
       </c>
       <c r="G201" s="2">
-        <v>117.8973245233416</v>
+        <v>117.07659275666846</v>
       </c>
       <c r="H201" s="2">
-        <v>58.948662261670798</v>
+        <v>58.53829637833423</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -38163,13 +38187,13 @@
         <v>30</v>
       </c>
       <c r="F202" s="2">
-        <v>133.7274061</v>
+        <v>131.66848110000001</v>
       </c>
       <c r="G202" s="2">
-        <v>155.2274061</v>
+        <v>153.16848110000001</v>
       </c>
       <c r="H202" s="2">
-        <v>155.2274061</v>
+        <v>153.16848110000001</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -38189,13 +38213,13 @@
         <v>30</v>
       </c>
       <c r="F203" s="2">
-        <v>12.358799999999999</v>
+        <v>12.3444</v>
       </c>
       <c r="G203" s="2">
-        <v>33.858800000000002</v>
+        <v>33.8444</v>
       </c>
       <c r="H203" s="2">
-        <v>33.858800000000002</v>
+        <v>33.8444</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -38215,13 +38239,13 @@
         <v>30</v>
       </c>
       <c r="F204" s="2">
-        <v>76.14093033245031</v>
+        <v>74.970198828928233</v>
       </c>
       <c r="G204" s="2">
-        <v>97.64093033245031</v>
+        <v>96.470198828928233</v>
       </c>
       <c r="H204" s="2">
-        <v>32.221507009708603</v>
+        <v>31.835165613546319</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -38241,13 +38265,13 @@
         <v>30</v>
       </c>
       <c r="F205" s="2">
-        <v>71.271146426338291</v>
+        <v>70.098841952418553</v>
       </c>
       <c r="G205" s="2">
-        <v>92.771146426338291</v>
+        <v>91.598841952418553</v>
       </c>
       <c r="H205" s="2">
-        <v>30.614478320691639</v>
+        <v>30.227617844298123</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -38267,13 +38291,13 @@
         <v>30</v>
       </c>
       <c r="F206" s="2">
-        <v>80.727048096895658</v>
+        <v>79.572884640437891</v>
       </c>
       <c r="G206" s="2">
-        <v>102.22704809689566</v>
+        <v>101.07288464043789</v>
       </c>
       <c r="H206" s="2">
-        <v>33.73492587197557</v>
+        <v>33.354051931344507</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -38397,13 +38421,13 @@
         <v>63</v>
       </c>
       <c r="F211" s="2">
-        <v>139.71557966622478</v>
+        <v>136.89004966622477</v>
       </c>
       <c r="G211" s="2">
-        <v>161.21557966622478</v>
+        <v>158.39004966622477</v>
       </c>
       <c r="H211" s="2">
-        <v>1094.492570354</v>
+        <v>1075.3100471839998</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -38423,13 +38447,13 @@
         <v>63</v>
       </c>
       <c r="F212" s="2">
-        <v>144.15267983821758</v>
+        <v>141.03374059801612</v>
       </c>
       <c r="G212" s="2">
-        <v>165.65267983821758</v>
+        <v>162.53374059801612</v>
       </c>
       <c r="H212" s="2">
-        <v>756.5357888211397</v>
+        <v>742.29159331113965</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -38449,13 +38473,13 @@
         <v>63</v>
       </c>
       <c r="F213" s="2">
-        <v>144.61983450657107</v>
+        <v>141.50495265471923</v>
       </c>
       <c r="G213" s="2">
-        <v>166.11983450657107</v>
+        <v>163.00495265471923</v>
       </c>
       <c r="H213" s="2">
-        <v>574.11014805470961</v>
+        <v>563.34511637470962</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -38475,13 +38499,13 @@
         <v>63</v>
       </c>
       <c r="F214" s="2">
-        <v>89.247060934343395</v>
+        <v>87.631210842249018</v>
       </c>
       <c r="G214" s="2">
-        <v>110.74706093434339</v>
+        <v>109.13121084224902</v>
       </c>
       <c r="H214" s="2">
-        <v>101.88729605959593</v>
+        <v>100.40071397486911</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -38501,13 +38525,13 @@
         <v>63</v>
       </c>
       <c r="F215" s="2">
-        <v>95.517484395704045</v>
+        <v>93.769768545686276</v>
       </c>
       <c r="G215" s="2">
-        <v>117.01748439570405</v>
+        <v>115.26976854568628</v>
       </c>
       <c r="H215" s="2">
-        <v>107.65608564404772</v>
+        <v>106.04818706203137</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -38527,13 +38551,13 @@
         <v>63</v>
       </c>
       <c r="F216" s="2">
-        <v>73.26277912596278</v>
+        <v>71.82047207434924</v>
       </c>
       <c r="G216" s="2">
-        <v>94.76277912596278</v>
+        <v>93.32047207434924</v>
       </c>
       <c r="H216" s="2">
-        <v>174.36351359177152</v>
+        <v>171.70966861680262</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -38553,13 +38577,13 @@
         <v>63</v>
       </c>
       <c r="F217" s="2">
-        <v>79.476409109062573</v>
+        <v>77.903431951699545</v>
       </c>
       <c r="G217" s="2">
-        <v>100.97640910906257</v>
+        <v>99.403431951699545</v>
       </c>
       <c r="H217" s="2">
-        <v>185.79659276067514</v>
+        <v>182.90231479112717</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -38579,13 +38603,13 @@
         <v>63</v>
       </c>
       <c r="F218" s="2">
-        <v>51.45953783325654</v>
+        <v>50.224625194708288</v>
       </c>
       <c r="G218" s="2">
-        <v>72.959537833256547</v>
+        <v>71.724625194708295</v>
       </c>
       <c r="H218" s="2">
-        <v>43.775722699953924</v>
+        <v>43.034775116824974</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -38605,13 +38629,13 @@
         <v>63</v>
       </c>
       <c r="F219" s="2">
-        <v>77.187054321575161</v>
+        <v>75.662130956369779</v>
       </c>
       <c r="G219" s="2">
-        <v>98.687054321575161</v>
+        <v>97.162130956369779</v>
       </c>
       <c r="H219" s="2">
-        <v>181.5841799516983</v>
+        <v>178.77832095972039</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
@@ -38631,13 +38655,13 @@
         <v>63</v>
       </c>
       <c r="F220" s="2">
-        <v>74.282915631688724</v>
+        <v>72.819132007323049</v>
       </c>
       <c r="G220" s="2">
-        <v>95.782915631688724</v>
+        <v>94.319132007323049</v>
       </c>
       <c r="H220" s="2">
-        <v>176.24056476230726</v>
+        <v>173.54720289347441</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -38657,13 +38681,13 @@
         <v>63</v>
       </c>
       <c r="F221" s="2">
-        <v>93.71687630816426</v>
+        <v>92.006924846094719</v>
       </c>
       <c r="G221" s="2">
-        <v>115.21687630816426</v>
+        <v>113.50692484609472</v>
       </c>
       <c r="H221" s="2">
-        <v>105.99952620351112</v>
+        <v>104.42637085840714</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -38683,13 +38707,13 @@
         <v>63</v>
       </c>
       <c r="F222" s="2">
-        <v>90.866526848135237</v>
+        <v>89.216582722066306</v>
       </c>
       <c r="G222" s="2">
-        <v>112.36652684813524</v>
+        <v>110.71658272206631</v>
       </c>
       <c r="H222" s="2">
-        <v>103.37720470028442</v>
+        <v>101.85925610430101</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -38709,13 +38733,13 @@
         <v>63</v>
       </c>
       <c r="F223" s="2">
-        <v>29.251964990000001</v>
+        <v>29.074970990000001</v>
       </c>
       <c r="G223" s="2">
-        <v>50.751964990000005</v>
+        <v>50.574970989999997</v>
       </c>
       <c r="H223" s="2">
-        <v>253.75982495000002</v>
+        <v>252.87485494999999</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -38761,13 +38785,13 @@
         <v>30</v>
       </c>
       <c r="F225" s="2">
-        <v>108.41245118991399</v>
+        <v>106.85680538702691</v>
       </c>
       <c r="G225" s="2">
-        <v>129.91245118991401</v>
+        <v>128.3568053870269</v>
       </c>
       <c r="H225" s="2">
-        <v>233.84241214184522</v>
+        <v>231.04224969664841</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -38813,13 +38837,13 @@
         <v>30</v>
       </c>
       <c r="F227" s="2">
-        <v>111.40979487069635</v>
+        <v>109.69061371493372</v>
       </c>
       <c r="G227" s="2">
-        <v>132.90979487069635</v>
+        <v>131.1906137149337</v>
       </c>
       <c r="H227" s="2">
-        <v>350.88185845863836</v>
+        <v>346.34322020742502</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -38839,13 +38863,13 @@
         <v>30</v>
       </c>
       <c r="F228" s="2">
-        <v>114.31866692282301</v>
+        <v>112.12635847751694</v>
       </c>
       <c r="G228" s="2">
-        <v>135.81866692282301</v>
+        <v>133.62635847751693</v>
       </c>
       <c r="H228" s="2">
-        <v>472.64896089142411</v>
+        <v>465.01972750175889</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -38865,13 +38889,13 @@
         <v>63</v>
       </c>
       <c r="F229" s="2">
-        <v>135.50074419398237</v>
+        <v>132.79989435580708</v>
       </c>
       <c r="G229" s="2">
-        <v>157.00074419398237</v>
+        <v>154.29989435580708</v>
       </c>
       <c r="H229" s="2">
-        <v>936.82344060549292</v>
+        <v>920.70746962110093</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
@@ -38891,13 +38915,13 @@
         <v>30</v>
       </c>
       <c r="F230" s="2">
-        <v>132.22004569949672</v>
+        <v>129.63914879592048</v>
       </c>
       <c r="G230" s="2">
-        <v>153.72004569949672</v>
+        <v>151.13914879592048</v>
       </c>
       <c r="H230" s="2">
-        <v>807.95256019655483</v>
+        <v>794.38736607135809</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
@@ -38917,13 +38941,13 @@
         <v>30</v>
       </c>
       <c r="F231" s="2">
-        <v>137.24347146738452</v>
+        <v>134.43860052545412</v>
       </c>
       <c r="G231" s="2">
-        <v>158.74347146738452</v>
+        <v>155.93860052545412</v>
       </c>
       <c r="H231" s="2">
-        <v>934.52281652849274</v>
+        <v>918.01054129334852</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
@@ -38969,13 +38993,13 @@
         <v>30</v>
       </c>
       <c r="F233" s="2">
-        <v>111.40979487069635</v>
+        <v>109.69061371493372</v>
       </c>
       <c r="G233" s="2">
-        <v>132.90979487069635</v>
+        <v>131.1906137149337</v>
       </c>
       <c r="H233" s="2">
-        <v>350.88185845863836</v>
+        <v>346.34322020742502</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
@@ -38995,13 +39019,13 @@
         <v>30</v>
       </c>
       <c r="F234" s="2">
-        <v>111.40979487069635</v>
+        <v>109.69061371493372</v>
       </c>
       <c r="G234" s="2">
-        <v>132.90979487069635</v>
+        <v>131.1906137149337</v>
       </c>
       <c r="H234" s="2">
-        <v>350.88185845863836</v>
+        <v>346.34322020742502</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
@@ -39021,13 +39045,13 @@
         <v>30</v>
       </c>
       <c r="F235" s="2">
-        <v>111.40979487069635</v>
+        <v>109.69061371493372</v>
       </c>
       <c r="G235" s="2">
-        <v>132.90979487069635</v>
+        <v>131.1906137149337</v>
       </c>
       <c r="H235" s="2">
-        <v>350.88185845863836</v>
+        <v>346.34322020742502</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
@@ -39047,13 +39071,13 @@
         <v>30</v>
       </c>
       <c r="F236" s="2">
-        <v>107.2768941316809</v>
+        <v>105.93991164997242</v>
       </c>
       <c r="G236" s="2">
-        <v>128.7768941316809</v>
+        <v>127.43991164997242</v>
       </c>
       <c r="H236" s="2">
-        <v>180.28765178435324</v>
+        <v>178.41587630996136</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
@@ -39099,13 +39123,13 @@
         <v>30</v>
       </c>
       <c r="F238" s="2">
-        <v>25.893080366666663</v>
+        <v>25.623204394666676</v>
       </c>
       <c r="G238" s="2">
-        <v>47.393080366666666</v>
+        <v>47.123204394666672</v>
       </c>
       <c r="H238" s="2">
-        <v>236.96540183333332</v>
+        <v>235.61602197333337</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
@@ -39125,13 +39149,13 @@
         <v>30</v>
       </c>
       <c r="F239" s="2">
-        <v>56.254993656983601</v>
+        <v>55.393940527292742</v>
       </c>
       <c r="G239" s="2">
-        <v>77.754993656983601</v>
+        <v>76.893940527292742</v>
       </c>
       <c r="H239" s="2">
-        <v>155.5099873139672</v>
+        <v>153.78788105458548</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
@@ -39151,13 +39175,13 @@
         <v>30</v>
       </c>
       <c r="F240" s="2">
-        <v>93.215363922777783</v>
+        <v>91.300780033888898</v>
       </c>
       <c r="G240" s="2">
-        <v>114.71536392277778</v>
+        <v>112.8007800338889</v>
       </c>
       <c r="H240" s="2">
-        <v>344.14609176833335</v>
+        <v>338.40234010166671</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
@@ -39177,13 +39201,13 @@
         <v>30</v>
       </c>
       <c r="F241" s="2">
-        <v>104.05091830363709</v>
+        <v>102.43030763186758</v>
       </c>
       <c r="G241" s="2">
-        <v>125.55091830363709</v>
+        <v>123.93030763186758</v>
       </c>
       <c r="H241" s="2">
-        <v>341.49849778589294</v>
+        <v>337.09043675867986</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
@@ -39203,13 +39227,13 @@
         <v>30</v>
       </c>
       <c r="F242" s="2">
-        <v>105.43199301284383</v>
+        <v>103.87495977976643</v>
       </c>
       <c r="G242" s="2">
-        <v>126.93199301284383</v>
+        <v>125.37495977976643</v>
       </c>
       <c r="H242" s="2">
-        <v>456.95517484623781</v>
+        <v>451.34985520715912</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
@@ -39229,13 +39253,13 @@
         <v>30</v>
       </c>
       <c r="F243" s="2">
-        <v>91.866368304438268</v>
+        <v>89.851196895870117</v>
       </c>
       <c r="G243" s="2">
-        <v>113.36636830443827</v>
+        <v>111.35119689587012</v>
       </c>
       <c r="H243" s="2">
-        <v>566.83184152219133</v>
+        <v>556.75598447935056</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
@@ -39255,13 +39279,13 @@
         <v>30</v>
       </c>
       <c r="F244" s="2">
-        <v>109.35229527260665</v>
+        <v>107.25975309652398</v>
       </c>
       <c r="G244" s="2">
-        <v>130.85229527260665</v>
+        <v>128.75975309652398</v>
       </c>
       <c r="H244" s="2">
-        <v>628.09101730851194</v>
+        <v>618.04681486331503</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
@@ -39281,13 +39305,13 @@
         <v>30</v>
       </c>
       <c r="F245" s="2">
-        <v>36.714335417950451</v>
+        <v>36.627990670591579</v>
       </c>
       <c r="G245" s="2">
-        <v>58.214335417950451</v>
+        <v>58.127990670591579</v>
       </c>
       <c r="H245" s="2">
-        <v>308.53597771513739</v>
+        <v>308.07835055413534</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
@@ -39307,13 +39331,13 @@
         <v>30</v>
       </c>
       <c r="F246" s="2">
-        <v>97.747607250303346</v>
+        <v>95.652385508014149</v>
       </c>
       <c r="G246" s="2">
-        <v>119.24760725030335</v>
+        <v>117.15238550801415</v>
       </c>
       <c r="H246" s="2">
-        <v>696.40602634177151</v>
+        <v>684.16993136680264</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
@@ -39333,13 +39357,13 @@
         <v>30</v>
       </c>
       <c r="F247" s="2">
-        <v>79.876161985922664</v>
+        <v>78.758355732905102</v>
       </c>
       <c r="G247" s="2">
-        <v>101.37616198592266</v>
+        <v>100.2583557329051</v>
       </c>
       <c r="H247" s="2">
-        <v>235.19269580734061</v>
+        <v>232.59938530033986</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
@@ -39359,13 +39383,13 @@
         <v>30</v>
       </c>
       <c r="F248" s="2">
-        <v>63.881323842592593</v>
+        <v>62.644653858148153</v>
       </c>
       <c r="G248" s="2">
-        <v>85.381323842592593</v>
+        <v>84.14465385814816</v>
       </c>
       <c r="H248" s="2">
-        <v>384.21595729166665</v>
+        <v>378.65094236166669</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
@@ -39385,13 +39409,13 @@
         <v>30</v>
       </c>
       <c r="F249" s="2">
-        <v>103.23658550573546</v>
+        <v>101.179354033952</v>
       </c>
       <c r="G249" s="2">
-        <v>124.73658550573546</v>
+        <v>122.679354033952</v>
       </c>
       <c r="H249" s="2">
-        <v>619.31714703597652</v>
+        <v>609.10299277857166</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
@@ -39411,13 +39435,13 @@
         <v>30</v>
       </c>
       <c r="F250" s="2">
-        <v>75.507832948440679</v>
+        <v>74.512632593899582</v>
       </c>
       <c r="G250" s="2">
-        <v>97.007832948440679</v>
+        <v>96.012632593899582</v>
       </c>
       <c r="H250" s="2">
-        <v>271.62193225563391</v>
+        <v>268.83537126291878</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
@@ -39437,13 +39461,13 @@
         <v>30</v>
       </c>
       <c r="F251" s="2">
-        <v>69.977053854947542</v>
+        <v>68.673900958122161</v>
       </c>
       <c r="G251" s="2">
-        <v>91.477053854947542</v>
+        <v>90.173900958122161</v>
       </c>
       <c r="H251" s="2">
-        <v>395.1808726533734</v>
+        <v>389.55125213908775</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
@@ -39463,13 +39487,13 @@
         <v>30</v>
       </c>
       <c r="F252" s="2">
-        <v>50.161247483333341</v>
+        <v>49.104491138888889</v>
       </c>
       <c r="G252" s="2">
-        <v>71.661247483333341</v>
+        <v>70.604491138888889</v>
       </c>
       <c r="H252" s="2">
-        <v>286.64498993333336</v>
+        <v>282.41796455555556</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
@@ -39489,13 +39513,13 @@
         <v>30</v>
       </c>
       <c r="F253" s="2">
-        <v>108.86450092728542</v>
+        <v>107.23926984675147</v>
       </c>
       <c r="G253" s="2">
-        <v>130.36450092728541</v>
+        <v>128.73926984675148</v>
       </c>
       <c r="H253" s="2">
-        <v>406.73724289313049</v>
+        <v>401.66652192186461</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
@@ -39515,13 +39539,13 @@
         <v>30</v>
       </c>
       <c r="F254" s="2">
-        <v>110.49661533628151</v>
+        <v>108.87217874322349</v>
       </c>
       <c r="G254" s="2">
-        <v>131.99661533628151</v>
+        <v>130.37217874322349</v>
       </c>
       <c r="H254" s="2">
-        <v>411.82943984919831</v>
+        <v>406.76119767885729</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
@@ -39541,13 +39565,13 @@
         <v>30</v>
       </c>
       <c r="F255" s="2">
-        <v>106.97504749213667</v>
+        <v>104.83928763112253</v>
       </c>
       <c r="G255" s="2">
-        <v>128.47504749213667</v>
+        <v>126.33928763112253</v>
       </c>
       <c r="H255" s="2">
-        <v>745.15527545439261</v>
+        <v>732.76786826051068</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
@@ -39567,13 +39591,13 @@
         <v>63</v>
       </c>
       <c r="F256" s="2">
-        <v>52.839335786862236</v>
+        <v>51.832119016439563</v>
       </c>
       <c r="G256" s="2">
-        <v>74.339335786862236</v>
+        <v>73.332119016439563</v>
       </c>
       <c r="H256" s="2">
-        <v>371.69667893431119</v>
+        <v>366.6605950821978</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
@@ -39593,13 +39617,13 @@
         <v>30</v>
       </c>
       <c r="F257" s="2">
-        <v>120.26900932412669</v>
+        <v>118.94836667719493</v>
       </c>
       <c r="G257" s="2">
-        <v>141.76900932412667</v>
+        <v>140.44836667719494</v>
       </c>
       <c r="H257" s="2">
-        <v>297.71491958066605</v>
+        <v>294.94157002210937</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
@@ -39619,13 +39643,13 @@
         <v>30</v>
       </c>
       <c r="F258" s="2">
-        <v>106.37306233529033</v>
+        <v>104.14764330035322</v>
       </c>
       <c r="G258" s="2">
-        <v>127.87306233529033</v>
+        <v>125.64764330035322</v>
       </c>
       <c r="H258" s="2">
-        <v>373.38934201904777</v>
+        <v>366.89111843703142</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
@@ -39645,13 +39669,13 @@
         <v>30</v>
       </c>
       <c r="F259" s="2">
-        <v>49.069500696092796</v>
+        <v>48.402909414483304</v>
       </c>
       <c r="G259" s="2">
-        <v>70.569500696092803</v>
+        <v>69.902909414483304</v>
       </c>
       <c r="H259" s="2">
-        <v>211.70850208827841</v>
+        <v>209.70872824344991</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
@@ -39671,13 +39695,13 @@
         <v>30</v>
       </c>
       <c r="F260" s="2">
-        <v>117.84415363076104</v>
+        <v>116.52233060243648</v>
       </c>
       <c r="G260" s="2">
-        <v>139.34415363076104</v>
+        <v>138.02233060243648</v>
       </c>
       <c r="H260" s="2">
-        <v>292.62272262459823</v>
+        <v>289.84689426511665</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
@@ -39697,13 +39721,13 @@
         <v>30</v>
       </c>
       <c r="F261" s="2">
-        <v>66.664727124804571</v>
+        <v>65.804568942154262</v>
       </c>
       <c r="G261" s="2">
-        <v>88.164727124804571</v>
+        <v>87.304568942154262</v>
       </c>
       <c r="H261" s="2">
-        <v>292.70689405435121</v>
+        <v>289.85116888795216</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
@@ -39723,13 +39747,13 @@
         <v>30</v>
       </c>
       <c r="F262" s="2">
-        <v>117.15508929795429</v>
+        <v>115.21422784708651</v>
       </c>
       <c r="G262" s="2">
-        <v>138.65508929795431</v>
+        <v>136.71422784708651</v>
       </c>
       <c r="H262" s="2">
-        <v>385.46114824831301</v>
+        <v>380.06555341490053</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
@@ -39749,13 +39773,13 @@
         <v>30</v>
       </c>
       <c r="F263" s="2">
-        <v>118.10843693113478</v>
+        <v>116.63301920017132</v>
       </c>
       <c r="G263" s="2">
-        <v>139.60843693113478</v>
+        <v>138.1330192001713</v>
       </c>
       <c r="H263" s="2">
-        <v>251.2951864760426</v>
+        <v>248.63943456030836</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
@@ -39775,13 +39799,13 @@
         <v>63</v>
       </c>
       <c r="F264" s="2">
-        <v>114.47261826454488</v>
+        <v>112.42253629803363</v>
       </c>
       <c r="G264" s="2">
-        <v>135.97261826454488</v>
+        <v>133.92253629803363</v>
       </c>
       <c r="H264" s="2">
-        <v>513.97649703997968</v>
+        <v>506.22718720656718</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
@@ -39801,13 +39825,13 @@
         <v>63</v>
       </c>
       <c r="F265" s="2">
-        <v>135.7446409508494</v>
+        <v>135.03792410713709</v>
       </c>
       <c r="G265" s="2">
-        <v>157.2446409508494</v>
+        <v>156.53792410713709</v>
       </c>
       <c r="H265" s="2">
-        <v>198.12824759807026</v>
+        <v>197.23778437499274</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
@@ -39827,13 +39851,13 @@
         <v>30</v>
       </c>
       <c r="F266" s="2">
-        <v>45.805675083822244</v>
+        <v>45.240127957765552</v>
       </c>
       <c r="G266" s="2">
-        <v>67.305675083822251</v>
+        <v>66.740127957765552</v>
       </c>
       <c r="H266" s="2">
-        <v>134.6113501676445</v>
+        <v>133.4802559155311</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
@@ -39905,13 +39929,13 @@
         <v>30</v>
       </c>
       <c r="F269" s="2">
-        <v>108.41245118991399</v>
+        <v>106.85680538702691</v>
       </c>
       <c r="G269" s="2">
-        <v>129.91245118991401</v>
+        <v>128.3568053870269</v>
       </c>
       <c r="H269" s="2">
-        <v>233.84241214184522</v>
+        <v>231.04224969664841</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
@@ -39931,13 +39955,13 @@
         <v>30</v>
       </c>
       <c r="F270" s="2">
-        <v>18.337756838095235</v>
+        <v>18.077711713015873</v>
       </c>
       <c r="G270" s="2">
-        <v>39.837756838095231</v>
+        <v>39.577711713015873</v>
       </c>
       <c r="H270" s="2">
-        <v>139.43214893333331</v>
+        <v>138.52199099555554</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -39957,13 +39981,13 @@
         <v>30</v>
       </c>
       <c r="F271" s="2">
-        <v>133.15537111373214</v>
+        <v>130.59597122839077</v>
       </c>
       <c r="G271" s="2">
-        <v>154.65537111373214</v>
+        <v>152.09597122839077</v>
       </c>
       <c r="H271" s="2">
-        <v>1328.3349824958455</v>
+        <v>1306.3522968806483</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
@@ -39983,13 +40007,13 @@
         <v>30</v>
       </c>
       <c r="F272" s="2">
-        <v>131.79032016254519</v>
+        <v>129.27455375876812</v>
       </c>
       <c r="G272" s="2">
-        <v>153.29032016254519</v>
+        <v>150.77455375876812</v>
       </c>
       <c r="H272" s="2">
-        <v>1445.3744288126386</v>
+        <v>1421.6532673914246</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
@@ -40087,13 +40111,13 @@
         <v>63</v>
       </c>
       <c r="F276" s="2">
-        <v>135.12138485033933</v>
+        <v>132.65138004343675</v>
       </c>
       <c r="G276" s="2">
-        <v>156.62138485033933</v>
+        <v>154.15138004343675</v>
       </c>
       <c r="H276" s="2">
-        <v>1392.2074899346662</v>
+        <v>1370.2516172061091</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
@@ -40113,13 +40137,13 @@
         <v>30</v>
       </c>
       <c r="F277" s="2">
-        <v>133.54111972990515</v>
+        <v>130.7305165535646</v>
       </c>
       <c r="G277" s="2">
-        <v>155.04111972990515</v>
+        <v>152.2305165535646</v>
       </c>
       <c r="H277" s="2">
-        <v>539.54309666006986</v>
+        <v>529.76219760640481</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
@@ -40139,13 +40163,13 @@
         <v>30</v>
       </c>
       <c r="F278" s="2">
-        <v>117.26355326603118</v>
+        <v>115.13632810890817</v>
       </c>
       <c r="G278" s="2">
-        <v>138.76355326603118</v>
+        <v>136.63632810890817</v>
       </c>
       <c r="H278" s="2">
-        <v>344.13361209975733</v>
+        <v>338.85809371009225</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
@@ -40165,13 +40189,13 @@
         <v>30</v>
       </c>
       <c r="F279" s="2">
-        <v>110.08450008596863</v>
+        <v>107.85699449853549</v>
       </c>
       <c r="G279" s="2">
-        <v>131.58450008596861</v>
+        <v>129.35699449853547</v>
       </c>
       <c r="H279" s="2">
-        <v>700.02954045735305</v>
+        <v>688.17921073220873</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
@@ -40243,13 +40267,13 @@
         <v>30</v>
       </c>
       <c r="F282" s="2">
-        <v>102.32448549030109</v>
+        <v>101.57732734209684</v>
       </c>
       <c r="G282" s="2">
-        <v>123.82448549030109</v>
+        <v>123.07732734209684</v>
       </c>
       <c r="H282" s="2">
-        <v>152.30411715307034</v>
+        <v>151.3851126307791</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
@@ -40269,13 +40293,13 @@
         <v>30</v>
       </c>
       <c r="F283" s="2">
-        <v>90.644485091652939</v>
+        <v>89.146131404794232</v>
       </c>
       <c r="G283" s="2">
-        <v>112.14448509165294</v>
+        <v>110.64613140479423</v>
       </c>
       <c r="H283" s="2">
-        <v>408.20592573361671</v>
+        <v>402.75191831345103</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
@@ -40295,13 +40319,13 @@
         <v>63</v>
       </c>
       <c r="F284" s="2">
-        <v>132.97839216506068</v>
+        <v>130.17866324259111</v>
       </c>
       <c r="G284" s="2">
-        <v>154.47839216506068</v>
+        <v>151.67866324259111</v>
       </c>
       <c r="H284" s="2">
-        <v>675.99744411430561</v>
+        <v>663.7458303495788</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
@@ -40321,13 +40345,13 @@
         <v>63</v>
       </c>
       <c r="F285" s="2">
-        <v>135.97428303225769</v>
+        <v>133.24540710990757</v>
       </c>
       <c r="G285" s="2">
-        <v>157.47428303225769</v>
+        <v>154.74540710990757</v>
       </c>
       <c r="H285" s="2">
-        <v>752.09717576206265</v>
+        <v>739.06406435691849</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
@@ -40347,13 +40371,13 @@
         <v>63</v>
       </c>
       <c r="F286" s="2">
-        <v>133.85374790755</v>
+        <v>131.25144000919914</v>
       </c>
       <c r="G286" s="2">
-        <v>155.35374790755</v>
+        <v>152.75144000919914</v>
       </c>
       <c r="H286" s="2">
-        <v>754.39779983906283</v>
+        <v>741.76099268467101</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
@@ -40373,13 +40397,13 @@
         <v>30</v>
       </c>
       <c r="F287" s="2">
-        <v>38.351156543650276</v>
+        <v>37.759398858403841</v>
       </c>
       <c r="G287" s="2">
-        <v>59.851156543650276</v>
+        <v>59.259398858403841</v>
       </c>
       <c r="H287" s="2">
-        <v>119.70231308730055</v>
+        <v>118.51879771680768</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
@@ -40399,13 +40423,13 @@
         <v>30</v>
       </c>
       <c r="F288" s="2">
-        <v>87.76680164242039</v>
+        <v>86.704191323639279</v>
       </c>
       <c r="G288" s="2">
-        <v>109.26680164242039</v>
+        <v>108.20419132363928</v>
       </c>
       <c r="H288" s="2">
-        <v>305.9470445987771</v>
+        <v>302.97173570619003</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
@@ -40425,13 +40449,13 @@
         <v>30</v>
       </c>
       <c r="F289" s="2">
-        <v>116.09045326390888</v>
+        <v>114.51230209696067</v>
       </c>
       <c r="G289" s="2">
-        <v>137.5904532639089</v>
+        <v>136.01230209696067</v>
       </c>
       <c r="H289" s="2">
-        <v>429.28221418339575</v>
+        <v>424.35838254251729</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
@@ -40451,13 +40475,13 @@
         <v>30</v>
       </c>
       <c r="F290" s="2">
-        <v>141.83407442657776</v>
+        <v>141.03158819810886</v>
       </c>
       <c r="G290" s="2">
-        <v>163.33407442657776</v>
+        <v>162.53158819810886</v>
       </c>
       <c r="H290" s="2">
-        <v>156.80071144951464</v>
+        <v>156.03032467018451</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
@@ -40477,13 +40501,13 @@
         <v>30</v>
       </c>
       <c r="F291" s="2">
-        <v>111.40979487069635</v>
+        <v>109.69061371493372</v>
       </c>
       <c r="G291" s="2">
-        <v>132.90979487069635</v>
+        <v>131.1906137149337</v>
       </c>
       <c r="H291" s="2">
-        <v>350.88185845863836</v>
+        <v>346.34322020742502</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
@@ -40503,13 +40527,13 @@
         <v>30</v>
       </c>
       <c r="F292" s="2">
-        <v>119.82810831693374</v>
+        <v>117.29433251350306</v>
       </c>
       <c r="G292" s="2">
-        <v>141.32810831693374</v>
+        <v>138.79433251350306</v>
       </c>
       <c r="H292" s="2">
-        <v>748.4736616464811</v>
+        <v>735.05478499151229</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
@@ -40529,13 +40553,13 @@
         <v>30</v>
       </c>
       <c r="F293" s="2">
-        <v>130.00843479242263</v>
+        <v>127.36390179392167</v>
       </c>
       <c r="G293" s="2">
-        <v>151.50843479242263</v>
+        <v>148.86390179392168</v>
       </c>
       <c r="H293" s="2">
-        <v>1031.3179156320209</v>
+        <v>1013.316579511225</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
@@ -40555,13 +40579,13 @@
         <v>63</v>
       </c>
       <c r="F294" s="2">
-        <v>123.41415365333771</v>
+        <v>120.99110343009536</v>
       </c>
       <c r="G294" s="2">
-        <v>144.91415365333771</v>
+        <v>142.49110343009536</v>
       </c>
       <c r="H294" s="2">
-        <v>1441.7509146970567</v>
+        <v>1417.6439880260189</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
@@ -40581,13 +40605,13 @@
         <v>63</v>
       </c>
       <c r="F295" s="2">
-        <v>112.88217362316973</v>
+        <v>110.71711363829625</v>
       </c>
       <c r="G295" s="2">
-        <v>134.38217362316973</v>
+        <v>132.21711363829627</v>
       </c>
       <c r="H295" s="2">
-        <v>1100.1868554528905</v>
+        <v>1082.4615093567315</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
@@ -40607,13 +40631,13 @@
         <v>30</v>
       </c>
       <c r="F296" s="2">
-        <v>88.391881121220493</v>
+        <v>86.833525582917332</v>
       </c>
       <c r="G296" s="2">
-        <v>109.89188112122049</v>
+        <v>108.33352558291733</v>
       </c>
       <c r="H296" s="2">
-        <v>347.25834434305676</v>
+        <v>342.33394084201876</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
@@ -40633,13 +40657,13 @@
         <v>63</v>
       </c>
       <c r="F297" s="2">
-        <v>73.26277912596278</v>
+        <v>71.82047207434924</v>
       </c>
       <c r="G297" s="2">
-        <v>94.76277912596278</v>
+        <v>93.32047207434924</v>
       </c>
       <c r="H297" s="2">
-        <v>348.72702718354304</v>
+        <v>343.41933723360523</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
@@ -40659,13 +40683,13 @@
         <v>63</v>
       </c>
       <c r="F298" s="2">
-        <v>74.291843360185823</v>
+        <v>73.140949923604339</v>
       </c>
       <c r="G298" s="2">
-        <v>95.791843360185823</v>
+        <v>94.640949923604339</v>
       </c>
       <c r="H298" s="2">
-        <v>266.6844919147573</v>
+        <v>263.48040458731447</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
@@ -40685,13 +40709,13 @@
         <v>30</v>
       </c>
       <c r="F299" s="2">
-        <v>87.76680164242039</v>
+        <v>86.704191323639279</v>
       </c>
       <c r="G299" s="2">
-        <v>109.26680164242039</v>
+        <v>108.20419132363928</v>
       </c>
       <c r="H299" s="2">
-        <v>305.9470445987771</v>
+        <v>302.97173570619003</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
@@ -40711,13 +40735,13 @@
         <v>30</v>
       </c>
       <c r="F300" s="2">
-        <v>105.065280925067</v>
+        <v>102.83808141365708</v>
       </c>
       <c r="G300" s="2">
-        <v>126.565280925067</v>
+        <v>124.33808141365708</v>
       </c>
       <c r="H300" s="2">
-        <v>496.13590122626266</v>
+        <v>487.40527914153574</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
@@ -40737,13 +40761,13 @@
         <v>30</v>
       </c>
       <c r="F301" s="2">
-        <v>101.57433800436932</v>
+        <v>99.396778589697107</v>
       </c>
       <c r="G301" s="2">
-        <v>123.07433800436932</v>
+        <v>120.89677858969711</v>
       </c>
       <c r="H301" s="2">
-        <v>492.29735201747729</v>
+        <v>483.58711435878843</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
@@ -40763,13 +40787,13 @@
         <v>30</v>
       </c>
       <c r="F302" s="2">
-        <v>90.644485091652939</v>
+        <v>89.146131404794232</v>
       </c>
       <c r="G302" s="2">
-        <v>112.14448509165294</v>
+        <v>110.64613140479423</v>
       </c>
       <c r="H302" s="2">
-        <v>408.20592573361671</v>
+        <v>402.75191831345103</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
@@ -40815,13 +40839,13 @@
         <v>30</v>
       </c>
       <c r="F304" s="2">
-        <v>45.805675083822244</v>
+        <v>45.240127957765552</v>
       </c>
       <c r="G304" s="2">
-        <v>67.305675083822251</v>
+        <v>66.740127957765552</v>
       </c>
       <c r="H304" s="2">
-        <v>134.6113501676445</v>
+        <v>133.4802559155311</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
@@ -40841,13 +40865,13 @@
         <v>30</v>
       </c>
       <c r="F305" s="2">
-        <v>45.805675083822244</v>
+        <v>45.240127957765552</v>
       </c>
       <c r="G305" s="2">
-        <v>67.305675083822251</v>
+        <v>66.740127957765552</v>
       </c>
       <c r="H305" s="2">
-        <v>134.6113501676445</v>
+        <v>133.4802559155311</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
@@ -40867,13 +40891,13 @@
         <v>30</v>
       </c>
       <c r="F306" s="2">
-        <v>45.805675083822244</v>
+        <v>45.240127957765552</v>
       </c>
       <c r="G306" s="2">
-        <v>67.305675083822251</v>
+        <v>66.740127957765552</v>
       </c>
       <c r="H306" s="2">
-        <v>134.6113501676445</v>
+        <v>133.4802559155311</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
@@ -40893,13 +40917,13 @@
         <v>30</v>
       </c>
       <c r="F307" s="2">
-        <v>132.2142469784375</v>
+        <v>129.08234509043751</v>
       </c>
       <c r="G307" s="2">
-        <v>138.2142469784375</v>
+        <v>135.08234509043751</v>
       </c>
       <c r="H307" s="2">
-        <v>414.64274093531253</v>
+        <v>405.24703527131254</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
@@ -40919,13 +40943,13 @@
         <v>30</v>
       </c>
       <c r="F308" s="2">
-        <v>120.93743524006135</v>
+        <v>119.46339462072285</v>
       </c>
       <c r="G308" s="2">
-        <v>142.43743524006135</v>
+        <v>140.96339462072285</v>
       </c>
       <c r="H308" s="2">
-        <v>256.38738343211043</v>
+        <v>253.73411031730114</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
@@ -40945,13 +40969,13 @@
         <v>30</v>
       </c>
       <c r="F309" s="2">
-        <v>110.86924039146453</v>
+        <v>108.54440222989484</v>
       </c>
       <c r="G309" s="2">
-        <v>132.36924039146453</v>
+        <v>130.04440222989484</v>
       </c>
       <c r="H309" s="2">
-        <v>980.45896357957781</v>
+        <v>963.2388873168311</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
@@ -40971,13 +40995,13 @@
         <v>30</v>
       </c>
       <c r="F310" s="2">
-        <v>138.92019582868448</v>
+        <v>136.31908696312595</v>
       </c>
       <c r="G310" s="2">
-        <v>160.42019582868448</v>
+        <v>157.81908696312595</v>
       </c>
       <c r="H310" s="2">
-        <v>1214.220462227313</v>
+        <v>1194.5326692239003</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
@@ -40997,13 +41021,13 @@
         <v>30</v>
       </c>
       <c r="F311" s="2">
-        <v>135.12138485033933</v>
+        <v>132.65138004343675</v>
       </c>
       <c r="G311" s="2">
-        <v>156.62138485033933</v>
+        <v>154.15138004343675</v>
       </c>
       <c r="H311" s="2">
-        <v>1392.2074899346662</v>
+        <v>1370.2516172061091</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
@@ -41023,13 +41047,13 @@
         <v>30</v>
       </c>
       <c r="F312" s="2">
-        <v>135.50074419398237</v>
+        <v>132.79989435580708</v>
       </c>
       <c r="G312" s="2">
-        <v>157.00074419398237</v>
+        <v>154.29989435580708</v>
       </c>
       <c r="H312" s="2">
-        <v>936.82344060549292</v>
+        <v>920.70746962110093</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
@@ -41049,13 +41073,13 @@
         <v>63</v>
       </c>
       <c r="F313" s="2">
-        <v>132.82997206897178</v>
+        <v>130.35578983504251</v>
       </c>
       <c r="G313" s="2">
-        <v>154.32997206897178</v>
+        <v>151.85578983504251</v>
       </c>
       <c r="H313" s="2">
-        <v>795.72533598761856</v>
+        <v>782.96845238947924</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
@@ -41075,13 +41099,13 @@
         <v>30</v>
       </c>
       <c r="F314" s="2">
-        <v>134.57961971502289</v>
+        <v>131.98889888717235</v>
       </c>
       <c r="G314" s="2">
-        <v>156.07961971502289</v>
+        <v>153.48889888717235</v>
       </c>
       <c r="H314" s="2">
-        <v>978.15097675404843</v>
+        <v>961.91492932590916</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
@@ -41101,13 +41125,13 @@
         <v>63</v>
       </c>
       <c r="F315" s="2">
-        <v>135.4159588976558</v>
+        <v>132.97924521181048</v>
       </c>
       <c r="G315" s="2">
-        <v>156.9159588976558</v>
+        <v>154.47924521181048</v>
       </c>
       <c r="H315" s="2">
-        <v>871.8250676353756</v>
+        <v>858.28668639681905</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
@@ -41127,13 +41151,13 @@
         <v>30</v>
       </c>
       <c r="F316" s="2">
-        <v>52.810757827816872</v>
+        <v>51.992407796378075</v>
       </c>
       <c r="G316" s="2">
-        <v>74.310757827816872</v>
+        <v>73.492407796378075</v>
       </c>
       <c r="H316" s="2">
-        <v>154.93793007099816</v>
+        <v>153.23167025544828</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
@@ -41153,13 +41177,13 @@
         <v>30</v>
       </c>
       <c r="F317" s="2">
-        <v>81.070728594183478</v>
+        <v>79.930510961137429</v>
       </c>
       <c r="G317" s="2">
-        <v>102.57072859418348</v>
+        <v>101.43051096113743</v>
       </c>
       <c r="H317" s="2">
-        <v>287.71089370668466</v>
+        <v>284.51258324599053</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
@@ -41179,13 +41203,13 @@
         <v>30</v>
       </c>
       <c r="F318" s="2">
-        <v>43.173704083333334</v>
+        <v>42.37652513888888</v>
       </c>
       <c r="G318" s="2">
-        <v>64.673704083333334</v>
+        <v>63.87652513888888</v>
       </c>
       <c r="H318" s="2">
-        <v>258.69481633333334</v>
+        <v>255.50610055555552</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
@@ -41205,13 +41229,13 @@
         <v>30</v>
       </c>
       <c r="F319" s="2">
-        <v>98.323674285374025</v>
+        <v>96.164410803142232</v>
       </c>
       <c r="G319" s="2">
-        <v>119.82367428537403</v>
+        <v>117.66441080314223</v>
       </c>
       <c r="H319" s="2">
-        <v>359.47102285612209</v>
+        <v>352.9932324094267</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
@@ -41231,13 +41255,13 @@
         <v>30</v>
       </c>
       <c r="F320" s="2">
-        <v>93.517718605102019</v>
+        <v>91.927805519767134</v>
       </c>
       <c r="G320" s="2">
-        <v>115.01771860510202</v>
+        <v>113.42780551976713</v>
       </c>
       <c r="H320" s="2">
-        <v>379.55847139683664</v>
+        <v>374.31175821523152</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
@@ -41257,13 +41281,13 @@
         <v>30</v>
       </c>
       <c r="F321" s="2">
-        <v>98.492147649257376</v>
+        <v>96.338683041166618</v>
       </c>
       <c r="G321" s="2">
-        <v>119.99214764925738</v>
+        <v>117.83868304116662</v>
       </c>
       <c r="H321" s="2">
-        <v>539.9646644216582</v>
+        <v>530.27407368524973</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
@@ -41283,13 +41307,13 @@
         <v>30</v>
       </c>
       <c r="F322" s="2">
-        <v>94.104998333333313</v>
+        <v>92.044381333333334</v>
       </c>
       <c r="G322" s="2">
-        <v>115.60499833333331</v>
+        <v>113.54438133333333</v>
       </c>
       <c r="H322" s="2">
-        <v>346.81499499999995</v>
+        <v>340.63314400000002</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
@@ -41309,13 +41333,13 @@
         <v>30</v>
       </c>
       <c r="F323" s="2">
-        <v>84.271991066862242</v>
+        <v>82.596964216439545</v>
       </c>
       <c r="G323" s="2">
-        <v>105.77199106686224</v>
+        <v>104.09696421643955</v>
       </c>
       <c r="H323" s="2">
-        <v>528.85995533431117</v>
+        <v>520.48482108219775</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
@@ -41335,13 +41359,13 @@
         <v>30</v>
       </c>
       <c r="F324" s="2">
-        <v>52.839335786862236</v>
+        <v>51.832119016439563</v>
       </c>
       <c r="G324" s="2">
-        <v>74.339335786862236</v>
+        <v>73.332119016439563</v>
       </c>
       <c r="H324" s="2">
-        <v>371.69667893431119</v>
+        <v>366.6605950821978</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
@@ -41361,13 +41385,13 @@
         <v>30</v>
       </c>
       <c r="F325" s="2">
-        <v>109.48093238733732</v>
+        <v>107.76081229183039</v>
       </c>
       <c r="G325" s="2">
-        <v>130.9809323873373</v>
+        <v>129.2608122918304</v>
       </c>
       <c r="H325" s="2">
-        <v>172.89483075128524</v>
+        <v>170.62427222521615</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
@@ -41387,13 +41411,13 @@
         <v>30</v>
       </c>
       <c r="F326" s="2">
-        <v>114.47261826454488</v>
+        <v>112.42253629803363</v>
       </c>
       <c r="G326" s="2">
-        <v>135.97261826454488</v>
+        <v>133.92253629803363</v>
       </c>
       <c r="H326" s="2">
-        <v>513.97649703997968</v>
+        <v>506.22718720656718</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
@@ -41413,13 +41437,13 @@
         <v>30</v>
       </c>
       <c r="F327" s="2">
-        <v>108.82498705031816</v>
+        <v>106.69008835287042</v>
       </c>
       <c r="G327" s="2">
-        <v>130.32498705031816</v>
+        <v>128.19008835287042</v>
       </c>
       <c r="H327" s="2">
-        <v>755.88492489184523</v>
+        <v>743.50251244664844</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
@@ -41491,13 +41515,13 @@
         <v>30</v>
       </c>
       <c r="F330" s="2">
-        <v>110.49661533628151</v>
+        <v>108.87217874322349</v>
       </c>
       <c r="G330" s="2">
-        <v>131.99661533628151</v>
+        <v>130.37217874322349</v>
       </c>
       <c r="H330" s="2">
-        <v>411.82943984919831</v>
+        <v>406.76119767885729</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
@@ -41517,13 +41541,13 @@
         <v>30</v>
       </c>
       <c r="F331" s="2">
-        <v>108.41245118991399</v>
+        <v>106.85680538702691</v>
       </c>
       <c r="G331" s="2">
-        <v>129.91245118991401</v>
+        <v>128.3568053870269</v>
       </c>
       <c r="H331" s="2">
-        <v>233.84241214184522</v>
+        <v>231.04224969664841</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
@@ -41543,13 +41567,13 @@
         <v>30</v>
       </c>
       <c r="F332" s="2">
-        <v>113.3386573540554</v>
+        <v>111.62041513803702</v>
       </c>
       <c r="G332" s="2">
-        <v>134.83865735405539</v>
+        <v>133.120415138037</v>
       </c>
       <c r="H332" s="2">
-        <v>355.97405541470624</v>
+        <v>351.43789596441769</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
@@ -41595,13 +41619,13 @@
         <v>30</v>
       </c>
       <c r="F334" s="2">
-        <v>98.492147649257376</v>
+        <v>96.338683041166618</v>
       </c>
       <c r="G334" s="2">
-        <v>119.99214764925738</v>
+        <v>117.83868304116662</v>
       </c>
       <c r="H334" s="2">
-        <v>539.9646644216582</v>
+        <v>530.27407368524973</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
@@ -41621,13 +41645,13 @@
         <v>30</v>
       </c>
       <c r="F335" s="2">
-        <v>108.41245118991399</v>
+        <v>106.85680538702691</v>
       </c>
       <c r="G335" s="2">
-        <v>129.91245118991401</v>
+        <v>128.3568053870269</v>
       </c>
       <c r="H335" s="2">
-        <v>233.84241214184522</v>
+        <v>231.04224969664841</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
@@ -41751,13 +41775,13 @@
         <v>30</v>
       </c>
       <c r="F340" s="2">
-        <v>48.887810784901603</v>
+        <v>48.001475599679054</v>
       </c>
       <c r="G340" s="2">
-        <v>70.387810784901603</v>
+        <v>69.501475599679054</v>
       </c>
       <c r="H340" s="2">
-        <v>492.71467549431122</v>
+        <v>486.51032919775338</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
@@ -41933,13 +41957,13 @@
         <v>63</v>
       </c>
       <c r="F347" s="2">
-        <v>132.2142469784375</v>
+        <v>129.08234509043751</v>
       </c>
       <c r="G347" s="2">
-        <v>138.2142469784375</v>
+        <v>135.08234509043751</v>
       </c>
       <c r="H347" s="2">
-        <v>138.2142469784375</v>
+        <v>135.08234509043751</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
@@ -41959,13 +41983,13 @@
         <v>63</v>
       </c>
       <c r="F348" s="2">
-        <v>132.93435523018795</v>
+        <v>129.89771860085463</v>
       </c>
       <c r="G348" s="2">
-        <v>138.93435523018795</v>
+        <v>135.89771860085463</v>
       </c>
       <c r="H348" s="2">
-        <v>416.80306569056381</v>
+        <v>407.69315580256387</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
@@ -41985,13 +42009,13 @@
         <v>63</v>
       </c>
       <c r="F349" s="2">
-        <v>131.22493731087184</v>
+        <v>128.1859848388718</v>
       </c>
       <c r="G349" s="2">
-        <v>137.22493731087184</v>
+        <v>134.1859848388718</v>
       </c>
       <c r="H349" s="2">
-        <v>548.89974924348735</v>
+        <v>536.74393935548721</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
@@ -42011,13 +42035,13 @@
         <v>63</v>
       </c>
       <c r="F350" s="2">
-        <v>129.84110970935347</v>
+        <v>126.8064277317535</v>
       </c>
       <c r="G350" s="2">
-        <v>135.84110970935347</v>
+        <v>132.8064277317535</v>
       </c>
       <c r="H350" s="2">
-        <v>679.20554854676743</v>
+        <v>664.03213865876751</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
@@ -45313,13 +45337,13 @@
         <v>63</v>
       </c>
       <c r="F477" s="2">
-        <v>114.19089063688369</v>
+        <v>112.47410779460267</v>
       </c>
       <c r="G477" s="2">
-        <v>135.69089063688369</v>
+        <v>133.97410779460267</v>
       </c>
       <c r="H477" s="2">
-        <v>537.33592692205946</v>
+        <v>530.53746686662657</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
@@ -45339,13 +45363,13 @@
         <v>63</v>
       </c>
       <c r="F478" s="2">
-        <v>123.7216</v>
+        <v>120.70399999999999</v>
       </c>
       <c r="G478" s="2">
-        <v>123.7216</v>
+        <v>120.70399999999999</v>
       </c>
       <c r="H478" s="2">
-        <v>123.7216</v>
+        <v>120.70399999999999</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
@@ -45365,13 +45389,13 @@
         <v>63</v>
       </c>
       <c r="F479" s="2">
-        <v>122.8427375</v>
+        <v>120.15613250000001</v>
       </c>
       <c r="G479" s="2">
-        <v>144.3427375</v>
+        <v>141.65613250000001</v>
       </c>
       <c r="H479" s="2">
-        <v>259.81692750000002</v>
+        <v>254.98103850000004</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -45391,13 +45415,13 @@
         <v>63</v>
       </c>
       <c r="F480" s="2">
-        <v>126.09575022970085</v>
+        <v>123.34118869123932</v>
       </c>
       <c r="G480" s="2">
-        <v>147.59575022970085</v>
+        <v>144.84118869123932</v>
       </c>
       <c r="H480" s="2">
-        <v>383.74895059722223</v>
+        <v>376.58709059722224</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
@@ -45443,13 +45467,13 @@
         <v>63</v>
       </c>
       <c r="F482" s="2">
-        <v>118.5861688527778</v>
+        <v>115.99036060646199</v>
       </c>
       <c r="G482" s="2">
-        <v>140.0861688527778</v>
+        <v>137.49036060646199</v>
       </c>
       <c r="H482" s="2">
-        <v>252.15510393500006</v>
+        <v>247.4826490916316</v>
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
@@ -45469,13 +45493,13 @@
         <v>63</v>
       </c>
       <c r="F483" s="2">
-        <v>118.36392366047012</v>
+        <v>115.77279426030815</v>
       </c>
       <c r="G483" s="2">
-        <v>139.86392366047011</v>
+        <v>137.27279426030816</v>
       </c>
       <c r="H483" s="2">
-        <v>363.64620151722227</v>
+        <v>356.9092650768012</v>
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
@@ -45599,13 +45623,13 @@
         <v>63</v>
       </c>
       <c r="F488" s="2">
-        <v>43.489709521547297</v>
+        <v>43.420699834532797</v>
       </c>
       <c r="G488" s="2">
-        <v>64.989709521547297</v>
+        <v>64.920699834532797</v>
       </c>
       <c r="H488" s="2">
-        <v>139.72787547132668</v>
+        <v>139.5795046442455</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
@@ -45625,13 +45649,13 @@
         <v>63</v>
       </c>
       <c r="F489" s="2">
-        <v>25.444622837350906</v>
+        <v>25.27202283735091</v>
       </c>
       <c r="G489" s="2">
-        <v>46.944622837350906</v>
+        <v>46.77202283735091</v>
       </c>
       <c r="H489" s="2">
-        <v>100.93093910030444</v>
+        <v>100.55984910030445</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
@@ -45651,13 +45675,13 @@
         <v>63</v>
       </c>
       <c r="F490" s="2">
-        <v>126.17665587267186</v>
+        <v>125.64232780592555</v>
       </c>
       <c r="G490" s="2">
-        <v>147.67665587267186</v>
+        <v>147.14232780592556</v>
       </c>
       <c r="H490" s="2">
-        <v>35.442397409441242</v>
+        <v>35.314158673422135</v>
       </c>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
@@ -45677,13 +45701,13 @@
         <v>63</v>
       </c>
       <c r="F491" s="2">
-        <v>116.48757380895063</v>
+        <v>113.93594651092593</v>
       </c>
       <c r="G491" s="2">
-        <v>137.98757380895063</v>
+        <v>135.43594651092593</v>
       </c>
       <c r="H491" s="2">
-        <v>248.37763285611115</v>
+        <v>243.78470371966668</v>
       </c>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
@@ -45703,13 +45727,13 @@
         <v>63</v>
       </c>
       <c r="F492" s="2">
-        <v>132.86517888661658</v>
+        <v>130.25932971771294</v>
       </c>
       <c r="G492" s="2">
-        <v>154.36517888661658</v>
+        <v>151.75932971771294</v>
       </c>
       <c r="H492" s="2">
-        <v>1112.5098442358458</v>
+        <v>1093.7294892755574</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
@@ -45755,13 +45779,13 @@
         <v>63</v>
       </c>
       <c r="F494" s="2">
-        <v>116.66347747005007</v>
+        <v>114.48616228548295</v>
       </c>
       <c r="G494" s="2">
-        <v>138.16347747005005</v>
+        <v>135.98616228548295</v>
       </c>
       <c r="H494" s="2">
-        <v>1438.1436369857508</v>
+        <v>1415.4799632295919</v>
       </c>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
@@ -45781,13 +45805,13 @@
         <v>63</v>
       </c>
       <c r="F495" s="2">
-        <v>124.85499542200854</v>
+        <v>122.12655503739317</v>
       </c>
       <c r="G495" s="2">
-        <v>146.35499542200853</v>
+        <v>143.62655503739319</v>
       </c>
       <c r="H495" s="2">
-        <v>526.87798351923072</v>
+        <v>517.05559813461548</v>
       </c>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
@@ -45807,13 +45831,13 @@
         <v>63</v>
       </c>
       <c r="F496" s="2">
-        <v>118.5861688527778</v>
+        <v>115.99036060646199</v>
       </c>
       <c r="G496" s="2">
-        <v>140.0861688527778</v>
+        <v>137.49036060646199</v>
       </c>
       <c r="H496" s="2">
-        <v>504.31020787000011</v>
+        <v>494.9652981832632</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
@@ -45833,13 +45857,13 @@
         <v>63</v>
       </c>
       <c r="F497" s="2">
-        <v>90.868792922222227</v>
+        <v>89.707989722222223</v>
       </c>
       <c r="G497" s="2">
-        <v>112.36879292222223</v>
+        <v>111.20798972222222</v>
       </c>
       <c r="H497" s="2">
-        <v>112.36879292222223</v>
+        <v>111.20798972222222</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
@@ -45885,13 +45909,13 @@
         <v>63</v>
       </c>
       <c r="F499" s="2">
-        <v>168.92557500000001</v>
+        <v>166.10004499999999</v>
       </c>
       <c r="G499" s="2">
-        <v>190.42557500000001</v>
+        <v>187.60004499999999</v>
       </c>
       <c r="H499" s="2">
-        <v>190.42557500000001</v>
+        <v>187.60004499999999</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
@@ -45911,13 +45935,13 @@
         <v>63</v>
       </c>
       <c r="F500" s="2">
-        <v>113.57905000000001</v>
+        <v>111.08747</v>
       </c>
       <c r="G500" s="2">
-        <v>135.07905</v>
+        <v>132.58747</v>
       </c>
       <c r="H500" s="2">
-        <v>135.07905</v>
+        <v>132.58747</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
@@ -45937,13 +45961,13 @@
         <v>63</v>
       </c>
       <c r="F501" s="2">
-        <v>98.782030548064455</v>
+        <v>97.313465729323823</v>
       </c>
       <c r="G501" s="2">
-        <v>120.28203054806445</v>
+        <v>118.81346572932382</v>
       </c>
       <c r="H501" s="2">
-        <v>534.05221563340626</v>
+        <v>527.53178783819783</v>
       </c>
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
@@ -45963,13 +45987,13 @@
         <v>63</v>
       </c>
       <c r="F502" s="2">
-        <v>126.84091369506898</v>
+        <v>124.55096527854924</v>
       </c>
       <c r="G502" s="2">
-        <v>148.34091369506899</v>
+        <v>146.05096527854926</v>
       </c>
       <c r="H502" s="2">
-        <v>338.21728322475735</v>
+        <v>332.99620083509234</v>
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
@@ -45989,13 +46013,13 @@
         <v>63</v>
       </c>
       <c r="F503" s="2">
-        <v>39.421930486111108</v>
+        <v>38.515690486111119</v>
       </c>
       <c r="G503" s="2">
-        <v>60.921930486111108</v>
+        <v>60.015690486111119</v>
       </c>
       <c r="H503" s="2">
-        <v>60.921930486111108</v>
+        <v>60.015690486111119</v>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
@@ -46041,13 +46065,13 @@
         <v>63</v>
       </c>
       <c r="F505" s="2">
-        <v>113.40337403713622</v>
+        <v>111.74212823424912</v>
       </c>
       <c r="G505" s="2">
-        <v>134.90337403713622</v>
+        <v>133.24212823424912</v>
       </c>
       <c r="H505" s="2">
-        <v>242.82607326684519</v>
+        <v>239.83583082164841</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -46067,13 +46091,13 @@
         <v>63</v>
       </c>
       <c r="F506" s="2">
-        <v>118.82178051517728</v>
+        <v>116.54486746224644</v>
       </c>
       <c r="G506" s="2">
-        <v>140.3217805151773</v>
+        <v>138.04486746224643</v>
       </c>
       <c r="H506" s="2">
-        <v>437.80395520735317</v>
+        <v>430.69998648220889</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
@@ -46093,13 +46117,13 @@
         <v>63</v>
       </c>
       <c r="F507" s="2">
-        <v>124.21122245934916</v>
+        <v>123.53039721223476</v>
       </c>
       <c r="G507" s="2">
-        <v>145.71122245934916</v>
+        <v>145.03039721223476</v>
       </c>
       <c r="H507" s="2">
-        <v>128.22587576422725</v>
+        <v>127.62674954676659</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -46119,13 +46143,13 @@
         <v>63</v>
       </c>
       <c r="F508" s="2">
-        <v>124.21122245934916</v>
+        <v>123.53039721223476</v>
       </c>
       <c r="G508" s="2">
-        <v>145.71122245934916</v>
+        <v>145.03039721223476</v>
       </c>
       <c r="H508" s="2">
-        <v>128.22587576422725</v>
+        <v>127.62674954676659</v>
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
@@ -46145,13 +46169,13 @@
         <v>63</v>
       </c>
       <c r="F509" s="2">
-        <v>124.59985882298551</v>
+        <v>123.9108517576893</v>
       </c>
       <c r="G509" s="2">
-        <v>146.09985882298551</v>
+        <v>145.4108517576893</v>
       </c>
       <c r="H509" s="2">
-        <v>128.56787576422724</v>
+        <v>127.96154954676659</v>
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
@@ -46171,13 +46195,13 @@
         <v>63</v>
       </c>
       <c r="F510" s="2">
-        <v>133.21143458056127</v>
+        <v>132.31936084859842</v>
       </c>
       <c r="G510" s="2">
-        <v>154.71143458056127</v>
+        <v>153.81936084859842</v>
       </c>
       <c r="H510" s="2">
-        <v>68.07303121544696</v>
+        <v>67.680518773383312</v>
       </c>
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
@@ -46197,13 +46221,13 @@
         <v>63</v>
       </c>
       <c r="F511" s="2">
-        <v>133.83973003510673</v>
+        <v>132.9344290304166</v>
       </c>
       <c r="G511" s="2">
-        <v>155.33973003510673</v>
+        <v>154.4344290304166</v>
       </c>
       <c r="H511" s="2">
-        <v>68.349481215446957</v>
+        <v>67.951148773383309</v>
       </c>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
@@ -46223,13 +46247,13 @@
         <v>63</v>
       </c>
       <c r="F512" s="2">
-        <v>128.89325276237946</v>
+        <v>128.0920881213257</v>
       </c>
       <c r="G512" s="2">
-        <v>150.39325276237946</v>
+        <v>149.5920881213257</v>
       </c>
       <c r="H512" s="2">
-        <v>66.173031215446969</v>
+        <v>65.820518773383313</v>
       </c>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
@@ -46249,13 +46273,13 @@
         <v>63</v>
       </c>
       <c r="F513" s="2">
-        <v>112.40249142810458</v>
+        <v>109.93546848692812</v>
       </c>
       <c r="G513" s="2">
-        <v>133.90249142810458</v>
+        <v>131.43546848692813</v>
       </c>
       <c r="H513" s="2">
-        <v>227.63423542777778</v>
+        <v>223.44029642777781</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
@@ -46275,13 +46299,13 @@
         <v>63</v>
       </c>
       <c r="F514" s="2">
-        <v>104.76449142810458</v>
+        <v>102.45826848692811</v>
       </c>
       <c r="G514" s="2">
-        <v>126.26449142810458</v>
+        <v>123.95826848692811</v>
       </c>
       <c r="H514" s="2">
-        <v>214.64963542777778</v>
+        <v>210.72905642777778</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
@@ -46301,13 +46325,13 @@
         <v>63</v>
       </c>
       <c r="F515" s="2">
-        <v>96.993491428104576</v>
+        <v>94.958868486928111</v>
       </c>
       <c r="G515" s="2">
-        <v>118.49349142810458</v>
+        <v>116.45886848692811</v>
       </c>
       <c r="H515" s="2">
-        <v>201.43893542777778</v>
+        <v>197.98007642777779</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
@@ -46327,13 +46351,13 @@
         <v>63</v>
       </c>
       <c r="F516" s="2">
-        <v>111.43079402991454</v>
+        <v>108.98422787606839</v>
       </c>
       <c r="G516" s="2">
-        <v>132.93079402991452</v>
+        <v>130.48422787606839</v>
       </c>
       <c r="H516" s="2">
-        <v>345.62006447777776</v>
+        <v>339.25899247777784</v>
       </c>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
@@ -46353,13 +46377,13 @@
         <v>63</v>
       </c>
       <c r="F517" s="2">
-        <v>102.32979402991454</v>
+        <v>100.07482787606837</v>
       </c>
       <c r="G517" s="2">
-        <v>123.82979402991454</v>
+        <v>121.57482787606837</v>
       </c>
       <c r="H517" s="2">
-        <v>321.95746447777782</v>
+        <v>316.09455247777777</v>
       </c>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
@@ -46379,13 +46403,13 @@
         <v>63</v>
       </c>
       <c r="F518" s="2">
-        <v>94.558794029914537</v>
+        <v>92.575427876068375</v>
       </c>
       <c r="G518" s="2">
-        <v>116.05879402991454</v>
+        <v>114.07542787606837</v>
       </c>
       <c r="H518" s="2">
-        <v>301.75286447777779</v>
+        <v>296.59611247777781</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
@@ -46405,13 +46429,13 @@
         <v>63</v>
       </c>
       <c r="F519" s="2">
-        <v>145.12815110576148</v>
+        <v>143.87325828288954</v>
       </c>
       <c r="G519" s="2">
-        <v>166.62815110576148</v>
+        <v>165.37325828288954</v>
       </c>
       <c r="H519" s="2">
-        <v>833.1407555288074</v>
+        <v>826.86629141444769</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
@@ -46431,13 +46455,13 @@
         <v>63</v>
       </c>
       <c r="F520" s="2">
-        <v>125.61920297742803</v>
+        <v>123.38903452413474</v>
       </c>
       <c r="G520" s="2">
-        <v>147.11920297742802</v>
+        <v>144.88903452413473</v>
       </c>
       <c r="H520" s="2">
-        <v>511.97482636144952</v>
+        <v>504.21384014398888</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
@@ -46457,13 +46481,13 @@
         <v>63</v>
       </c>
       <c r="F521" s="2">
-        <v>115.23215082262401</v>
+        <v>113.08751477563213</v>
       </c>
       <c r="G521" s="2">
-        <v>136.73215082262402</v>
+        <v>134.58751477563214</v>
       </c>
       <c r="H521" s="2">
-        <v>1356.3829361604303</v>
+        <v>1335.1081465742709</v>
       </c>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
@@ -46483,13 +46507,13 @@
         <v>63</v>
       </c>
       <c r="F522" s="2">
-        <v>131.80740805227262</v>
+        <v>129.30858509352393</v>
       </c>
       <c r="G522" s="2">
-        <v>153.30740805227262</v>
+        <v>150.80858509352393</v>
       </c>
       <c r="H522" s="2">
-        <v>1370.5682279873172</v>
+        <v>1348.2287507361038</v>
       </c>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
@@ -46509,13 +46533,13 @@
         <v>63</v>
       </c>
       <c r="F523" s="2">
-        <v>140.3549792902665</v>
+        <v>137.52944929026648</v>
       </c>
       <c r="G523" s="2">
-        <v>161.8549792902665</v>
+        <v>159.02944929026648</v>
       </c>
       <c r="H523" s="2">
-        <v>1019.6863695286789</v>
+        <v>1001.8855305286788</v>
       </c>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
@@ -46535,13 +46559,13 @@
         <v>63</v>
       </c>
       <c r="F524" s="2">
-        <v>144.89964517600484</v>
+        <v>141.7624872690281</v>
       </c>
       <c r="G524" s="2">
-        <v>166.39964517600484</v>
+        <v>163.2624872690281</v>
       </c>
       <c r="H524" s="2">
-        <v>715.51847425682081</v>
+        <v>702.02869525682081</v>
       </c>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
@@ -46561,13 +46585,13 @@
         <v>63</v>
       </c>
       <c r="F525" s="2">
-        <v>145.56890858064517</v>
+        <v>142.43087858064513</v>
       </c>
       <c r="G525" s="2">
-        <v>167.06890858064517</v>
+        <v>163.93087858064513</v>
       </c>
       <c r="H525" s="2">
-        <v>534.62050745806459</v>
+        <v>524.57881145806448</v>
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
@@ -46587,13 +46611,13 @@
         <v>63</v>
       </c>
       <c r="F526" s="2">
-        <v>112.2335278899712</v>
+        <v>110.09073375030464</v>
       </c>
       <c r="G526" s="2">
-        <v>133.73352788997119</v>
+        <v>131.59073375030465</v>
       </c>
       <c r="H526" s="2">
-        <v>1059.1695408885719</v>
+        <v>1042.1986113024129</v>
       </c>
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
@@ -46613,13 +46637,13 @@
         <v>63</v>
       </c>
       <c r="F527" s="2">
-        <v>104.27157690357775</v>
+        <v>102.10343908497973</v>
       </c>
       <c r="G527" s="2">
-        <v>125.77157690357775</v>
+        <v>123.60343908497973</v>
       </c>
       <c r="H527" s="2">
-        <v>329.52153148737375</v>
+        <v>323.84101040264687</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
@@ -46665,13 +46689,13 @@
         <v>63</v>
       </c>
       <c r="F529" s="2">
-        <v>124.87944585511025</v>
+        <v>122.54533806847471</v>
       </c>
       <c r="G529" s="2">
-        <v>146.37944585511025</v>
+        <v>144.04533806847471</v>
       </c>
       <c r="H529" s="2">
-        <v>327.88995871544699</v>
+        <v>322.66155727338338</v>
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
@@ -46691,13 +46715,13 @@
         <v>63</v>
       </c>
       <c r="F530" s="2">
-        <v>111.41750398821978</v>
+        <v>109.19347071713662</v>
       </c>
       <c r="G530" s="2">
-        <v>132.91750398821978</v>
+        <v>130.69347071713662</v>
       </c>
       <c r="H530" s="2">
-        <v>1007.5146802307059</v>
+        <v>990.65650803589563</v>
       </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
@@ -46717,13 +46741,13 @@
         <v>63</v>
       </c>
       <c r="F531" s="2">
-        <v>44.908726198639343</v>
+        <v>43.918091956562726</v>
       </c>
       <c r="G531" s="2">
-        <v>66.408726198639343</v>
+        <v>65.418091956562733</v>
       </c>
       <c r="H531" s="2">
-        <v>66.408726198639343</v>
+        <v>65.418091956562733</v>
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
@@ -46743,13 +46767,13 @@
         <v>63</v>
       </c>
       <c r="F532" s="2">
-        <v>68.397866426025089</v>
+        <v>67.389694467582459</v>
       </c>
       <c r="G532" s="2">
-        <v>89.897866426025089</v>
+        <v>88.889694467582459</v>
       </c>
       <c r="H532" s="2">
-        <v>89.897866426025089</v>
+        <v>88.889694467582459</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -46769,13 +46793,13 @@
         <v>63</v>
       </c>
       <c r="F533" s="2">
-        <v>116.68096572113306</v>
+        <v>114.5377641126921</v>
       </c>
       <c r="G533" s="2">
-        <v>138.18096572113308</v>
+        <v>136.03776411269212</v>
       </c>
       <c r="H533" s="2">
-        <v>295.70726664322478</v>
+        <v>291.12081520116112</v>
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
@@ -46795,13 +46819,13 @@
         <v>63</v>
       </c>
       <c r="F534" s="2">
-        <v>109.86918295435196</v>
+        <v>107.4396060298041</v>
       </c>
       <c r="G534" s="2">
-        <v>131.36918295435197</v>
+        <v>128.93960602980411</v>
       </c>
       <c r="H534" s="2">
-        <v>202.30854174970204</v>
+        <v>198.56699328589835</v>
       </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
@@ -46821,13 +46845,13 @@
         <v>63</v>
       </c>
       <c r="F535" s="2">
-        <v>88.457620321621476</v>
+        <v>86.894407831226133</v>
       </c>
       <c r="G535" s="2">
-        <v>109.95762032162148</v>
+        <v>108.39440783122613</v>
       </c>
       <c r="H535" s="2">
-        <v>345.26692780989146</v>
+        <v>340.35844059005007</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
@@ -46847,13 +46871,13 @@
         <v>63</v>
       </c>
       <c r="F536" s="2">
-        <v>115.40586541924216</v>
+        <v>113.42478704721677</v>
       </c>
       <c r="G536" s="2">
-        <v>136.90586541924216</v>
+        <v>134.92478704721677</v>
       </c>
       <c r="H536" s="2">
-        <v>473.69429435057788</v>
+        <v>466.83976318337</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
@@ -46873,13 +46897,13 @@
         <v>63</v>
       </c>
       <c r="F537" s="2">
-        <v>95.228801601961592</v>
+        <v>93.212097287675874</v>
       </c>
       <c r="G537" s="2">
-        <v>116.72880160196159</v>
+        <v>114.71209728767587</v>
       </c>
       <c r="H537" s="2">
-        <v>81.710161121373105</v>
+        <v>80.298468101373103</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
@@ -46899,13 +46923,13 @@
         <v>63</v>
       </c>
       <c r="F538" s="2">
-        <v>111.19258900196159</v>
+        <v>108.72995328767587</v>
       </c>
       <c r="G538" s="2">
-        <v>132.69258900196161</v>
+        <v>130.22995328767587</v>
       </c>
       <c r="H538" s="2">
-        <v>92.884812301373117</v>
+        <v>91.160967301373105</v>
       </c>
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
@@ -46925,13 +46949,13 @@
         <v>63</v>
       </c>
       <c r="F539" s="2">
-        <v>102.69031735957793</v>
+        <v>100.4103420349026</v>
       </c>
       <c r="G539" s="2">
-        <v>124.19031735957793</v>
+        <v>121.9103420349026</v>
       </c>
       <c r="H539" s="2">
-        <v>191.25308873375002</v>
+        <v>187.74192673375001</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
@@ -46951,13 +46975,13 @@
         <v>63</v>
       </c>
       <c r="F540" s="2">
-        <v>110.16935828425325</v>
+        <v>107.73346187905845</v>
       </c>
       <c r="G540" s="2">
-        <v>131.66935828425324</v>
+        <v>129.23346187905844</v>
       </c>
       <c r="H540" s="2">
-        <v>304.156217636625</v>
+        <v>298.52929694062499</v>
       </c>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
@@ -46977,13 +47001,13 @@
         <v>63</v>
       </c>
       <c r="F541" s="2">
-        <v>102.99049268425325</v>
+        <v>100.70419787905844</v>
       </c>
       <c r="G541" s="2">
-        <v>124.49049268425325</v>
+        <v>122.20419787905844</v>
       </c>
       <c r="H541" s="2">
-        <v>287.57303810062501</v>
+        <v>282.29169710062502</v>
       </c>
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
@@ -47003,13 +47027,13 @@
         <v>63</v>
       </c>
       <c r="F542" s="2">
-        <v>90.42495472704843</v>
+        <v>88.699844727396069</v>
       </c>
       <c r="G542" s="2">
-        <v>111.92495472704843</v>
+        <v>110.19984472739607</v>
       </c>
       <c r="H542" s="2">
-        <v>184.6761752996299</v>
+        <v>181.82974380020352</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
@@ -47029,13 +47053,13 @@
         <v>63</v>
       </c>
       <c r="F543" s="2">
-        <v>96.855438794469705</v>
+        <v>94.995093339924267</v>
       </c>
       <c r="G543" s="2">
-        <v>118.35543879446971</v>
+        <v>116.49509333992427</v>
       </c>
       <c r="H543" s="2">
-        <v>195.286474010875</v>
+        <v>192.21690401087503</v>
       </c>
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
@@ -47055,13 +47079,13 @@
         <v>63</v>
       </c>
       <c r="F544" s="2">
-        <v>133.01334095024285</v>
+        <v>130.39913250138525</v>
       </c>
       <c r="G544" s="2">
-        <v>154.51334095024285</v>
+        <v>151.89913250138525</v>
       </c>
       <c r="H544" s="2">
-        <v>704.58083473310728</v>
+        <v>692.66004420631668</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
@@ -47081,13 +47105,13 @@
         <v>63</v>
       </c>
       <c r="F545" s="2">
-        <v>105.065280925067</v>
+        <v>102.83808141365708</v>
       </c>
       <c r="G545" s="2">
-        <v>126.565280925067</v>
+        <v>124.33808141365708</v>
       </c>
       <c r="H545" s="2">
-        <v>496.13590122626266</v>
+        <v>487.40527914153574</v>
       </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
@@ -47107,13 +47131,13 @@
         <v>63</v>
       </c>
       <c r="F546" s="2">
-        <v>117.3158719827602</v>
+        <v>114.92198793046829</v>
       </c>
       <c r="G546" s="2">
-        <v>138.8158719827602</v>
+        <v>136.42198793046828</v>
       </c>
       <c r="H546" s="2">
-        <v>1260.4481176034626</v>
+        <v>1238.7116504086518</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
@@ -47133,13 +47157,13 @@
         <v>63</v>
       </c>
       <c r="F547" s="2">
-        <v>91.300749873151162</v>
+        <v>89.557202066212412</v>
       </c>
       <c r="G547" s="2">
-        <v>112.80074987315116</v>
+        <v>111.05720206621241</v>
       </c>
       <c r="H547" s="2">
-        <v>186.12123729069941</v>
+        <v>183.24438340925047</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
@@ -47159,13 +47183,13 @@
         <v>63</v>
       </c>
       <c r="F548" s="2">
-        <v>94.460182969295488</v>
+        <v>92.46300604438315</v>
       </c>
       <c r="G548" s="2">
-        <v>115.96018296929549</v>
+        <v>113.96300604438315</v>
       </c>
       <c r="H548" s="2">
-        <v>178.57868177271504</v>
+        <v>175.50302930835005</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
@@ -47185,13 +47209,13 @@
         <v>63</v>
       </c>
       <c r="F549" s="2">
-        <v>94.141139134469711</v>
+        <v>92.337793679924246</v>
       </c>
       <c r="G549" s="2">
-        <v>115.64113913446971</v>
+        <v>113.83779367992425</v>
       </c>
       <c r="H549" s="2">
-        <v>190.80787957187502</v>
+        <v>187.832359571875</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
@@ -47211,13 +47235,13 @@
         <v>63</v>
       </c>
       <c r="F550" s="2">
-        <v>115.41884921738664</v>
+        <v>113.20911725550663</v>
       </c>
       <c r="G550" s="2">
-        <v>136.91884921738665</v>
+        <v>134.70911725550661</v>
       </c>
       <c r="H550" s="2">
-        <v>1311.6825755025641</v>
+        <v>1290.5133433077533</v>
       </c>
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
@@ -47237,13 +47261,13 @@
         <v>63</v>
       </c>
       <c r="F551" s="2">
-        <v>124.8273627997801</v>
+        <v>122.35815338757068</v>
       </c>
       <c r="G551" s="2">
-        <v>146.3273627997801</v>
+        <v>143.85815338757067</v>
       </c>
       <c r="H551" s="2">
-        <v>1134.0370616982957</v>
+        <v>1114.9006887536727</v>
       </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
@@ -47263,13 +47287,13 @@
         <v>63</v>
       </c>
       <c r="F552" s="2">
-        <v>99.811823526436342</v>
+        <v>97.746626045799943</v>
       </c>
       <c r="G552" s="2">
-        <v>121.31182352643634</v>
+        <v>119.24662604579994</v>
       </c>
       <c r="H552" s="2">
-        <v>386.98471704933195</v>
+        <v>380.39673708610184</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
@@ -47289,13 +47313,13 @@
         <v>63</v>
       </c>
       <c r="F553" s="2">
-        <v>145.47446752234092</v>
+        <v>142.30755821199608</v>
       </c>
       <c r="G553" s="2">
-        <v>166.97446752234092</v>
+        <v>163.80755821199608</v>
       </c>
       <c r="H553" s="2">
-        <v>968.45191162957724</v>
+        <v>950.08383762957726</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
@@ -47315,13 +47339,13 @@
         <v>63</v>
       </c>
       <c r="F554" s="2">
-        <v>85.862830245575722</v>
+        <v>84.367495787976679</v>
       </c>
       <c r="G554" s="2">
-        <v>107.36283024557572</v>
+        <v>105.86749578797668</v>
       </c>
       <c r="H554" s="2">
-        <v>319.94123413181563</v>
+        <v>315.48513744817052</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
@@ -47341,13 +47365,13 @@
         <v>63</v>
       </c>
       <c r="F555" s="2">
-        <v>129.07401542030422</v>
+        <v>126.59446392442034</v>
       </c>
       <c r="G555" s="2">
-        <v>150.57401542030422</v>
+        <v>148.09446392442032</v>
       </c>
       <c r="H555" s="2">
-        <v>1028.4205253206778</v>
+        <v>1011.4851886037908</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
@@ -47367,13 +47391,13 @@
         <v>63</v>
       </c>
       <c r="F556" s="2">
-        <v>590.94000000000005</v>
+        <v>580.49</v>
       </c>
       <c r="G556" s="2">
-        <v>612.44000000000005</v>
+        <v>601.99</v>
       </c>
       <c r="H556" s="2">
-        <v>612.44000000000005</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
@@ -47393,13 +47417,13 @@
         <v>63</v>
       </c>
       <c r="F557" s="2">
-        <v>69.776540100709596</v>
+        <v>68.445225371974971</v>
       </c>
       <c r="G557" s="2">
-        <v>91.276540100709596</v>
+        <v>89.945225371974971</v>
       </c>
       <c r="H557" s="2">
-        <v>162.4722413792631</v>
+        <v>160.10250116211546</v>
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
@@ -47419,13 +47443,13 @@
         <v>63</v>
       </c>
       <c r="F558" s="2">
-        <v>76.628171427238797</v>
+        <v>75.152754985524609</v>
       </c>
       <c r="G558" s="2">
-        <v>98.128171427238797</v>
+        <v>96.652754985524609</v>
       </c>
       <c r="H558" s="2">
-        <v>174.66814514048505</v>
+        <v>172.04190387423381</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
@@ -47445,13 +47469,13 @@
         <v>63</v>
       </c>
       <c r="F559" s="2">
-        <v>73.332663902070237</v>
+        <v>71.92648341541225</v>
       </c>
       <c r="G559" s="2">
-        <v>94.832663902070237</v>
+        <v>93.42648341541225</v>
       </c>
       <c r="H559" s="2">
-        <v>168.80214174568502</v>
+        <v>166.29914047943382</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
@@ -47471,13 +47495,13 @@
         <v>63</v>
       </c>
       <c r="F560" s="2">
-        <v>70.492274640751717</v>
+        <v>69.145891801700415</v>
       </c>
       <c r="G560" s="2">
-        <v>91.992274640751717</v>
+        <v>90.645891801700415</v>
       </c>
       <c r="H560" s="2">
-        <v>163.74624886053806</v>
+        <v>161.34968740702675</v>
       </c>
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
@@ -47497,13 +47521,13 @@
         <v>63</v>
       </c>
       <c r="F561" s="2">
-        <v>113.03047184681124</v>
+        <v>110.64919960871531</v>
       </c>
       <c r="G561" s="2">
-        <v>134.53047184681122</v>
+        <v>132.14919960871532</v>
       </c>
       <c r="H561" s="2">
-        <v>898.66355193669892</v>
+        <v>882.75665338621832</v>
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
@@ -47523,13 +47547,13 @@
         <v>63</v>
       </c>
       <c r="F562" s="2">
-        <v>154.55939727968445</v>
+        <v>151.1709043167215</v>
       </c>
       <c r="G562" s="2">
-        <v>176.05939727968445</v>
+        <v>172.6709043167215</v>
       </c>
       <c r="H562" s="2">
-        <v>686.63164939076933</v>
+        <v>673.41652683521386</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
@@ -47549,13 +47573,13 @@
         <v>63</v>
       </c>
       <c r="F563" s="2">
-        <v>149.66509528538248</v>
+        <v>146.39597554179272</v>
       </c>
       <c r="G563" s="2">
-        <v>171.16509528538248</v>
+        <v>167.89597554179272</v>
       </c>
       <c r="H563" s="2">
-        <v>462.14575727053273</v>
+        <v>453.3191339628404</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
@@ -47575,13 +47599,13 @@
         <v>63</v>
       </c>
       <c r="F564" s="2">
-        <v>139.14973155454729</v>
+        <v>136.36816195571024</v>
       </c>
       <c r="G564" s="2">
-        <v>160.64973155454729</v>
+        <v>157.86816195571024</v>
       </c>
       <c r="H564" s="2">
-        <v>1214.5119705523775</v>
+        <v>1193.4833043851693</v>
       </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
@@ -47601,13 +47625,13 @@
         <v>63</v>
       </c>
       <c r="F565" s="2">
-        <v>73.202355763974197</v>
+        <v>71.79899017874979</v>
       </c>
       <c r="G565" s="2">
-        <v>94.702355763974197</v>
+        <v>93.29899017874979</v>
       </c>
       <c r="H565" s="2">
-        <v>337.14038651974812</v>
+        <v>332.14440503634927</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
@@ -47627,13 +47651,13 @@
         <v>63</v>
       </c>
       <c r="F566" s="2">
-        <v>106.60000000000001</v>
+        <v>104</v>
       </c>
       <c r="G566" s="2">
-        <v>128.10000000000002</v>
+        <v>125.5</v>
       </c>
       <c r="H566" s="2">
-        <v>32.025000000000006</v>
+        <v>31.375</v>
       </c>
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
@@ -47653,13 +47677,13 @@
         <v>63</v>
       </c>
       <c r="F567" s="2">
-        <v>114.27760999327894</v>
+        <v>111.98836687634854</v>
       </c>
       <c r="G567" s="2">
-        <v>135.77760999327893</v>
+        <v>133.48836687634855</v>
       </c>
       <c r="H567" s="2">
-        <v>966.73658315214595</v>
+        <v>950.43717215960169</v>
       </c>
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
@@ -47679,13 +47703,13 @@
         <v>63</v>
       </c>
       <c r="F568" s="2">
-        <v>116.92093629611465</v>
+        <v>114.54262560465243</v>
       </c>
       <c r="G568" s="2">
-        <v>138.42093629611463</v>
+        <v>136.04262560465241</v>
       </c>
       <c r="H568" s="2">
-        <v>1248.5568453909539</v>
+        <v>1227.1044829539646</v>
       </c>
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
@@ -47705,13 +47729,13 @@
         <v>63</v>
       </c>
       <c r="F569" s="2">
-        <v>120.0074577428951</v>
+        <v>118.08168400724387</v>
       </c>
       <c r="G569" s="2">
-        <v>141.5074577428951</v>
+        <v>139.58168400724387</v>
       </c>
       <c r="H569" s="2">
-        <v>566.0298309715804</v>
+        <v>558.32673602897546</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -47731,13 +47755,13 @@
         <v>63</v>
       </c>
       <c r="F570" s="2">
-        <v>57.997389433850131</v>
+        <v>56.68585367571059</v>
       </c>
       <c r="G570" s="2">
-        <v>79.497389433850131</v>
+        <v>78.18585367571059</v>
       </c>
       <c r="H570" s="2">
-        <v>683.67754913111105</v>
+        <v>672.39834161111105</v>
       </c>
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
@@ -47757,13 +47781,13 @@
         <v>63</v>
       </c>
       <c r="F571" s="2">
-        <v>106.06160463403468</v>
+        <v>104.07848022300959</v>
       </c>
       <c r="G571" s="2">
-        <v>127.56160463403468</v>
+        <v>125.57848022300959</v>
       </c>
       <c r="H571" s="2">
-        <v>482.18286551665113</v>
+        <v>474.68665524297631</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
@@ -47783,13 +47807,13 @@
         <v>63</v>
       </c>
       <c r="F572" s="2">
-        <v>607.56500000000005</v>
+        <v>596.76499999999999</v>
       </c>
       <c r="G572" s="2">
-        <v>629.06500000000005</v>
+        <v>618.26499999999999</v>
       </c>
       <c r="H572" s="2">
-        <v>629.06500000000005</v>
+        <v>618.26499999999999</v>
       </c>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
@@ -47809,13 +47833,13 @@
         <v>63</v>
       </c>
       <c r="F573" s="2">
-        <v>52.725989433850131</v>
+        <v>51.537253675710595</v>
       </c>
       <c r="G573" s="2">
-        <v>74.225989433850131</v>
+        <v>73.037253675710588</v>
       </c>
       <c r="H573" s="2">
-        <v>638.34350913111109</v>
+        <v>628.12038161111104</v>
       </c>
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
@@ -47835,13 +47859,13 @@
         <v>63</v>
       </c>
       <c r="F574" s="2">
-        <v>52.028884588888893</v>
+        <v>50.854824722222219</v>
       </c>
       <c r="G574" s="2">
-        <v>73.5288845888889</v>
+        <v>72.354824722222219</v>
       </c>
       <c r="H574" s="2">
-        <v>441.1733075333334</v>
+        <v>434.12894833333331</v>
       </c>
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
@@ -47861,13 +47885,13 @@
         <v>63</v>
       </c>
       <c r="F575" s="2">
-        <v>133.94847596494969</v>
+        <v>131.35739038603171</v>
       </c>
       <c r="G575" s="2">
-        <v>155.44847596494969</v>
+        <v>152.85739038603171</v>
       </c>
       <c r="H575" s="2">
-        <v>999.53370045462646</v>
+        <v>982.87302018218384</v>
       </c>
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
@@ -47887,13 +47911,13 @@
         <v>63</v>
       </c>
       <c r="F576" s="2">
-        <v>135.30788994737</v>
+        <v>132.92139418200321</v>
       </c>
       <c r="G576" s="2">
-        <v>156.80788994737</v>
+        <v>154.42139418200321</v>
       </c>
       <c r="H576" s="2">
-        <v>768.3586607421131</v>
+        <v>756.66483149181579</v>
       </c>
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
@@ -47913,13 +47937,13 @@
         <v>63</v>
       </c>
       <c r="F577" s="2">
-        <v>140.35063347878457</v>
+        <v>139.53021582500901</v>
       </c>
       <c r="G577" s="2">
-        <v>161.85063347878457</v>
+        <v>161.03021582500901</v>
       </c>
       <c r="H577" s="2">
-        <v>32.370126695756916</v>
+        <v>32.206043165001802</v>
       </c>
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
@@ -47939,13 +47963,13 @@
         <v>63</v>
       </c>
       <c r="F578" s="2">
-        <v>130.69814339941954</v>
+        <v>130.08093606310425</v>
       </c>
       <c r="G578" s="2">
-        <v>152.19814339941954</v>
+        <v>151.58093606310425</v>
       </c>
       <c r="H578" s="2">
-        <v>53.269350189796832</v>
+        <v>53.053327622086485</v>
       </c>
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
@@ -47965,13 +47989,13 @@
         <v>63</v>
       </c>
       <c r="F579" s="2">
-        <v>95.795542261079035</v>
+        <v>94.233121521840104</v>
       </c>
       <c r="G579" s="2">
-        <v>117.29554226107904</v>
+        <v>115.7331215218401</v>
       </c>
       <c r="H579" s="2">
-        <v>518.44629679396928</v>
+        <v>511.54039712653326</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
@@ -47991,13 +48015,13 @@
         <v>63</v>
       </c>
       <c r="F580" s="2">
-        <v>92.590087778945744</v>
+        <v>90.634913961550239</v>
       </c>
       <c r="G580" s="2">
-        <v>114.09008777894574</v>
+        <v>112.13491396155024</v>
       </c>
       <c r="H580" s="2">
-        <v>466.6284590158881</v>
+        <v>458.63179810274045</v>
       </c>
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
@@ -48017,13 +48041,13 @@
         <v>63</v>
       </c>
       <c r="F581" s="2">
-        <v>124.9965150292276</v>
+        <v>122.41130460864144</v>
       </c>
       <c r="G581" s="2">
-        <v>146.4965150292276</v>
+        <v>143.91130460864144</v>
       </c>
       <c r="H581" s="2">
-        <v>1303.8189837601255</v>
+        <v>1280.810611016909</v>
       </c>
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
@@ -48043,13 +48067,13 @@
         <v>63</v>
       </c>
       <c r="F582" s="2">
-        <v>82.116861753027962</v>
+        <v>80.307834967437898</v>
       </c>
       <c r="G582" s="2">
-        <v>103.61686175302796</v>
+        <v>101.8078349674379</v>
       </c>
       <c r="H582" s="2">
-        <v>166.82314742237503</v>
+        <v>163.91061429757502</v>
       </c>
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
@@ -48069,13 +48093,13 @@
         <v>63</v>
       </c>
       <c r="F583" s="2">
-        <v>77.688838953027954</v>
+        <v>75.987812647437892</v>
       </c>
       <c r="G583" s="2">
-        <v>99.188838953027954</v>
+        <v>97.487812647437892</v>
       </c>
       <c r="H583" s="2">
-        <v>159.694030714375</v>
+        <v>156.95537836237503</v>
       </c>
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.25">
@@ -48095,13 +48119,13 @@
         <v>63</v>
       </c>
       <c r="F584" s="2">
-        <v>100.60882256127375</v>
+        <v>98.886764909903164</v>
       </c>
       <c r="G584" s="2">
-        <v>122.10882256127375</v>
+        <v>120.38676490990316</v>
       </c>
       <c r="H584" s="2">
-        <v>362.663203006983</v>
+        <v>357.54869178241239</v>
       </c>
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.25">
@@ -48147,13 +48171,13 @@
         <v>63</v>
       </c>
       <c r="F586" s="2">
-        <v>94.354856636139331</v>
+        <v>92.222312394062726</v>
       </c>
       <c r="G586" s="2">
-        <v>115.85485663613933</v>
+        <v>113.72231239406273</v>
       </c>
       <c r="H586" s="2">
-        <v>579.27428318069667</v>
+        <v>568.61156197031369</v>
       </c>
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
@@ -48173,13 +48197,13 @@
         <v>63</v>
       </c>
       <c r="F587" s="2">
-        <v>118.20735731635214</v>
+        <v>116.26397848254005</v>
       </c>
       <c r="G587" s="2">
-        <v>139.70735731635216</v>
+        <v>137.76397848254004</v>
       </c>
       <c r="H587" s="2">
-        <v>377.20986475415083</v>
+        <v>371.96274190285811</v>
       </c>
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
@@ -48199,13 +48223,13 @@
         <v>63</v>
       </c>
       <c r="F588" s="2">
-        <v>106.44894667613457</v>
+        <v>104.37137096796435</v>
       </c>
       <c r="G588" s="2">
-        <v>127.94894667613457</v>
+        <v>125.87137096796435</v>
       </c>
       <c r="H588" s="2">
-        <v>429.90846083181214</v>
+        <v>422.92780645236019</v>
       </c>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
@@ -48225,13 +48249,13 @@
         <v>63</v>
       </c>
       <c r="F589" s="2">
-        <v>118.180692247238</v>
+        <v>116.23344354621427</v>
       </c>
       <c r="G589" s="2">
-        <v>139.680692247238</v>
+        <v>137.73344354621429</v>
       </c>
       <c r="H589" s="2">
-        <v>125.71262302251421</v>
+        <v>123.96009919159286</v>
       </c>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
@@ -48251,13 +48275,13 @@
         <v>63</v>
       </c>
       <c r="F590" s="2">
-        <v>113.03573036100829</v>
+        <v>111.0934056862736</v>
       </c>
       <c r="G590" s="2">
-        <v>134.53573036100829</v>
+        <v>132.5934056862736</v>
       </c>
       <c r="H590" s="2">
-        <v>121.08215732490747</v>
+        <v>119.33406511764625</v>
       </c>
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
@@ -48277,13 +48301,13 @@
         <v>63</v>
       </c>
       <c r="F591" s="2">
-        <v>123.40564934081016</v>
+        <v>121.4650862151323</v>
       </c>
       <c r="G591" s="2">
-        <v>144.90564934081016</v>
+        <v>142.96508621513232</v>
       </c>
       <c r="H591" s="2">
-        <v>130.41508440672914</v>
+        <v>128.66857759361909</v>
       </c>
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.25">
@@ -48303,13 +48327,13 @@
         <v>63</v>
       </c>
       <c r="F592" s="2">
-        <v>111.38459803470967</v>
+        <v>109.58033255364059</v>
       </c>
       <c r="G592" s="2">
-        <v>132.88459803470965</v>
+        <v>131.08033255364057</v>
       </c>
       <c r="H592" s="2">
-        <v>465.09609312148382</v>
+        <v>458.78116393774201</v>
       </c>
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.25">
@@ -48329,13 +48353,13 @@
         <v>63</v>
       </c>
       <c r="F593" s="2">
-        <v>134.19115382895947</v>
+        <v>131.55427751504749</v>
       </c>
       <c r="G593" s="2">
-        <v>155.69115382895947</v>
+        <v>153.05427751504749</v>
       </c>
       <c r="H593" s="2">
-        <v>632.10608454557553</v>
+        <v>621.40036671109283</v>
       </c>
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.25">
@@ -48355,13 +48379,13 @@
         <v>63</v>
       </c>
       <c r="F594" s="2">
-        <v>129.57630176069588</v>
+        <v>129.04237497315864</v>
       </c>
       <c r="G594" s="2">
-        <v>151.07630176069588</v>
+        <v>150.54237497315864</v>
       </c>
       <c r="H594" s="2">
-        <v>181.29156211283507</v>
+        <v>180.65084996779038</v>
       </c>
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.25">
@@ -48381,13 +48405,13 @@
         <v>63</v>
       </c>
       <c r="F595" s="2">
-        <v>129.57630176069588</v>
+        <v>129.04237497315864</v>
       </c>
       <c r="G595" s="2">
-        <v>151.07630176069588</v>
+        <v>150.54237497315864</v>
       </c>
       <c r="H595" s="2">
-        <v>181.29156211283507</v>
+        <v>180.65084996779038</v>
       </c>
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.25">
@@ -48407,13 +48431,13 @@
         <v>63</v>
       </c>
       <c r="F596" s="2">
-        <v>104.32408103864363</v>
+        <v>102.68021813544779</v>
       </c>
       <c r="G596" s="2">
-        <v>125.82408103864363</v>
+        <v>124.18021813544779</v>
       </c>
       <c r="H596" s="2">
-        <v>239.06575397342289</v>
+        <v>235.94241445735079</v>
       </c>
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.25">
@@ -48433,13 +48457,13 @@
         <v>63</v>
       </c>
       <c r="F597" s="2">
-        <v>99.273531453405951</v>
+        <v>97.633080095162526</v>
       </c>
       <c r="G597" s="2">
-        <v>120.77353145340595</v>
+        <v>119.13308009516253</v>
       </c>
       <c r="H597" s="2">
-        <v>229.46970976147131</v>
+        <v>226.35285218080878</v>
       </c>
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.25">
@@ -48459,13 +48483,13 @@
         <v>63</v>
       </c>
       <c r="F598" s="2">
-        <v>109.57160756971577</v>
+        <v>107.9344302418658</v>
       </c>
       <c r="G598" s="2">
-        <v>131.07160756971575</v>
+        <v>129.43443024186581</v>
       </c>
       <c r="H598" s="2">
-        <v>249.03605438245992</v>
+        <v>245.92541745954503</v>
       </c>
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.25">
@@ -48485,13 +48509,13 @@
         <v>63</v>
       </c>
       <c r="F599" s="2">
-        <v>109.03210388421908</v>
+        <v>107.27733259467277</v>
       </c>
       <c r="G599" s="2">
-        <v>130.53210388421908</v>
+        <v>128.77733259467277</v>
       </c>
       <c r="H599" s="2">
-        <v>169.69173504948481</v>
+        <v>167.4105323730746</v>
       </c>
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.25">
@@ -48511,13 +48535,13 @@
         <v>63</v>
       </c>
       <c r="F600" s="2">
-        <v>103.97533712810231</v>
+        <v>102.22410827131637</v>
       </c>
       <c r="G600" s="2">
-        <v>125.47533712810231</v>
+        <v>123.72410827131637</v>
       </c>
       <c r="H600" s="2">
-        <v>163.117938266533</v>
+        <v>160.84134075271129</v>
       </c>
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.25">
@@ -48537,13 +48561,13 @@
         <v>63</v>
       </c>
       <c r="F601" s="2">
-        <v>114.27963041529124</v>
+        <v>112.53154470109079</v>
       </c>
       <c r="G601" s="2">
-        <v>135.77963041529125</v>
+        <v>134.03154470109081</v>
       </c>
       <c r="H601" s="2">
-        <v>176.51351953987864</v>
+        <v>174.24100811141807</v>
       </c>
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.25">
@@ -48563,13 +48587,13 @@
         <v>63</v>
       </c>
       <c r="F602" s="2">
-        <v>138.40088052328932</v>
+        <v>135.52342130773897</v>
       </c>
       <c r="G602" s="2">
-        <v>159.90088052328932</v>
+        <v>157.02342130773897</v>
       </c>
       <c r="H602" s="2">
-        <v>1215.2466919769988</v>
+        <v>1193.3780019388162</v>
       </c>
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.25">
@@ -48589,13 +48613,13 @@
         <v>63</v>
       </c>
       <c r="F603" s="2">
-        <v>129.57630176069588</v>
+        <v>129.04237497315864</v>
       </c>
       <c r="G603" s="2">
-        <v>151.07630176069588</v>
+        <v>150.54237497315864</v>
       </c>
       <c r="H603" s="2">
-        <v>181.29156211283507</v>
+        <v>180.65084996779038</v>
       </c>
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.25">
@@ -48615,13 +48639,13 @@
         <v>63</v>
       </c>
       <c r="F604" s="2">
-        <v>57.347624877636662</v>
+        <v>56.984664877636661</v>
       </c>
       <c r="G604" s="2">
-        <v>78.847624877636662</v>
+        <v>78.484664877636661</v>
       </c>
       <c r="H604" s="2">
-        <v>78.847624877636662</v>
+        <v>78.484664877636661</v>
       </c>
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.25">
@@ -48641,13 +48665,13 @@
         <v>63</v>
       </c>
       <c r="F605" s="2">
-        <v>54.687624877636665</v>
+        <v>54.380664877636661</v>
       </c>
       <c r="G605" s="2">
-        <v>76.187624877636665</v>
+        <v>75.880664877636661</v>
       </c>
       <c r="H605" s="2">
-        <v>76.187624877636665</v>
+        <v>75.880664877636661</v>
       </c>
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.25">
@@ -48667,13 +48691,13 @@
         <v>63</v>
       </c>
       <c r="F606" s="2">
-        <v>58.10762487763666</v>
+        <v>57.72866487763666</v>
       </c>
       <c r="G606" s="2">
-        <v>79.607624877636653</v>
+        <v>79.22866487763666</v>
       </c>
       <c r="H606" s="2">
-        <v>79.607624877636653</v>
+        <v>79.22866487763666</v>
       </c>
     </row>
     <row r="607" spans="1:8" x14ac:dyDescent="0.25">
@@ -48693,13 +48717,13 @@
         <v>63</v>
       </c>
       <c r="F607" s="2">
-        <v>96.968787060945743</v>
+        <v>95.447273303561289</v>
       </c>
       <c r="G607" s="2">
-        <v>118.46878706094574</v>
+        <v>116.94727330356129</v>
       </c>
       <c r="H607" s="2">
-        <v>319.86572506455354</v>
+        <v>315.75763791961549</v>
       </c>
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.25">
@@ -48719,13 +48743,13 @@
         <v>63</v>
       </c>
       <c r="F608" s="2">
-        <v>92.002184299897181</v>
+        <v>90.482314785903228</v>
       </c>
       <c r="G608" s="2">
-        <v>113.50218429989718</v>
+        <v>111.98231478590323</v>
       </c>
       <c r="H608" s="2">
-        <v>306.4558976097224</v>
+        <v>302.35224992193872</v>
       </c>
     </row>
     <row r="609" spans="1:8" x14ac:dyDescent="0.25">
@@ -48745,13 +48769,13 @@
         <v>63</v>
       </c>
       <c r="F609" s="2">
-        <v>102.21631359201788</v>
+        <v>100.70148540997931</v>
       </c>
       <c r="G609" s="2">
-        <v>123.71631359201788</v>
+        <v>122.20148540997931</v>
       </c>
       <c r="H609" s="2">
-        <v>334.03404669844832</v>
+        <v>329.94401060694418</v>
       </c>
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.25">
@@ -48771,13 +48795,13 @@
         <v>63</v>
       </c>
       <c r="F610" s="2">
-        <v>142.25902276108613</v>
+        <v>139.32643704288648</v>
       </c>
       <c r="G610" s="2">
-        <v>163.75902276108613</v>
+        <v>160.82643704288648</v>
       </c>
       <c r="H610" s="2">
-        <v>933.42642973819102</v>
+        <v>916.71069114445299</v>
       </c>
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.25">
@@ -48797,13 +48821,13 @@
         <v>63</v>
       </c>
       <c r="F611" s="2">
-        <v>103.27558582997827</v>
+        <v>101.10911441834854</v>
       </c>
       <c r="G611" s="2">
-        <v>124.77558582997827</v>
+        <v>122.60911441834854</v>
       </c>
       <c r="H611" s="2">
-        <v>530.29623977740766</v>
+        <v>521.0887362779813</v>
       </c>
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.25">
@@ -48823,13 +48847,13 @@
         <v>63</v>
       </c>
       <c r="F612" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
       <c r="G612" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
       <c r="H612" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.25">
@@ -48849,13 +48873,13 @@
         <v>63</v>
       </c>
       <c r="F613" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
       <c r="G613" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
       <c r="H613" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
@@ -48875,13 +48899,13 @@
         <v>63</v>
       </c>
       <c r="F614" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
       <c r="G614" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
       <c r="H614" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.25">
@@ -48901,13 +48925,13 @@
         <v>63</v>
       </c>
       <c r="F615" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
       <c r="G615" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
       <c r="H615" s="2">
-        <v>39.36</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
@@ -48927,13 +48951,13 @@
         <v>63</v>
       </c>
       <c r="F616" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
       <c r="G616" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
       <c r="H616" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
@@ -48953,13 +48977,13 @@
         <v>63</v>
       </c>
       <c r="F617" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
       <c r="G617" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
       <c r="H617" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
@@ -48979,13 +49003,13 @@
         <v>63</v>
       </c>
       <c r="F618" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
       <c r="G618" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
       <c r="H618" s="2">
-        <v>34.44</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
@@ -49031,13 +49055,13 @@
         <v>63</v>
       </c>
       <c r="F620" s="2">
-        <v>65.600000000000009</v>
+        <v>64</v>
       </c>
       <c r="G620" s="2">
-        <v>65.600000000000009</v>
+        <v>64</v>
       </c>
       <c r="H620" s="2">
-        <v>65.600000000000009</v>
+        <v>64</v>
       </c>
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
@@ -49057,13 +49081,13 @@
         <v>63</v>
       </c>
       <c r="F621" s="2">
-        <v>65.600000000000009</v>
+        <v>64</v>
       </c>
       <c r="G621" s="2">
-        <v>65.600000000000009</v>
+        <v>64</v>
       </c>
       <c r="H621" s="2">
-        <v>65.600000000000009</v>
+        <v>64</v>
       </c>
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
@@ -49083,13 +49107,13 @@
         <v>63</v>
       </c>
       <c r="F622" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
       <c r="G622" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
       <c r="H622" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
@@ -49109,13 +49133,13 @@
         <v>63</v>
       </c>
       <c r="F623" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
       <c r="G623" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
       <c r="H623" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
@@ -49135,13 +49159,13 @@
         <v>63</v>
       </c>
       <c r="F624" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
       <c r="G624" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
       <c r="H624" s="2">
-        <v>90.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
@@ -49161,13 +49185,13 @@
         <v>63</v>
       </c>
       <c r="F625" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
       <c r="G625" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
       <c r="H625" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
@@ -49187,13 +49211,13 @@
         <v>63</v>
       </c>
       <c r="F626" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
       <c r="G626" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
       <c r="H626" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
@@ -49213,13 +49237,13 @@
         <v>63</v>
       </c>
       <c r="F627" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
       <c r="G627" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
       <c r="H627" s="2">
-        <v>118.89999999999999</v>
+        <v>116</v>
       </c>
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
@@ -49239,13 +49263,13 @@
         <v>63</v>
       </c>
       <c r="F628" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G628" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H628" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
@@ -49265,13 +49289,13 @@
         <v>63</v>
       </c>
       <c r="F629" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G629" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H629" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
@@ -49291,13 +49315,13 @@
         <v>63</v>
       </c>
       <c r="F630" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G630" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H630" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
@@ -49317,13 +49341,13 @@
         <v>63</v>
       </c>
       <c r="F631" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G631" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H631" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
@@ -49343,13 +49367,13 @@
         <v>63</v>
       </c>
       <c r="F632" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G632" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H632" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
@@ -49369,13 +49393,13 @@
         <v>63</v>
       </c>
       <c r="F633" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
       <c r="G633" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
       <c r="H633" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
@@ -49395,13 +49419,13 @@
         <v>63</v>
       </c>
       <c r="F634" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
       <c r="G634" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
       <c r="H634" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
@@ -49421,13 +49445,13 @@
         <v>63</v>
       </c>
       <c r="F635" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
       <c r="G635" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
       <c r="H635" s="2">
-        <v>36.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
@@ -49447,13 +49471,13 @@
         <v>63</v>
       </c>
       <c r="F636" s="2">
-        <v>108.77799178426326</v>
+        <v>107.03661201747988</v>
       </c>
       <c r="G636" s="2">
-        <v>130.27799178426326</v>
+        <v>128.53661201747988</v>
       </c>
       <c r="H636" s="2">
-        <v>364.77837699593709</v>
+        <v>359.90251364894362</v>
       </c>
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
@@ -49473,13 +49497,13 @@
         <v>63</v>
       </c>
       <c r="F637" s="2">
-        <v>82.116861753027962</v>
+        <v>80.307834967437898</v>
       </c>
       <c r="G637" s="2">
-        <v>103.61686175302796</v>
+        <v>101.8078349674379</v>
       </c>
       <c r="H637" s="2">
-        <v>333.64629484475006</v>
+        <v>327.82122859515005</v>
       </c>
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
@@ -49499,13 +49523,13 @@
         <v>63</v>
       </c>
       <c r="F638" s="2">
-        <v>77.688838953027954</v>
+        <v>75.987812647437892</v>
       </c>
       <c r="G638" s="2">
-        <v>99.188838953027954</v>
+        <v>97.487812647437892</v>
       </c>
       <c r="H638" s="2">
-        <v>319.38806142875001</v>
+        <v>313.91075672475006</v>
       </c>
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
@@ -49525,13 +49549,13 @@
         <v>63</v>
       </c>
       <c r="F639" s="2">
-        <v>127.19513267865764</v>
+        <v>124.36406002760577</v>
       </c>
       <c r="G639" s="2">
-        <v>148.69513267865764</v>
+        <v>145.86406002760577</v>
       </c>
       <c r="H639" s="2">
-        <v>386.62221447777779</v>
+        <v>379.26114247777781</v>
       </c>
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
@@ -49551,13 +49575,13 @@
         <v>63</v>
       </c>
       <c r="F640" s="2">
-        <v>122.83074782898365</v>
+        <v>120.74658535371722</v>
       </c>
       <c r="G640" s="2">
-        <v>144.33074782898365</v>
+        <v>142.24658535371722</v>
       </c>
       <c r="H640" s="2">
-        <v>404.14052699593714</v>
+        <v>398.30466364894357</v>
       </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
@@ -49577,13 +49601,13 @@
         <v>63</v>
       </c>
       <c r="F641" s="2">
-        <v>141.79399452584636</v>
+        <v>138.85534254289811</v>
       </c>
       <c r="G641" s="2">
-        <v>163.29399452584636</v>
+        <v>160.35534254289811</v>
       </c>
       <c r="H641" s="2">
-        <v>587.85838029304693</v>
+        <v>577.2792331544332</v>
       </c>
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
@@ -49603,13 +49627,13 @@
         <v>63</v>
       </c>
       <c r="F642" s="2">
-        <v>116.73290022970087</v>
+        <v>114.18743869123932</v>
       </c>
       <c r="G642" s="2">
-        <v>138.23290022970087</v>
+        <v>135.68743869123932</v>
       </c>
       <c r="H642" s="2">
-        <v>359.40554059722228</v>
+        <v>352.78734059722223</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
@@ -49629,13 +49653,13 @@
         <v>63</v>
       </c>
       <c r="F643" s="2">
-        <v>101.94252346875125</v>
+        <v>99.802788065865784</v>
       </c>
       <c r="G643" s="2">
-        <v>123.44252346875125</v>
+        <v>121.30278806586578</v>
       </c>
       <c r="H643" s="2">
-        <v>488.83239293625496</v>
+        <v>480.3590407408285</v>
       </c>
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
@@ -49655,13 +49679,13 @@
         <v>63</v>
       </c>
       <c r="F644" s="2">
-        <v>109.99388356659723</v>
+        <v>107.57756815934722</v>
       </c>
       <c r="G644" s="2">
-        <v>131.49388356659722</v>
+        <v>129.07756815934721</v>
       </c>
       <c r="H644" s="2">
-        <v>810.00232277023883</v>
+        <v>795.11781986157882</v>
       </c>
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
@@ -49681,13 +49705,13 @@
         <v>63</v>
       </c>
       <c r="F645" s="2">
-        <v>95.07755677522222</v>
+        <v>93.083269300422231</v>
       </c>
       <c r="G645" s="2">
-        <v>116.57755677522222</v>
+        <v>114.58326930042223</v>
       </c>
       <c r="H645" s="2">
-        <v>897.64718716921107</v>
+        <v>882.2911736132512</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -50955,13 +50979,13 @@
         <v>63</v>
       </c>
       <c r="F694" s="2">
-        <v>137.74396021737698</v>
+        <v>136.85189662250045</v>
       </c>
       <c r="G694" s="2">
-        <v>159.24396021737698</v>
+        <v>158.35189662250045</v>
       </c>
       <c r="H694" s="2">
-        <v>140.13468499129175</v>
+        <v>139.34966902780039</v>
       </c>
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
@@ -50981,13 +51005,13 @@
         <v>63</v>
       </c>
       <c r="F695" s="2">
-        <v>146.8733319291259</v>
+        <v>146.19254536306639</v>
       </c>
       <c r="G695" s="2">
-        <v>168.3733319291259</v>
+        <v>167.69254536306639</v>
       </c>
       <c r="H695" s="2">
-        <v>296.33706419526158</v>
+        <v>295.13887983899684</v>
       </c>
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.25">
@@ -51007,13 +51031,13 @@
         <v>63</v>
       </c>
       <c r="F696" s="2">
-        <v>148.56392143390974</v>
+        <v>148.03003913656394</v>
       </c>
       <c r="G696" s="2">
-        <v>170.06392143390974</v>
+        <v>169.53003913656394</v>
       </c>
       <c r="H696" s="2">
-        <v>204.07670572069168</v>
+        <v>203.43604696387672</v>
       </c>
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.25">
@@ -51033,13 +51057,13 @@
         <v>63</v>
       </c>
       <c r="F697" s="2">
-        <v>110.80649142810458</v>
+        <v>108.3730684869281</v>
       </c>
       <c r="G697" s="2">
-        <v>132.30649142810458</v>
+        <v>129.8730684869281</v>
       </c>
       <c r="H697" s="2">
-        <v>231.53635999918302</v>
+        <v>227.27786985212418</v>
       </c>
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.25">
@@ -51059,13 +51083,13 @@
         <v>63</v>
       </c>
       <c r="F698" s="2">
-        <v>95.397491428104573</v>
+        <v>93.3964684869281</v>
       </c>
       <c r="G698" s="2">
-        <v>116.89749142810457</v>
+        <v>114.8964684869281</v>
       </c>
       <c r="H698" s="2">
-        <v>204.57060999918301</v>
+        <v>201.06881985212416</v>
       </c>
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
@@ -51085,13 +51109,13 @@
         <v>63</v>
       </c>
       <c r="F699" s="2">
-        <v>98.04212460185353</v>
+        <v>96.053459442659332</v>
       </c>
       <c r="G699" s="2">
-        <v>119.54212460185353</v>
+        <v>117.55345944265933</v>
       </c>
       <c r="H699" s="2">
-        <v>1028.0622715759403</v>
+        <v>1010.9597512068702</v>
       </c>
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.25">
@@ -51111,13 +51135,13 @@
         <v>63</v>
       </c>
       <c r="F700" s="2">
-        <v>126.67186636919934</v>
+        <v>125.98695410454098</v>
       </c>
       <c r="G700" s="2">
-        <v>148.17186636919934</v>
+        <v>147.48695410454098</v>
       </c>
       <c r="H700" s="2">
-        <v>260.78396652845453</v>
+        <v>259.57851409353322</v>
       </c>
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.25">
@@ -51137,13 +51161,13 @@
         <v>63</v>
       </c>
       <c r="F701" s="2">
-        <v>125.033289812864</v>
+        <v>122.88427685771845</v>
       </c>
       <c r="G701" s="2">
-        <v>146.53328981286398</v>
+        <v>144.38427685771845</v>
       </c>
       <c r="H701" s="2">
-        <v>278.42790397342281</v>
+        <v>274.34456445735083</v>
       </c>
     </row>
     <row r="702" spans="1:8" x14ac:dyDescent="0.25">
@@ -51163,13 +51187,13 @@
         <v>63</v>
       </c>
       <c r="F702" s="2">
-        <v>103.57800263091184</v>
+        <v>101.95172653145404</v>
       </c>
       <c r="G702" s="2">
-        <v>125.07800263091184</v>
+        <v>123.45172653145404</v>
       </c>
       <c r="H702" s="2">
-        <v>450.28080947128262</v>
+        <v>444.42621551323458</v>
       </c>
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.25">
@@ -51189,13 +51213,13 @@
         <v>63</v>
       </c>
       <c r="F703" s="2">
-        <v>116.38160464444393</v>
+        <v>113.80948683650897</v>
       </c>
       <c r="G703" s="2">
-        <v>137.88160464444394</v>
+        <v>135.30948683650897</v>
       </c>
       <c r="H703" s="2">
-        <v>849.3644727702391</v>
+        <v>833.51996986157883</v>
       </c>
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.25">
@@ -51215,13 +51239,13 @@
         <v>63</v>
       </c>
       <c r="F704" s="2">
-        <v>192.03974108204829</v>
+        <v>190.45788974673849</v>
       </c>
       <c r="G704" s="2">
-        <v>213.53974108204829</v>
+        <v>211.95788974673849</v>
       </c>
       <c r="H704" s="2">
-        <v>811.49372405999986</v>
+        <v>805.48237261555551</v>
       </c>
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
@@ -51241,13 +51265,13 @@
         <v>63</v>
       </c>
       <c r="F705" s="2">
-        <v>147.17042647920516</v>
+        <v>145.2476952147525</v>
       </c>
       <c r="G705" s="2">
-        <v>168.67042647920516</v>
+        <v>166.7476952147525</v>
       </c>
       <c r="H705" s="2">
-        <v>755.69411175478285</v>
+        <v>747.07969887065553</v>
       </c>
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.25">
@@ -51267,13 +51291,13 @@
         <v>63</v>
       </c>
       <c r="F706" s="2">
-        <v>70.304155535277829</v>
+        <v>69.532995144803422</v>
       </c>
       <c r="G706" s="2">
-        <v>91.804155535277829</v>
+        <v>91.032995144803422</v>
       </c>
       <c r="H706" s="2">
-        <v>475.54552567273913</v>
+        <v>471.55091485008171</v>
       </c>
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.25">
@@ -51293,13 +51317,13 @@
         <v>63</v>
       </c>
       <c r="F707" s="2">
-        <v>516.70589403142174</v>
+        <v>513.57555731178172</v>
       </c>
       <c r="G707" s="2">
-        <v>538.20589403142174</v>
+        <v>535.07555731178172</v>
       </c>
       <c r="H707" s="2">
-        <v>538.47499697843739</v>
+        <v>535.3430950904376</v>
       </c>
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.25">
@@ -51319,13 +51343,13 @@
         <v>63</v>
       </c>
       <c r="F708" s="2">
-        <v>507.21064165760868</v>
+        <v>504.08030493796855</v>
       </c>
       <c r="G708" s="2">
-        <v>528.71064165760868</v>
+        <v>525.58030493796855</v>
       </c>
       <c r="H708" s="2">
-        <v>528.9749969784375</v>
+        <v>525.84309509043749</v>
       </c>
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.25">
@@ -51345,13 +51369,13 @@
         <v>63</v>
       </c>
       <c r="F709" s="2">
-        <v>127.21129316641986</v>
+        <v>126.4600517576893</v>
       </c>
       <c r="G709" s="2">
-        <v>148.71129316641986</v>
+        <v>147.96005175768931</v>
       </c>
       <c r="H709" s="2">
-        <v>196.29890697967423</v>
+        <v>195.30726832014992</v>
       </c>
     </row>
     <row r="710" spans="1:8" x14ac:dyDescent="0.25">
@@ -52515,13 +52539,13 @@
         <v>63</v>
       </c>
       <c r="F754" s="2">
-        <v>147.3594867789744</v>
+        <v>144.42345628542154</v>
       </c>
       <c r="G754" s="2">
-        <v>168.8594867789744</v>
+        <v>165.92345628542154</v>
       </c>
       <c r="H754" s="2">
-        <v>530.21878848597964</v>
+        <v>520.99965273622365</v>
       </c>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
@@ -52541,13 +52565,13 @@
         <v>63</v>
       </c>
       <c r="F755" s="2">
-        <v>140.9623488289931</v>
+        <v>138.35430416785073</v>
       </c>
       <c r="G755" s="2">
-        <v>162.4623488289931</v>
+        <v>159.85430416785073</v>
       </c>
       <c r="H755" s="2">
-        <v>644.97552485110259</v>
+        <v>634.62158754636744</v>
       </c>
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
@@ -52567,13 +52591,13 @@
         <v>63</v>
       </c>
       <c r="F756" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="G756" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="H756" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
@@ -52593,13 +52617,13 @@
         <v>63</v>
       </c>
       <c r="F757" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="G757" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="H757" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -52619,13 +52643,13 @@
         <v>63</v>
       </c>
       <c r="F758" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="G758" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="H758" s="2">
-        <v>79.539999999999992</v>
+        <v>77.599999999999994</v>
       </c>
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
@@ -52645,13 +52669,13 @@
         <v>63</v>
       </c>
       <c r="F759" s="2">
-        <v>100.22109738123299</v>
+        <v>98.417585486978965</v>
       </c>
       <c r="G759" s="2">
-        <v>121.72109738123299</v>
+        <v>119.91758548697896</v>
       </c>
       <c r="H759" s="2">
-        <v>310.38879832214411</v>
+        <v>305.78984299179632</v>
       </c>
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
@@ -52671,13 +52695,13 @@
         <v>63</v>
       </c>
       <c r="F760" s="2">
-        <v>117.41150705649785</v>
+        <v>115.10754126287202</v>
       </c>
       <c r="G760" s="2">
-        <v>138.91150705649784</v>
+        <v>136.60754126287202</v>
       </c>
       <c r="H760" s="2">
-        <v>1300.2117060488197</v>
+        <v>1278.646586220482</v>
       </c>
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
@@ -52697,13 +52721,13 @@
         <v>63</v>
       </c>
       <c r="F761" s="2">
-        <v>90.326943939712464</v>
+        <v>88.457138689384678</v>
       </c>
       <c r="G761" s="2">
-        <v>111.82694393971246</v>
+        <v>109.95713868938468</v>
       </c>
       <c r="H761" s="2">
-        <v>1060.1194285484742</v>
+        <v>1042.3936747753669</v>
       </c>
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
@@ -52723,13 +52747,13 @@
         <v>63</v>
       </c>
       <c r="F762" s="2">
-        <v>93.640196760759068</v>
+        <v>91.847469033660161</v>
       </c>
       <c r="G762" s="2">
-        <v>115.14019676075907</v>
+        <v>113.34746903366016</v>
       </c>
       <c r="H762" s="2">
-        <v>379.9626493105049</v>
+        <v>374.04664781107851</v>
       </c>
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
@@ -52749,13 +52773,13 @@
         <v>63</v>
       </c>
       <c r="F763" s="2">
-        <v>76.410939792169998</v>
+        <v>74.982672272957245</v>
       </c>
       <c r="G763" s="2">
-        <v>97.910939792169998</v>
+        <v>96.482672272957245</v>
       </c>
       <c r="H763" s="2">
-        <v>264.35953743885904</v>
+        <v>260.50321513698458</v>
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
@@ -52775,13 +52799,13 @@
         <v>63</v>
       </c>
       <c r="F764" s="2">
-        <v>107.29796876127612</v>
+        <v>104.98566862096723</v>
       </c>
       <c r="G764" s="2">
-        <v>128.79796876127614</v>
+        <v>126.48566862096723</v>
       </c>
       <c r="H764" s="2">
-        <v>911.88961882983506</v>
+        <v>895.518533836448</v>
       </c>
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.25">
@@ -52801,13 +52825,13 @@
         <v>63</v>
       </c>
       <c r="F765" s="2">
-        <v>51.420269745165619</v>
+        <v>50.349116747796444</v>
       </c>
       <c r="G765" s="2">
-        <v>72.920269745165626</v>
+        <v>71.849116747796444</v>
       </c>
       <c r="H765" s="2">
-        <v>772.95485929875565</v>
+        <v>761.60063752664223</v>
       </c>
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
@@ -52827,13 +52851,13 @@
         <v>63</v>
       </c>
       <c r="F766" s="2">
-        <v>129.56</v>
+        <v>126.4</v>
       </c>
       <c r="G766" s="2">
-        <v>151.06</v>
+        <v>147.9</v>
       </c>
       <c r="H766" s="2">
-        <v>151.06</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
@@ -52853,13 +52877,13 @@
         <v>63</v>
       </c>
       <c r="F767" s="2">
-        <v>237.79999999999998</v>
+        <v>232</v>
       </c>
       <c r="G767" s="2">
-        <v>259.29999999999995</v>
+        <v>253.5</v>
       </c>
       <c r="H767" s="2">
-        <v>259.29999999999995</v>
+        <v>253.5</v>
       </c>
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.25">
@@ -52983,13 +53007,13 @@
         <v>63</v>
       </c>
       <c r="F772" s="2">
-        <v>135.46218250809548</v>
+        <v>132.62659459265606</v>
       </c>
       <c r="G772" s="2">
-        <v>156.96218250809548</v>
+        <v>154.12659459265606</v>
       </c>
       <c r="H772" s="2">
-        <v>1196.0518307116877</v>
+        <v>1174.4446507960392</v>
       </c>
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.25">
@@ -53009,13 +53033,13 @@
         <v>63</v>
       </c>
       <c r="F773" s="2">
-        <v>124.40554064116733</v>
+        <v>123.72062448496203</v>
       </c>
       <c r="G773" s="2">
-        <v>145.90554064116733</v>
+        <v>145.22062448496203</v>
       </c>
       <c r="H773" s="2">
-        <v>256.79375152845449</v>
+        <v>255.58829909353318</v>
       </c>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
@@ -53035,13 +53059,13 @@
         <v>63</v>
       </c>
       <c r="F774" s="2">
-        <v>104.21006615982073</v>
+        <v>102.00774331749044</v>
       </c>
       <c r="G774" s="2">
-        <v>125.71006615982073</v>
+        <v>123.50774331749044</v>
       </c>
       <c r="H774" s="2">
-        <v>406.04351369622094</v>
+        <v>398.93001091549411</v>
       </c>
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.25">
@@ -53061,13 +53085,13 @@
         <v>63</v>
       </c>
       <c r="F775" s="2">
-        <v>102.156844637926</v>
+        <v>100.03158831738513</v>
       </c>
       <c r="G775" s="2">
-        <v>123.656844637926</v>
+        <v>121.53158831738513</v>
       </c>
       <c r="H775" s="2">
-        <v>304.19583780929793</v>
+        <v>298.96770726076744</v>
       </c>
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.25">
@@ -53087,13 +53111,13 @@
         <v>63</v>
       </c>
       <c r="F776" s="2">
-        <v>129.50012697843749</v>
+        <v>126.4064170904375</v>
       </c>
       <c r="G776" s="2">
-        <v>135.50012697843749</v>
+        <v>132.40641709043751</v>
       </c>
       <c r="H776" s="2">
-        <v>135.50012697843749</v>
+        <v>132.40641709043751</v>
       </c>
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.25">
@@ -53399,13 +53423,13 @@
         <v>63</v>
       </c>
       <c r="F788" s="2">
-        <v>133.27293332758714</v>
+        <v>130.23636468332043</v>
       </c>
       <c r="G788" s="2">
-        <v>139.27293332758714</v>
+        <v>136.23636468332043</v>
       </c>
       <c r="H788" s="2">
-        <v>417.81879998276145</v>
+        <v>408.70909404996132</v>
       </c>
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
@@ -53425,13 +53449,13 @@
         <v>63</v>
       </c>
       <c r="F789" s="2">
-        <v>129.80776970935349</v>
+        <v>126.77308773175351</v>
       </c>
       <c r="G789" s="2">
-        <v>135.80776970935349</v>
+        <v>132.77308773175349</v>
       </c>
       <c r="H789" s="2">
-        <v>679.03884854676744</v>
+        <v>663.86543865876752</v>
       </c>
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
@@ -53685,13 +53709,13 @@
         <v>63</v>
       </c>
       <c r="F799" s="2">
-        <v>114.8</v>
+        <v>112</v>
       </c>
       <c r="G799" s="2">
-        <v>114.8</v>
+        <v>112</v>
       </c>
       <c r="H799" s="2">
-        <v>86.1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
@@ -53711,13 +53735,13 @@
         <v>63</v>
       </c>
       <c r="F800" s="2">
-        <v>114.8</v>
+        <v>112</v>
       </c>
       <c r="G800" s="2">
-        <v>114.8</v>
+        <v>112</v>
       </c>
       <c r="H800" s="2">
-        <v>86.1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
@@ -53737,13 +53761,13 @@
         <v>63</v>
       </c>
       <c r="F801" s="2">
-        <v>114.8</v>
+        <v>112</v>
       </c>
       <c r="G801" s="2">
-        <v>114.8</v>
+        <v>112</v>
       </c>
       <c r="H801" s="2">
-        <v>86.1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
@@ -53763,13 +53787,13 @@
         <v>63</v>
       </c>
       <c r="F802" s="2">
-        <v>102.24673288641776</v>
+        <v>101.99725006354581</v>
       </c>
       <c r="G802" s="2">
-        <v>123.74673288641776</v>
+        <v>123.49725006354581</v>
       </c>
       <c r="H802" s="2">
-        <v>123.74673288641776</v>
+        <v>123.49725006354581</v>
       </c>
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
@@ -53789,13 +53813,13 @@
         <v>63</v>
       </c>
       <c r="F803" s="2">
-        <v>95.219492684253254</v>
+        <v>93.204797879058447</v>
       </c>
       <c r="G803" s="2">
-        <v>116.71949268425325</v>
+        <v>114.70479787905845</v>
       </c>
       <c r="H803" s="2">
-        <v>269.62202810062502</v>
+        <v>264.96808310062499</v>
       </c>
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
@@ -53815,13 +53839,13 @@
         <v>63</v>
       </c>
       <c r="F804" s="2">
-        <v>102.33288044871796</v>
+        <v>100.07791429487179</v>
       </c>
       <c r="G804" s="2">
-        <v>123.83288044871796</v>
+        <v>121.57791429487179</v>
       </c>
       <c r="H804" s="2">
-        <v>241.47411687500002</v>
+        <v>237.07693287499998</v>
       </c>
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
@@ -53841,13 +53865,13 @@
         <v>63</v>
       </c>
       <c r="F805" s="2">
-        <v>111.44159649572651</v>
+        <v>108.99503034188035</v>
       </c>
       <c r="G805" s="2">
-        <v>132.94159649572651</v>
+        <v>130.49503034188035</v>
       </c>
       <c r="H805" s="2">
-        <v>259.23611316666671</v>
+        <v>254.46530916666669</v>
       </c>
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
@@ -53867,13 +53891,13 @@
         <v>63</v>
       </c>
       <c r="F806" s="2">
-        <v>109.53595451923078</v>
+        <v>107.12958836538462</v>
       </c>
       <c r="G806" s="2">
-        <v>131.03595451923078</v>
+        <v>128.62958836538462</v>
       </c>
       <c r="H806" s="2">
-        <v>340.69348175000005</v>
+        <v>334.43692975000005</v>
       </c>
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
@@ -53893,13 +53917,13 @@
         <v>63</v>
       </c>
       <c r="F807" s="2">
-        <v>101.89795451923078</v>
+        <v>99.65238836538461</v>
       </c>
       <c r="G807" s="2">
-        <v>123.39795451923078</v>
+        <v>121.15238836538461</v>
       </c>
       <c r="H807" s="2">
-        <v>320.83468175000002</v>
+        <v>314.99620974999999</v>
       </c>
     </row>
     <row r="808" spans="1:8" x14ac:dyDescent="0.25">
@@ -53919,13 +53943,13 @@
         <v>63</v>
       </c>
       <c r="F808" s="2">
-        <v>104.6538367854001</v>
+        <v>103.02975675195745</v>
       </c>
       <c r="G808" s="2">
-        <v>126.1538367854001</v>
+        <v>124.52975675195745</v>
       </c>
       <c r="H808" s="2">
-        <v>201.84613885664018</v>
+        <v>199.24761080313192</v>
       </c>
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.25">
@@ -53945,13 +53969,13 @@
         <v>63</v>
       </c>
       <c r="F809" s="2">
-        <v>110.05265175211817</v>
+        <v>108.4348277193762</v>
       </c>
       <c r="G809" s="2">
-        <v>131.55265175211815</v>
+        <v>129.93482771937619</v>
       </c>
       <c r="H809" s="2">
-        <v>210.48424280338907</v>
+        <v>207.89572435100192</v>
       </c>
     </row>
     <row r="810" spans="1:8" x14ac:dyDescent="0.25">
@@ -53971,13 +53995,13 @@
         <v>63</v>
       </c>
       <c r="F810" s="2">
-        <v>99.174598382832031</v>
+        <v>97.548178631548694</v>
       </c>
       <c r="G810" s="2">
-        <v>120.67459838283203</v>
+        <v>119.04817863154869</v>
       </c>
       <c r="H810" s="2">
-        <v>193.07935741253127</v>
+        <v>190.47708581047792</v>
       </c>
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
@@ -53997,13 +54021,13 @@
         <v>63</v>
       </c>
       <c r="F811" s="2">
-        <v>118.67061559975396</v>
+        <v>116.86812775995539</v>
       </c>
       <c r="G811" s="2">
-        <v>140.17061559975394</v>
+        <v>138.36812775995537</v>
       </c>
       <c r="H811" s="2">
-        <v>165.40132640770963</v>
+        <v>163.27439075674732</v>
       </c>
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
@@ -54023,13 +54047,13 @@
         <v>63</v>
       </c>
       <c r="F812" s="2">
-        <v>114.90657376862912</v>
+        <v>113.1027274874519</v>
       </c>
       <c r="G812" s="2">
-        <v>136.40657376862913</v>
+        <v>134.60272748745189</v>
       </c>
       <c r="H812" s="2">
-        <v>160.95975704698236</v>
+        <v>158.83121843519322</v>
       </c>
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
@@ -54049,13 +54073,13 @@
         <v>63</v>
       </c>
       <c r="F813" s="2">
-        <v>116.0269959524073</v>
+        <v>115.40147095131579</v>
       </c>
       <c r="G813" s="2">
-        <v>137.5269959524073</v>
+        <v>136.90147095131579</v>
       </c>
       <c r="H813" s="2">
-        <v>618.87148178583288</v>
+        <v>616.05661928092104</v>
       </c>
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
@@ -54075,13 +54099,13 @@
         <v>63</v>
       </c>
       <c r="F814" s="2">
-        <v>110.99076817482701</v>
+        <v>109.97009903563038</v>
       </c>
       <c r="G814" s="2">
-        <v>132.490768174827</v>
+        <v>131.47009903563037</v>
       </c>
       <c r="H814" s="2">
-        <v>596.20845678672151</v>
+        <v>591.61544566033672</v>
       </c>
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
@@ -54101,13 +54125,13 @@
         <v>63</v>
       </c>
       <c r="F815" s="2">
-        <v>116.05485945549373</v>
+        <v>115.42933445440221</v>
       </c>
       <c r="G815" s="2">
-        <v>137.55485945549373</v>
+        <v>136.92933445440221</v>
       </c>
       <c r="H815" s="2">
-        <v>618.99686754972174</v>
+        <v>616.1820050448099</v>
       </c>
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
@@ -54127,13 +54151,13 @@
         <v>63</v>
       </c>
       <c r="F816" s="2">
-        <v>126.4076714166423</v>
+        <v>125.6837119271037</v>
       </c>
       <c r="G816" s="2">
-        <v>147.9076714166423</v>
+        <v>147.1837119271037</v>
       </c>
       <c r="H816" s="2">
-        <v>118.32613713331385</v>
+        <v>117.74696954168297</v>
       </c>
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
@@ -54153,13 +54177,13 @@
         <v>63</v>
       </c>
       <c r="F817" s="2">
-        <v>126.83517141664231</v>
+        <v>129.38325192710371</v>
       </c>
       <c r="G817" s="2">
-        <v>148.33517141664231</v>
+        <v>150.88325192710371</v>
       </c>
       <c r="H817" s="2">
-        <v>118.66813713331385</v>
+        <v>120.70660154168297</v>
       </c>
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
@@ -54179,13 +54203,13 @@
         <v>63</v>
       </c>
       <c r="F818" s="2">
-        <v>126.4076714166423</v>
+        <v>125.6837119271037</v>
       </c>
       <c r="G818" s="2">
-        <v>147.9076714166423</v>
+        <v>147.1837119271037</v>
       </c>
       <c r="H818" s="2">
-        <v>118.32613713331385</v>
+        <v>117.74696954168297</v>
       </c>
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
@@ -54205,13 +54229,13 @@
         <v>63</v>
       </c>
       <c r="F819" s="2">
-        <v>94.788731270655276</v>
+        <v>92.8006651168091</v>
       </c>
       <c r="G819" s="2">
-        <v>116.28873127065528</v>
+        <v>114.3006651168091</v>
       </c>
       <c r="H819" s="2">
-        <v>226.76302597777777</v>
+        <v>222.88629697777773</v>
       </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
@@ -54231,13 +54255,13 @@
         <v>63</v>
       </c>
       <c r="F820" s="2">
-        <v>149.89270782318187</v>
+        <v>150.02610234654992</v>
       </c>
       <c r="G820" s="2">
-        <v>171.39270782318187</v>
+        <v>171.52610234654992</v>
       </c>
       <c r="H820" s="2">
-        <v>771.26718520431837</v>
+        <v>771.86746055947469</v>
       </c>
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
@@ -54245,7 +54269,7 @@
         <v>1714</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="C821" s="2">
         <v>1.3</v>
@@ -54257,13 +54281,13 @@
         <v>63</v>
       </c>
       <c r="F821" s="2">
-        <v>110.37210246688943</v>
+        <v>100.9027614875</v>
       </c>
       <c r="G821" s="2">
-        <v>131.87210246688943</v>
+        <v>122.4027614875</v>
       </c>
       <c r="H821" s="2">
-        <v>171.43373320695628</v>
+        <v>159.12358993375</v>
       </c>
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
@@ -54271,7 +54295,7 @@
         <v>1716</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="C822" s="2">
         <v>1.3</v>
@@ -54283,13 +54307,13 @@
         <v>63</v>
       </c>
       <c r="F822" s="2">
-        <v>103.19323687211541</v>
+        <v>92.968793548422852</v>
       </c>
       <c r="G822" s="2">
-        <v>124.69323687211541</v>
+        <v>114.46879354842285</v>
       </c>
       <c r="H822" s="2">
-        <v>162.10120793375003</v>
+        <v>148.80943161294971</v>
       </c>
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
@@ -54297,7 +54321,7 @@
         <v>1718</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="C823" s="2">
         <v>1.3</v>
@@ -54309,13 +54333,13 @@
         <v>63</v>
       </c>
       <c r="F823" s="2">
-        <v>94.976470533275261</v>
+        <v>107.9320254824015</v>
       </c>
       <c r="G823" s="2">
-        <v>116.47647053327526</v>
+        <v>129.43202548240151</v>
       </c>
       <c r="H823" s="2">
-        <v>151.41941169325784</v>
+        <v>168.26163312712197</v>
       </c>
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
@@ -54335,13 +54359,13 @@
         <v>63</v>
       </c>
       <c r="F824" s="2">
-        <v>71.224981499054522</v>
+        <v>69.877579822886233</v>
       </c>
       <c r="G824" s="2">
-        <v>92.724981499054522</v>
+        <v>91.377579822886233</v>
       </c>
       <c r="H824" s="2">
-        <v>152.99621947343996</v>
+        <v>150.77300670776228</v>
       </c>
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
@@ -54361,13 +54385,13 @@
         <v>63</v>
       </c>
       <c r="F825" s="2">
-        <v>78.122404960415182</v>
+        <v>76.629937526323502</v>
       </c>
       <c r="G825" s="2">
-        <v>99.622404960415182</v>
+        <v>98.129937526323502</v>
       </c>
       <c r="H825" s="2">
-        <v>164.37696818468504</v>
+        <v>161.91439691843377</v>
       </c>
     </row>
     <row r="826" spans="1:8" x14ac:dyDescent="0.25">
@@ -54387,13 +54411,13 @@
         <v>63</v>
       </c>
       <c r="F826" s="2">
-        <v>71.940716039096642</v>
+        <v>70.578246252611663</v>
       </c>
       <c r="G826" s="2">
-        <v>93.440716039096642</v>
+        <v>92.078246252611663</v>
       </c>
       <c r="H826" s="2">
-        <v>154.17718146450946</v>
+        <v>151.92910631680923</v>
       </c>
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
@@ -54413,13 +54437,13 @@
         <v>63</v>
       </c>
       <c r="F827" s="2">
-        <v>119.01527154603177</v>
+        <v>116.41050497881369</v>
       </c>
       <c r="G827" s="2">
-        <v>140.51527154603178</v>
+        <v>137.91050497881369</v>
       </c>
       <c r="H827" s="2">
-        <v>442.62310537000013</v>
+        <v>434.41809068326313</v>
       </c>
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
@@ -54439,13 +54463,13 @@
         <v>63</v>
       </c>
       <c r="F828" s="2">
-        <v>119.20860170945627</v>
+        <v>116.5997457773622</v>
       </c>
       <c r="G828" s="2">
-        <v>140.70860170945627</v>
+        <v>138.09974577736222</v>
       </c>
       <c r="H828" s="2">
-        <v>330.66521401722224</v>
+        <v>324.5344025768012</v>
       </c>
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
@@ -54465,13 +54489,13 @@
         <v>63</v>
       </c>
       <c r="F829" s="2">
-        <v>119.36066147575758</v>
+        <v>116.74859611614033</v>
       </c>
       <c r="G829" s="2">
-        <v>140.86066147575758</v>
+        <v>138.24859611614033</v>
       </c>
       <c r="H829" s="2">
-        <v>232.42009143499999</v>
+        <v>228.11018359163154</v>
       </c>
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
@@ -54491,13 +54515,13 @@
         <v>63</v>
       </c>
       <c r="F830" s="2">
-        <v>125.3270661965812</v>
+        <v>122.58876289987789</v>
       </c>
       <c r="G830" s="2">
-        <v>146.8270661965812</v>
+        <v>144.08876289987791</v>
       </c>
       <c r="H830" s="2">
-        <v>462.50525851923078</v>
+        <v>453.87960313461537</v>
       </c>
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
@@ -54517,13 +54541,13 @@
         <v>63</v>
       </c>
       <c r="F831" s="2">
-        <v>126.45942578605201</v>
+        <v>123.69726408392434</v>
       </c>
       <c r="G831" s="2">
-        <v>147.95942578605201</v>
+        <v>145.19726408392432</v>
       </c>
       <c r="H831" s="2">
-        <v>347.70465059722221</v>
+        <v>341.2135705972222</v>
       </c>
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
@@ -54543,13 +54567,13 @@
         <v>63</v>
       </c>
       <c r="F832" s="2">
-        <v>123.68489090909091</v>
+        <v>120.98055636363637</v>
       </c>
       <c r="G832" s="2">
-        <v>145.18489090909091</v>
+        <v>142.48055636363637</v>
       </c>
       <c r="H832" s="2">
-        <v>239.55507</v>
+        <v>235.092918</v>
       </c>
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
@@ -54569,13 +54593,13 @@
         <v>63</v>
       </c>
       <c r="F833" s="2">
-        <v>110.63558160966133</v>
+        <v>108.20583474261133</v>
       </c>
       <c r="G833" s="2">
-        <v>132.13558160966133</v>
+        <v>129.70583474261133</v>
       </c>
       <c r="H833" s="2">
-        <v>687.10502437023899</v>
+        <v>674.47034066157892</v>
       </c>
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
@@ -54595,13 +54619,13 @@
         <v>63</v>
       </c>
       <c r="F834" s="2">
-        <v>95.810209872186334</v>
+        <v>93.800576094346326</v>
       </c>
       <c r="G834" s="2">
-        <v>117.31020987218633</v>
+        <v>115.30057609434633</v>
       </c>
       <c r="H834" s="2">
-        <v>762.51636416921122</v>
+        <v>749.45374461325116</v>
       </c>
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
@@ -54621,13 +54645,13 @@
         <v>63</v>
       </c>
       <c r="F835" s="2">
-        <v>127.22460625928547</v>
+        <v>124.57346455467452</v>
       </c>
       <c r="G835" s="2">
-        <v>148.72460625928545</v>
+        <v>146.0734645546745</v>
       </c>
       <c r="H835" s="2">
-        <v>1188.3096040116907</v>
+        <v>1167.1269817918494</v>
       </c>
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
@@ -54647,13 +54671,13 @@
         <v>63</v>
       </c>
       <c r="F836" s="2">
-        <v>133.21143458056127</v>
+        <v>132.31936084859842</v>
       </c>
       <c r="G836" s="2">
-        <v>154.71143458056127</v>
+        <v>153.81936084859842</v>
       </c>
       <c r="H836" s="2">
-        <v>61.884573832224511</v>
+        <v>61.527744339439373</v>
       </c>
     </row>
     <row r="837" spans="1:8" x14ac:dyDescent="0.25">
@@ -54673,13 +54697,13 @@
         <v>63</v>
       </c>
       <c r="F837" s="2">
-        <v>133.83973003510673</v>
+        <v>132.9344290304166</v>
       </c>
       <c r="G837" s="2">
-        <v>155.33973003510673</v>
+        <v>154.4344290304166</v>
       </c>
       <c r="H837" s="2">
-        <v>62.135892014042696</v>
+        <v>61.773771612166641</v>
       </c>
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
@@ -54699,26 +54723,118 @@
         <v>63</v>
       </c>
       <c r="F838" s="2">
-        <v>128.89325276237946</v>
+        <v>128.0920881213257</v>
       </c>
       <c r="G838" s="2">
-        <v>150.39325276237946</v>
+        <v>149.5920881213257</v>
       </c>
       <c r="H838" s="2">
-        <v>60.157301104951785</v>
+        <v>59.836835248530285</v>
       </c>
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D839" s="2"/>
+      <c r="A839" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B839" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C839" s="2">
+        <v>0.80010000000000003</v>
+      </c>
+      <c r="D839" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E839" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F839" s="2">
+        <v>137.61267478107274</v>
+      </c>
+      <c r="G839" s="2">
+        <v>159.11267478107274</v>
+      </c>
+      <c r="H839" s="2">
+        <v>127.3060510923363</v>
+      </c>
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D840" s="2"/>
+      <c r="A840" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B840" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C840" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="D840" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E840" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F840" s="2">
+        <v>153.30714234654994</v>
+      </c>
+      <c r="G840" s="2">
+        <v>174.80714234654994</v>
+      </c>
+      <c r="H840" s="2">
+        <v>786.63214055947469</v>
+      </c>
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D841" s="2"/>
+      <c r="A841" s="2" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B841" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C841" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="D841" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E841" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F841" s="2">
+        <v>72.718010544256231</v>
+      </c>
+      <c r="G841" s="2">
+        <v>94.218010544256231</v>
+      </c>
+      <c r="H841" s="2">
+        <v>423.98104744915304</v>
+      </c>
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D842" s="2"/>
+      <c r="A842" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B842" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C842" s="2">
+        <v>3.54</v>
+      </c>
+      <c r="D842" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E842" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F842" s="2">
+        <v>116.86812775995537</v>
+      </c>
+      <c r="G842" s="2">
+        <v>138.36812775995537</v>
+      </c>
+      <c r="H842" s="2">
+        <v>489.82317227024203</v>
+      </c>
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D843" s="2"/>

--- a/produkte+.xlsx
+++ b/produkte+.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\statistika shitje BI\FAJLET PER UPDATE TE STATISTIKA SHITJESH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB43F28-0752-4DF3-943F-04C70A184525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{469D1608-A1FE-4583-B98B-78654EF96AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F852DC8A-6273-46A5-80EE-4F7A2FD95859}"/>
   </bookViews>
